--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R79f63939f5d442b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Rbc0d10642bc94719"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -37,6 +37,12 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFB82E63"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -87,7 +93,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -147,6 +153,9 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -158,7 +167,7 @@
         <x:color rgb="FF146C62"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE0F3EF"/>
         </x:patternFill>
       </x:fill>
@@ -169,7 +178,7 @@
         <x:color rgb="FF8A5B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D8"/>
         </x:patternFill>
       </x:fill>
@@ -180,7 +189,7 @@
         <x:color rgb="FF9D174D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE7EF"/>
         </x:patternFill>
       </x:fill>
@@ -396,23 +405,35 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="92" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="40" customHeight="1">
+    <x:row r="1" ht="24" hidden="0" customHeight="1">
       <x:c r="A1" s="3" t="str">
         <x:v>Law18Referee Management — Update Summaries</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.33.0 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="28" customHeight="1">
+        <x:v>Current version: v0.34.0 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+      </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3"/>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="9" t="str">
         <x:v>Date</x:v>
       </x:c>
@@ -426,1211 +447,1211 @@
         <x:v>Brief Summary</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="23" t="n">
-        <x:v>46255.5</x:v>
-      </x:c>
-      <x:c r="B5" s="24" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>46255.666666666664</x:v>
+      </x:c>
+      <x:c r="B5" s="29" t="str">
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A14" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A15" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
+        <x:v>v0.31.6</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D16" s="26" t="str">
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A17" s="25" t="n">
+        <x:v>46255.5</x:v>
+      </x:c>
+      <x:c r="B17" s="26" t="str">
         <x:v>v0.31.5</x:v>
       </x:c>
-      <x:c r="C16" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D16" s="26" t="str">
+      <x:c r="C17" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D17" s="26" t="str">
         <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="25" t="n">
-        <x:v>46254.5</x:v>
-      </x:c>
-      <x:c r="B17" s="26" t="str">
-        <x:v>v0.31.4</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D17" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A24" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A25" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
+        <x:v>v0.29.3</x:v>
+      </x:c>
+      <x:c r="C31" s="26" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D31" s="26" t="str">
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A32" s="25" t="n">
+        <x:v>46254.5</x:v>
+      </x:c>
+      <x:c r="B32" s="26" t="str">
         <x:v>v0.29.2</x:v>
       </x:c>
-      <x:c r="C31" s="26" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D31" s="26" t="str">
+      <x:c r="C32" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D32" s="26" t="str">
         <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="25" t="n">
-        <x:v>46253.5</x:v>
-      </x:c>
-      <x:c r="B32" s="26" t="str">
-        <x:v>v0.29.0</x:v>
-      </x:c>
-      <x:c r="C32" s="26" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D32" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A34" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A35" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A36" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A38" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
       <x:c r="A39" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A40" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
       <x:c r="A42" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
       <x:c r="A43" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
       <x:c r="A44" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45">
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A45" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="15" hidden="0" customHeight="1">
       <x:c r="A46" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="15" hidden="0" customHeight="1">
       <x:c r="A48" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
+        <x:v>v0.26.0</x:v>
+      </x:c>
+      <x:c r="C48" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D48" s="26" t="str">
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="15" hidden="0" customHeight="1">
+      <x:c r="A49" s="25" t="n">
+        <x:v>46253.5</x:v>
+      </x:c>
+      <x:c r="B49" s="26" t="str">
         <x:v>v0.25.3</x:v>
       </x:c>
-      <x:c r="C48" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D48" s="26" t="str">
+      <x:c r="C49" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D49" s="26" t="str">
         <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="25" t="n">
-        <x:v>46252.5</x:v>
-      </x:c>
-      <x:c r="B49" s="26" t="str">
-        <x:v>v0.25.2</x:v>
-      </x:c>
-      <x:c r="C49" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D49" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50">
+    <x:row r="50" ht="15" hidden="0" customHeight="1">
       <x:c r="A50" s="25" t="n">
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51">
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="25" t="n">
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52">
+        <x:v>Filters coaching games by venue or site.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="15" hidden="0" customHeight="1">
       <x:c r="A52" s="25" t="n">
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Guide.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53">
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="15" hidden="0" customHeight="1">
       <x:c r="A53" s="25" t="n">
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54">
+        <x:v>Guide.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="15" hidden="0" customHeight="1">
       <x:c r="A54" s="25" t="n">
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
+        <x:v>v0.24.0</x:v>
+      </x:c>
+      <x:c r="C54" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D54" s="26" t="str">
+        <x:v>Securely copies selected officials into another managed group.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="15" hidden="0" customHeight="1">
+      <x:c r="A55" s="25" t="n">
+        <x:v>46252.5</x:v>
+      </x:c>
+      <x:c r="B55" s="26" t="str">
         <x:v>v0.23.2</x:v>
       </x:c>
-      <x:c r="C54" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D54" s="26" t="str">
+      <x:c r="C55" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D55" s="26" t="str">
         <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="25" t="n">
-        <x:v>46248.5</x:v>
-      </x:c>
-      <x:c r="B55" s="26" t="str">
-        <x:v>v0.23.1</x:v>
-      </x:c>
-      <x:c r="C55" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
-      </x:c>
-      <x:c r="D55" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56">
+    <x:row r="56" ht="15" hidden="0" customHeight="1">
       <x:c r="A56" s="25" t="n">
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57">
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="15" hidden="0" customHeight="1">
       <x:c r="A57" s="25" t="n">
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58">
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="15" hidden="0" customHeight="1">
       <x:c r="A58" s="25" t="n">
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59">
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="15" hidden="0" customHeight="1">
       <x:c r="A59" s="25" t="n">
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60">
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="15" hidden="0" customHeight="1">
       <x:c r="A60" s="25" t="n">
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61">
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="15" hidden="0" customHeight="1">
       <x:c r="A61" s="25" t="n">
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62">
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="15" hidden="0" customHeight="1">
       <x:c r="A62" s="25" t="n">
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
+        <x:v>v0.21.6</x:v>
+      </x:c>
+      <x:c r="C62" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D62" s="26" t="str">
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="15" hidden="0" customHeight="1">
+      <x:c r="A63" s="25" t="n">
+        <x:v>46248.5</x:v>
+      </x:c>
+      <x:c r="B63" s="26" t="str">
         <x:v>v0.21.5</x:v>
       </x:c>
-      <x:c r="C62" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D62" s="26" t="str">
+      <x:c r="C63" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D63" s="26" t="str">
         <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="25" t="n">
-        <x:v>46247.5</x:v>
-      </x:c>
-      <x:c r="B63" s="26" t="str">
-        <x:v>v0.21.3</x:v>
-      </x:c>
-      <x:c r="C63" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D63" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64">
+    <x:row r="64" ht="15" hidden="0" customHeight="1">
       <x:c r="A64" s="25" t="n">
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65">
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="25" t="n">
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66">
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="25" t="n">
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67">
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="25" t="n">
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
+        <x:v>v0.20.1</x:v>
+      </x:c>
+      <x:c r="C67" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D67" s="26" t="str">
+        <x:v>Event insert returning rls.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="15" hidden="0" customHeight="1">
+      <x:c r="A68" s="25" t="n">
+        <x:v>46247.5</x:v>
+      </x:c>
+      <x:c r="B68" s="26" t="str">
         <x:v>v0.20.0</x:v>
       </x:c>
-      <x:c r="C67" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D67" s="26" t="str">
+      <x:c r="C68" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D68" s="26" t="str">
         <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
-    <x:row r="68">
-      <x:c r="A68" s="25" t="n">
-        <x:v>46242.5</x:v>
-      </x:c>
-      <x:c r="B68" s="26" t="str">
-        <x:v>v0.19.2</x:v>
-      </x:c>
-      <x:c r="C68" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D68" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69">
+    <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="25" t="n">
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
+        <x:v>v0.19.2</x:v>
+      </x:c>
+      <x:c r="C69" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D69" s="26" t="str">
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="15" hidden="0" customHeight="1">
+      <x:c r="A70" s="25" t="n">
+        <x:v>46242.5</x:v>
+      </x:c>
+      <x:c r="B70" s="26" t="str">
         <x:v>v0.19.1</x:v>
       </x:c>
-      <x:c r="C69" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D69" s="26" t="str">
+      <x:c r="C70" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D70" s="26" t="str">
         <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="25" t="n">
+    <x:row r="71" ht="15" hidden="0" customHeight="1">
+      <x:c r="A71" s="25" t="n">
         <x:v>46241.5</x:v>
       </x:c>
-      <x:c r="B70" s="26" t="str">
+      <x:c r="B71" s="26" t="str">
         <x:v>v0.19.0</x:v>
       </x:c>
-      <x:c r="C70" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D70" s="26" t="str">
+      <x:c r="C71" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D71" s="26" t="str">
         <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="25" t="n">
-        <x:v>46240.5</x:v>
-      </x:c>
-      <x:c r="B71" s="26" t="str">
-        <x:v>v0.18.1</x:v>
-      </x:c>
-      <x:c r="C71" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D71" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72">
+    <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="25" t="n">
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73">
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="25" t="n">
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
+        <x:v>v0.18.0</x:v>
+      </x:c>
+      <x:c r="C73" s="26" t="str">
+        <x:v>Changed</x:v>
+      </x:c>
+      <x:c r="D73" s="26" t="str">
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="15" hidden="0" customHeight="1">
+      <x:c r="A74" s="25" t="n">
+        <x:v>46240.5</x:v>
+      </x:c>
+      <x:c r="B74" s="26" t="str">
         <x:v>v0.17.0</x:v>
       </x:c>
-      <x:c r="C73" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D73" s="26" t="str">
+      <x:c r="C74" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D74" s="26" t="str">
         <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
-    <x:row r="74">
-      <x:c r="A74" s="25" t="n">
-        <x:v>46239.5</x:v>
-      </x:c>
-      <x:c r="B74" s="26" t="str">
-        <x:v>v0.16.0</x:v>
-      </x:c>
-      <x:c r="C74" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D74" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75">
+    <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="25" t="n">
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76">
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="25" t="n">
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77">
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="25" t="n">
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
+        <x:v>v0.15.0</x:v>
+      </x:c>
+      <x:c r="C77" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D77" s="26" t="str">
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="15" hidden="0" customHeight="1">
+      <x:c r="A78" s="25" t="n">
+        <x:v>46239.5</x:v>
+      </x:c>
+      <x:c r="B78" s="26" t="str">
         <x:v>v0.14.0</x:v>
       </x:c>
-      <x:c r="C77" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D77" s="26" t="str">
+      <x:c r="C78" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D78" s="26" t="str">
         <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
-    <x:row r="78">
-      <x:c r="A78" s="25" t="n">
-        <x:v>46238.5</x:v>
-      </x:c>
-      <x:c r="B78" s="26" t="str">
-        <x:v>v0.12.5</x:v>
-      </x:c>
-      <x:c r="C78" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D78" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79">
+    <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="25" t="n">
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80">
+        <x:v>Application header remains visible while scrolling.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="25" t="n">
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81">
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="25" t="n">
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82">
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="25" t="n">
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
+        <x:v>v0.12.2</x:v>
+      </x:c>
+      <x:c r="C82" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D82" s="26" t="str">
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="15" hidden="0" customHeight="1">
+      <x:c r="A83" s="25" t="n">
+        <x:v>46238.5</x:v>
+      </x:c>
+      <x:c r="B83" s="26" t="str">
         <x:v>v0.12.0</x:v>
       </x:c>
-      <x:c r="C82" s="26" t="str">
+      <x:c r="C83" s="26" t="str">
         <x:v>Fixed</x:v>
       </x:c>
-      <x:c r="D82" s="26" t="str">
+      <x:c r="D83" s="26" t="str">
         <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
-    <x:row r="83">
-      <x:c r="A83" s="25" t="n">
-        <x:v>46237.5</x:v>
-      </x:c>
-      <x:c r="B83" s="26" t="str">
-        <x:v>v0.11.2</x:v>
-      </x:c>
-      <x:c r="C83" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D83" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84">
+    <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="25" t="n">
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85">
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="25" t="n">
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
+        <x:v>v0.11.1</x:v>
+      </x:c>
+      <x:c r="C85" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D85" s="26" t="str">
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="15" hidden="0" customHeight="1">
+      <x:c r="A86" s="25" t="n">
+        <x:v>46237.5</x:v>
+      </x:c>
+      <x:c r="B86" s="26" t="str">
         <x:v>v0.11.0</x:v>
       </x:c>
-      <x:c r="C85" s="26" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D85" s="26" t="str">
+      <x:c r="C86" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D86" s="26" t="str">
         <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
-    <x:row r="86">
-      <x:c r="A86" s="25" t="n">
-        <x:v>46234.5</x:v>
-      </x:c>
-      <x:c r="B86" s="26" t="str">
-        <x:v>v0.10.4</x:v>
-      </x:c>
-      <x:c r="C86" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D86" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87">
+    <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="25" t="n">
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88">
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="25" t="n">
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89">
+        <x:v>Unified assignment filter context.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="15" hidden="0" customHeight="1">
       <x:c r="A89" s="25" t="n">
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="15" hidden="0" customHeight="1">
+      <x:c r="A90" s="25" t="n">
+        <x:v>46234.5</x:v>
+      </x:c>
+      <x:c r="B90" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C90" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D90" s="26" t="str">
         <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
-    <x:row r="90">
-      <x:c r="A90" s="25" t="n">
-        <x:v>46233.5</x:v>
-      </x:c>
-      <x:c r="B90" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C90" s="26" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D90" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91">
+    <x:row r="91" ht="15" hidden="0" customHeight="1">
       <x:c r="A91" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1638,13 +1659,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92">
+        <x:v>Add assignment import policy inheritance.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="15" hidden="0" customHeight="1">
       <x:c r="A92" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1655,10 +1676,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93">
+        <x:v>Document assignment import and notification behavior.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="15" hidden="0" customHeight="1">
       <x:c r="A93" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1669,10 +1690,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94">
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="15" hidden="0" customHeight="1">
       <x:c r="A94" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1683,10 +1704,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95">
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="15" hidden="0" customHeight="1">
       <x:c r="A95" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1697,10 +1718,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96">
+        <x:v>Rating history identifies each rating submitter.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="15" hidden="0" customHeight="1">
       <x:c r="A96" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1711,10 +1732,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97">
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1725,10 +1746,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98">
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="15" hidden="0" customHeight="1">
       <x:c r="A98" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1739,10 +1760,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99">
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="15" hidden="0" customHeight="1">
       <x:c r="A99" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1753,10 +1774,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100">
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="15" hidden="0" customHeight="1">
       <x:c r="A100" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1767,10 +1788,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101">
+        <x:v>Page refresh restores the current view and active event.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="15" hidden="0" customHeight="1">
       <x:c r="A101" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1781,10 +1802,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102">
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="15" hidden="0" customHeight="1">
       <x:c r="A102" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1795,10 +1816,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103">
+        <x:v>Align archived event actions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="15" hidden="0" customHeight="1">
       <x:c r="A103" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1809,10 +1830,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104">
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="15" hidden="0" customHeight="1">
       <x:c r="A104" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1823,10 +1844,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105">
+        <x:v>Sort officials by last name.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="15" hidden="0" customHeight="1">
       <x:c r="A105" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1834,13 +1855,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C105" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106">
+        <x:v>Official directory sorts populated values before missing values.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="15" hidden="0" customHeight="1">
       <x:c r="A106" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1848,13 +1869,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C106" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107">
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="15" hidden="0" customHeight="1">
       <x:c r="A107" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1865,10 +1886,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108">
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="15" hidden="0" customHeight="1">
       <x:c r="A108" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1879,10 +1900,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109">
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="15" hidden="0" customHeight="1">
       <x:c r="A109" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1890,13 +1911,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C109" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110">
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="15" hidden="0" customHeight="1">
       <x:c r="A110" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1904,13 +1925,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C110" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111">
+        <x:v>Fix ratings history migration syntax.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="15" hidden="0" customHeight="1">
       <x:c r="A111" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1921,10 +1942,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112">
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="15" hidden="0" customHeight="1">
       <x:c r="A112" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1935,10 +1956,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113">
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="15" hidden="0" customHeight="1">
       <x:c r="A113" s="25" t="n">
         <x:v>46233.5</x:v>
       </x:c>
@@ -1949,570 +1970,570 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="15" hidden="0" customHeight="1">
+      <x:c r="A114" s="25" t="n">
+        <x:v>46233.5</x:v>
+      </x:c>
+      <x:c r="B114" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C114" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D114" s="26" t="str">
         <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
-    <x:row r="114">
-      <x:c r="A114" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B114" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C114" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D114" s="26" t="str">
+    <x:row r="115" ht="15" hidden="0" customHeight="1">
+      <x:c r="A115" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B115" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C115" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D115" s="26" t="str">
         <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
-    <x:row r="115">
-      <x:c r="A115" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B115" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C115" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D115" s="26" t="str">
+    <x:row r="116" ht="15" hidden="0" customHeight="1">
+      <x:c r="A116" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B116" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C116" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D116" s="26" t="str">
         <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
-    <x:row r="116">
-      <x:c r="A116" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B116" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C116" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D116" s="26" t="str">
+    <x:row r="117" ht="15" hidden="0" customHeight="1">
+      <x:c r="A117" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B117" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C117" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D117" s="26" t="str">
         <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
-    <x:row r="117">
-      <x:c r="A117" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B117" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C117" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D117" s="26" t="str">
+    <x:row r="118" ht="15" hidden="0" customHeight="1">
+      <x:c r="A118" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B118" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C118" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D118" s="26" t="str">
         <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
-    <x:row r="118">
-      <x:c r="A118" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B118" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C118" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D118" s="26" t="str">
+    <x:row r="119" ht="15" hidden="0" customHeight="1">
+      <x:c r="A119" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B119" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C119" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D119" s="26" t="str">
         <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
-    <x:row r="119">
-      <x:c r="A119" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B119" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C119" s="26" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D119" s="26" t="str">
+    <x:row r="120" ht="15" hidden="0" customHeight="1">
+      <x:c r="A120" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B120" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C120" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D120" s="26" t="str">
         <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
-    <x:row r="120">
-      <x:c r="A120" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B120" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C120" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D120" s="26" t="str">
+    <x:row r="121" ht="15" hidden="0" customHeight="1">
+      <x:c r="A121" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B121" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C121" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D121" s="26" t="str">
         <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
-    <x:row r="121">
-      <x:c r="A121" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B121" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C121" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D121" s="26" t="str">
+    <x:row r="122" ht="15" hidden="0" customHeight="1">
+      <x:c r="A122" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B122" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C122" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D122" s="26" t="str">
         <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
-    <x:row r="122">
-      <x:c r="A122" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B122" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C122" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D122" s="26" t="str">
+    <x:row r="123" ht="15" hidden="0" customHeight="1">
+      <x:c r="A123" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B123" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C123" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D123" s="26" t="str">
         <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
-    <x:row r="123">
-      <x:c r="A123" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B123" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C123" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D123" s="26" t="str">
+    <x:row r="124" ht="15" hidden="0" customHeight="1">
+      <x:c r="A124" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B124" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C124" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D124" s="26" t="str">
         <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
-    <x:row r="124">
-      <x:c r="A124" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B124" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C124" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D124" s="26" t="str">
+    <x:row r="125" ht="15" hidden="0" customHeight="1">
+      <x:c r="A125" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B125" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C125" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D125" s="26" t="str">
         <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
-    <x:row r="125">
-      <x:c r="A125" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B125" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C125" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D125" s="26" t="str">
+    <x:row r="126" ht="15" hidden="0" customHeight="1">
+      <x:c r="A126" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B126" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C126" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D126" s="26" t="str">
         <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
-    <x:row r="126">
-      <x:c r="A126" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B126" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C126" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D126" s="26" t="str">
+    <x:row r="127" ht="15" hidden="0" customHeight="1">
+      <x:c r="A127" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B127" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C127" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D127" s="26" t="str">
         <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
-    <x:row r="127">
-      <x:c r="A127" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B127" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C127" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D127" s="26" t="str">
+    <x:row r="128" ht="15" hidden="0" customHeight="1">
+      <x:c r="A128" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B128" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C128" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D128" s="26" t="str">
         <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
-    <x:row r="128">
-      <x:c r="A128" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B128" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C128" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D128" s="26" t="str">
+    <x:row r="129" ht="15" hidden="0" customHeight="1">
+      <x:c r="A129" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B129" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C129" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D129" s="26" t="str">
         <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
-    <x:row r="129">
-      <x:c r="A129" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B129" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C129" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D129" s="26" t="str">
+    <x:row r="130" ht="15" hidden="0" customHeight="1">
+      <x:c r="A130" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B130" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C130" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D130" s="26" t="str">
         <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
-    <x:row r="130">
-      <x:c r="A130" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B130" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C130" s="26" t="str">
+    <x:row r="131" ht="15" hidden="0" customHeight="1">
+      <x:c r="A131" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B131" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C131" s="26" t="str">
         <x:v>Changed</x:v>
       </x:c>
-      <x:c r="D130" s="26" t="str">
+      <x:c r="D131" s="26" t="str">
         <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
-    <x:row r="131">
-      <x:c r="A131" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B131" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C131" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D131" s="26" t="str">
+    <x:row r="132" ht="15" hidden="0" customHeight="1">
+      <x:c r="A132" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B132" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C132" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D132" s="26" t="str">
         <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
-    <x:row r="132">
-      <x:c r="A132" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B132" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C132" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D132" s="26" t="str">
+    <x:row r="133" ht="15" hidden="0" customHeight="1">
+      <x:c r="A133" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B133" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C133" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D133" s="26" t="str">
         <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
-    <x:row r="133">
-      <x:c r="A133" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B133" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C133" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D133" s="26" t="str">
+    <x:row r="134" ht="15" hidden="0" customHeight="1">
+      <x:c r="A134" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B134" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C134" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D134" s="26" t="str">
         <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
-    <x:row r="134">
-      <x:c r="A134" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B134" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C134" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D134" s="26" t="str">
+    <x:row r="135" ht="15" hidden="0" customHeight="1">
+      <x:c r="A135" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B135" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C135" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D135" s="26" t="str">
         <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
-    <x:row r="135">
-      <x:c r="A135" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B135" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C135" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D135" s="26" t="str">
+    <x:row r="136" ht="15" hidden="0" customHeight="1">
+      <x:c r="A136" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B136" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C136" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D136" s="26" t="str">
         <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
-    <x:row r="136">
-      <x:c r="A136" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B136" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C136" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D136" s="26" t="str">
+    <x:row r="137" ht="15" hidden="0" customHeight="1">
+      <x:c r="A137" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B137" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C137" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D137" s="26" t="str">
         <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
-    <x:row r="137">
-      <x:c r="A137" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B137" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C137" s="26" t="str">
+    <x:row r="138" ht="15" hidden="0" customHeight="1">
+      <x:c r="A138" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B138" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C138" s="26" t="str">
         <x:v>Removed / Restricted</x:v>
       </x:c>
-      <x:c r="D137" s="26" t="str">
+      <x:c r="D138" s="26" t="str">
         <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
-    <x:row r="138">
-      <x:c r="A138" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B138" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C138" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D138" s="26" t="str">
+    <x:row r="139" ht="15" hidden="0" customHeight="1">
+      <x:c r="A139" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B139" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C139" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D139" s="26" t="str">
         <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
-    <x:row r="139">
-      <x:c r="A139" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B139" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C139" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D139" s="26" t="str">
+    <x:row r="140" ht="15" hidden="0" customHeight="1">
+      <x:c r="A140" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B140" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C140" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D140" s="26" t="str">
         <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
-    <x:row r="140">
-      <x:c r="A140" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B140" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C140" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D140" s="26" t="str">
+    <x:row r="141" ht="15" hidden="0" customHeight="1">
+      <x:c r="A141" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B141" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C141" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D141" s="26" t="str">
         <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
-    <x:row r="141">
-      <x:c r="A141" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B141" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C141" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D141" s="26" t="str">
+    <x:row r="142" ht="15" hidden="0" customHeight="1">
+      <x:c r="A142" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B142" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C142" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D142" s="26" t="str">
         <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
-    <x:row r="142">
-      <x:c r="A142" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B142" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C142" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D142" s="26" t="str">
+    <x:row r="143" ht="15" hidden="0" customHeight="1">
+      <x:c r="A143" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B143" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C143" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D143" s="26" t="str">
         <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
-    <x:row r="143">
-      <x:c r="A143" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B143" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C143" s="26" t="str">
+    <x:row r="144" ht="15" hidden="0" customHeight="1">
+      <x:c r="A144" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B144" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C144" s="26" t="str">
         <x:v>Removed / Restricted</x:v>
       </x:c>
-      <x:c r="D143" s="26" t="str">
+      <x:c r="D144" s="26" t="str">
         <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
-    <x:row r="144">
-      <x:c r="A144" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B144" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C144" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D144" s="26" t="str">
+    <x:row r="145" ht="15" hidden="0" customHeight="1">
+      <x:c r="A145" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B145" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C145" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D145" s="26" t="str">
         <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
-    <x:row r="145">
-      <x:c r="A145" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B145" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C145" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D145" s="26" t="str">
+    <x:row r="146" ht="15" hidden="0" customHeight="1">
+      <x:c r="A146" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B146" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C146" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D146" s="26" t="str">
         <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
-    <x:row r="146">
-      <x:c r="A146" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B146" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C146" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D146" s="26" t="str">
+    <x:row r="147" ht="15" hidden="0" customHeight="1">
+      <x:c r="A147" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B147" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C147" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D147" s="26" t="str">
         <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
-    <x:row r="147">
-      <x:c r="A147" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B147" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C147" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D147" s="26" t="str">
+    <x:row r="148" ht="15" hidden="0" customHeight="1">
+      <x:c r="A148" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B148" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C148" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D148" s="26" t="str">
         <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
-    <x:row r="148">
-      <x:c r="A148" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B148" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C148" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D148" s="26" t="str">
+    <x:row r="149" ht="15" hidden="0" customHeight="1">
+      <x:c r="A149" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B149" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C149" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D149" s="26" t="str">
         <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
-    <x:row r="149">
-      <x:c r="A149" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B149" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C149" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D149" s="26" t="str">
+    <x:row r="150" ht="15" hidden="0" customHeight="1">
+      <x:c r="A150" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B150" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C150" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D150" s="26" t="str">
         <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
-    <x:row r="150">
-      <x:c r="A150" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B150" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C150" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D150" s="26" t="str">
+    <x:row r="151" ht="15" hidden="0" customHeight="1">
+      <x:c r="A151" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B151" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C151" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D151" s="26" t="str">
         <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
-    <x:row r="151">
-      <x:c r="A151" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B151" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C151" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D151" s="26" t="str">
+    <x:row r="152" ht="15" hidden="0" customHeight="1">
+      <x:c r="A152" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B152" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C152" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D152" s="26" t="str">
         <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="152">
-      <x:c r="A152" s="25" t="n">
-        <x:v>46232.5</x:v>
-      </x:c>
-      <x:c r="B152" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C152" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D152" s="26" t="str">
+    <x:row r="153" ht="15" hidden="0" customHeight="1">
+      <x:c r="A153" s="25" t="n">
+        <x:v>46232.5</x:v>
+      </x:c>
+      <x:c r="B153" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C153" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D153" s="26" t="str">
         <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
-    <x:row r="153">
-      <x:c r="A153" s="25" t="n">
-        <x:v>46229.5</x:v>
-      </x:c>
-      <x:c r="B153" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C153" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D153" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154">
+    <x:row r="154" ht="15" hidden="0" customHeight="1">
       <x:c r="A154" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2520,13 +2541,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C154" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="155">
+        <x:v>Align assignment board crew tiles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="15" hidden="0" customHeight="1">
       <x:c r="A155" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2534,13 +2555,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C155" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156">
+        <x:v>Add check-in roster sorting and filters.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="15" hidden="0" customHeight="1">
       <x:c r="A156" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2548,13 +2569,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C156" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157">
+        <x:v>Auto-refresh live check-in attendance.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="15" hidden="0" customHeight="1">
       <x:c r="A157" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2562,13 +2583,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C157" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158">
+        <x:v>Fix daily check-in upsert constraint.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="15" hidden="0" customHeight="1">
       <x:c r="A158" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2576,13 +2597,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C158" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159">
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="15" hidden="0" customHeight="1">
       <x:c r="A159" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2596,7 +2617,7 @@
         <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
-    <x:row r="160">
+    <x:row r="160" ht="15" hidden="0" customHeight="1">
       <x:c r="A160" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2607,10 +2628,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161">
+        <x:v>Sort game times chronologically.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="15" hidden="0" customHeight="1">
       <x:c r="A161" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2618,13 +2639,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C161" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162">
+        <x:v>Support private owner records and multiple official roles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="15" hidden="0" customHeight="1">
       <x:c r="A162" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2632,13 +2653,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C162" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163">
+        <x:v>Add official record editing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="15" hidden="0" customHeight="1">
       <x:c r="A163" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2646,13 +2667,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C163" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164">
+        <x:v>Title-case dashboard navigation labels.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="15" hidden="0" customHeight="1">
       <x:c r="A164" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2660,13 +2681,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C164" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165">
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="15" hidden="0" customHeight="1">
       <x:c r="A165" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2674,41 +2695,41 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C165" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166">
+        <x:v>Fix recursive game privacy policy.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="15" hidden="0" customHeight="1">
       <x:c r="A166" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B166" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C166" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167">
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="15" hidden="0" customHeight="1">
       <x:c r="A167" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B167" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168">
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="15" hidden="0" customHeight="1">
       <x:c r="A168" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2719,10 +2740,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169">
+        <x:v>Interpret imported game times in event timezone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="15" hidden="0" customHeight="1">
       <x:c r="A169" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2730,13 +2751,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170">
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="15" hidden="0" customHeight="1">
       <x:c r="A170" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2747,10 +2768,10 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171">
+        <x:v>Add sortable operations and scoped event roles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="15" hidden="0" customHeight="1">
       <x:c r="A171" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2758,13 +2779,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172">
+        <x:v>Add organization and event position aliases.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="15" hidden="0" customHeight="1">
       <x:c r="A172" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2772,13 +2793,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173">
+        <x:v>Preserve Assignr assignment position titles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="15" hidden="0" customHeight="1">
       <x:c r="A173" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2786,13 +2807,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174">
+        <x:v>Fix scoped import job permissions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="15" hidden="0" customHeight="1">
       <x:c r="A174" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2800,13 +2821,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175">
+        <x:v>Add official account invitation email draft.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="15" hidden="0" customHeight="1">
       <x:c r="A175" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2814,13 +2835,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176">
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="15" hidden="0" customHeight="1">
       <x:c r="A176" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2828,13 +2849,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177">
+        <x:v>Fix schedule timestamp formatting.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="15" hidden="0" customHeight="1">
       <x:c r="A177" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2845,10 +2866,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178">
+        <x:v>Show dates on game schedule.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="15" hidden="0" customHeight="1">
       <x:c r="A178" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2856,13 +2877,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179">
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="15" hidden="0" customHeight="1">
       <x:c r="A179" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2873,10 +2894,10 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180">
+        <x:v>Add configurable crew ratings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="15" hidden="0" customHeight="1">
       <x:c r="A180" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2887,10 +2908,10 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181">
+        <x:v>Add reusable appearance themes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="15" hidden="0" customHeight="1">
       <x:c r="A181" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2898,13 +2919,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182">
+        <x:v>Add organization context and manual records.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="15" hidden="0" customHeight="1">
       <x:c r="A182" s="25" t="n">
         <x:v>46229.5</x:v>
       </x:c>
@@ -2912,55 +2933,55 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
+        <x:v>Replace Georgia display font with Inter.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="15" hidden="0" customHeight="1">
+      <x:c r="A183" s="25" t="n">
+        <x:v>46229.5</x:v>
+      </x:c>
+      <x:c r="B183" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C183" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D183" s="26" t="str">
         <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
-    <x:row r="183">
-      <x:c r="A183" s="25" t="n">
-        <x:v>46228.5</x:v>
-      </x:c>
-      <x:c r="B183" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C183" s="26" t="str">
-        <x:v>Fixed</x:v>
-      </x:c>
-      <x:c r="D183" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184">
+    <x:row r="184" ht="15" hidden="0" customHeight="1">
       <x:c r="A184" s="25" t="n">
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B184" s="26" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C184" s="26" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D184" s="26" t="str">
+        <x:v>Fix recursive event access policies.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="15" hidden="0" customHeight="1">
+      <x:c r="A185" s="25" t="n">
+        <x:v>46228.5</x:v>
+      </x:c>
+      <x:c r="B185" s="26" t="str">
         <x:v>v0.2.0</x:v>
       </x:c>
-      <x:c r="C184" s="26" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D184" s="26" t="str">
+      <x:c r="C185" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D185" s="26" t="str">
         <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
-    <x:row r="185">
-      <x:c r="A185" s="25" t="n">
-        <x:v>46227.5</x:v>
-      </x:c>
-      <x:c r="B185" s="26" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C185" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
-      </x:c>
-      <x:c r="D185" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="186">
+    <x:row r="186" ht="15" hidden="0" customHeight="1">
       <x:c r="A186" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -2968,13 +2989,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187">
+        <x:v>Remove footer slogan.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="15" hidden="0" customHeight="1">
       <x:c r="A187" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -2985,10 +3006,10 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="188">
+        <x:v>Add account membership controls.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="15" hidden="0" customHeight="1">
       <x:c r="A188" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -2999,10 +3020,10 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189">
+        <x:v>Add dashboard and account menu.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="15" hidden="0" customHeight="1">
       <x:c r="A189" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3010,13 +3031,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="190">
+        <x:v>Add selected Law18Ref logo.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="15" hidden="0" customHeight="1">
       <x:c r="A190" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3027,10 +3048,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="191">
+        <x:v>Apply navy and berry site branding.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="15" hidden="0" customHeight="1">
       <x:c r="A191" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3041,10 +3062,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="192">
+        <x:v>Update database comments for new brand.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="15" hidden="0" customHeight="1">
       <x:c r="A192" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3055,10 +3076,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="193">
+        <x:v>Update tests for Law18Referee Management.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="15" hidden="0" customHeight="1">
       <x:c r="A193" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3066,13 +3087,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="194">
+        <x:v>Document Law18Referee Management rebrand.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="15" hidden="0" customHeight="1">
       <x:c r="A194" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3080,13 +3101,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195">
+        <x:v>Add Law18Referee Management brand assets.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="15" hidden="0" customHeight="1">
       <x:c r="A195" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3094,13 +3115,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C195" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196">
+        <x:v>Rename platform to Law18Referee Management.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="15" hidden="0" customHeight="1">
       <x:c r="A196" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3111,10 +3132,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197">
+        <x:v>Test repeat schedule imports.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="15" hidden="0" customHeight="1">
       <x:c r="A197" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3125,10 +3146,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Support staged schedule imports.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198">
+        <x:v>Document repeat schedule imports.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="15" hidden="0" customHeight="1">
       <x:c r="A198" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3139,10 +3160,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199">
+        <x:v>Support staged schedule imports.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="15" hidden="0" customHeight="1">
       <x:c r="A199" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3153,10 +3174,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200">
+        <x:v>Grant authenticated access to RLS tables.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="15" hidden="0" customHeight="1">
       <x:c r="A200" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3164,13 +3185,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C200" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201">
+        <x:v>Document small-tournament pilot.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="15" hidden="0" customHeight="1">
       <x:c r="A201" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3181,10 +3202,10 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202">
+        <x:v>Add small-tournament Supabase migration.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="15" hidden="0" customHeight="1">
       <x:c r="A202" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3195,10 +3216,10 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203">
+        <x:v>Add installable mobile RefHQ experience.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="15" hidden="0" customHeight="1">
       <x:c r="A203" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3206,13 +3227,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C203" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204">
+        <x:v>Build small-tournament pilot workflows.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="15" hidden="0" customHeight="1">
       <x:c r="A204" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3223,10 +3244,10 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205">
+        <x:v>Require Supabase login for RefHQ.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="15" hidden="0" customHeight="1">
       <x:c r="A205" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3234,13 +3255,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C205" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206">
+        <x:v>Style Supabase sign-in.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="15" hidden="0" customHeight="1">
       <x:c r="A206" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3251,10 +3272,10 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="207">
+        <x:v>Add RefHQ sign-in screen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="15" hidden="0" customHeight="1">
       <x:c r="A207" s="25" t="n">
         <x:v>46227.5</x:v>
       </x:c>
@@ -3262,23 +3283,37 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C207" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D207" s="26" t="str">
+        <x:v>Add Supabase authentication client.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="15" hidden="0" customHeight="1">
+      <x:c r="A208" s="27" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B208" s="28" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C208" s="28" t="str">
         <x:v>Fixed</x:v>
       </x:c>
-      <x:c r="D207" s="26" t="str">
+      <x:c r="D208" s="28" t="str">
         <x:v>Fix Cloudflare package installation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="208">
-      <x:c r="A208" s="27" t="n">
+    <x:row r="209" ht="15" hidden="0" customHeight="1">
+      <x:c r="A209" t="n">
         <x:v>46226.5</x:v>
       </x:c>
-      <x:c r="B208" s="28" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C208" s="28" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D208" s="28" t="str">
+      <x:c r="B209" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C209" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D209" t="str">
         <x:v>Build RefHQ MVP.</x:v>
       </x:c>
     </x:row>
@@ -3294,7 +3329,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R780f1225f3e94e38"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra137436417774ec8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Rbc0d10642bc94719"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R5fa4640153a2413f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D208" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D209" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.34.0 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.34.2 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -452,41 +452,41 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -494,13 +494,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -508,83 +508,83 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -592,69 +592,69 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="25" t="n">
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A18" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -662,13 +662,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,13 +676,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,13 +690,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,27 +704,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,27 +732,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="15" hidden="0" customHeight="1">
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A26" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,13 +760,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,27 +774,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="15" hidden="0" customHeight="1">
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A29" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +802,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,55 +816,55 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="25" t="n">
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
+        <x:v>v0.29.4</x:v>
+      </x:c>
+      <x:c r="C32" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D32" s="26" t="str">
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A33" s="25" t="n">
+        <x:v>46254.5</x:v>
+      </x:c>
+      <x:c r="B33" s="26" t="str">
+        <x:v>v0.29.3</x:v>
+      </x:c>
+      <x:c r="C33" s="26" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D33" s="26" t="str">
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="25" t="n">
+        <x:v>46254.5</x:v>
+      </x:c>
+      <x:c r="B34" s="26" t="str">
         <x:v>v0.29.2</x:v>
       </x:c>
-      <x:c r="C32" s="26" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D32" s="26" t="str">
+      <x:c r="C34" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D34" s="26" t="str">
         <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="25" t="n">
-        <x:v>46253.5</x:v>
-      </x:c>
-      <x:c r="B33" s="26" t="str">
-        <x:v>v0.29.0</x:v>
-      </x:c>
-      <x:c r="C33" s="26" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D33" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A34" s="25" t="n">
-        <x:v>46253.5</x:v>
-      </x:c>
-      <x:c r="B34" s="26" t="str">
-        <x:v>v0.28.1</x:v>
-      </x:c>
-      <x:c r="C34" s="26" t="str">
-        <x:v>Fixed</x:v>
-      </x:c>
-      <x:c r="D34" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,13 +872,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,83 +886,83 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="15" hidden="0" customHeight="1">
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A37" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="15" hidden="0" customHeight="1">
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A39" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="15" hidden="0" customHeight="1">
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A41" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,27 +970,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="15" hidden="0" customHeight="1">
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A43" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,41 +998,41 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="26.399999618530273" hidden="0" customHeight="1">
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
       <x:c r="A45" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="15" hidden="0" customHeight="1">
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A46" s="25" t="n">
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,41 +1068,41 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
       <x:c r="A50" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,13 +1110,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,13 +1124,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,13 +1138,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,41 +1152,41 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
       <x:c r="A56" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="15" hidden="0" customHeight="1">
+        <x:v>Securely copies selected officials into another managed group.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A57" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1194,13 +1194,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1208,13 +1208,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1222,13 +1222,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1236,13 +1236,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1250,13 +1250,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1264,41 +1264,41 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
       <x:c r="A64" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1306,13 +1306,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1320,13 +1320,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1334,83 +1334,83 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
       <x:c r="A70" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1418,41 +1418,41 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1460,13 +1460,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1474,41 +1474,41 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1516,13 +1516,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1530,13 +1530,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1544,41 +1544,41 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1586,41 +1586,41 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1628,13 +1628,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1642,32 +1642,32 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
       <x:c r="A91" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
       <x:c r="A92" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
         <x:v>Early build</x:v>
@@ -1676,7 +1676,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1687,10 +1687,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1704,7 +1704,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1718,7 +1718,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1732,7 +1732,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1746,7 +1746,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1760,7 +1760,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1774,7 +1774,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1788,7 +1788,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1802,7 +1802,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1816,7 +1816,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1830,7 +1830,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1858,7 +1858,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1869,10 +1869,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C106" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1897,10 +1897,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C108" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1914,7 +1914,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1925,10 +1925,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C110" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1942,7 +1942,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1953,10 +1953,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C112" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1970,7 +1970,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1984,12 +1984,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
       <x:c r="A115" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B115" s="26" t="str">
         <x:v>Early build</x:v>
@@ -1998,12 +1998,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
       <x:c r="A116" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B116" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2012,7 +2012,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2026,7 +2026,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2040,7 +2040,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2054,7 +2054,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2065,10 +2065,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C120" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2082,7 +2082,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2093,10 +2093,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C122" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2110,7 +2110,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2124,7 +2124,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2138,7 +2138,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2152,7 +2152,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2166,7 +2166,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2180,7 +2180,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2194,7 +2194,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2208,7 +2208,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2219,10 +2219,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C131" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2236,7 +2236,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2247,10 +2247,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C133" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2264,7 +2264,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2278,7 +2278,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2292,7 +2292,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2306,7 +2306,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2317,13 +2317,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C138" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="139" ht="15" hidden="0" customHeight="1">
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A139" s="25" t="n">
         <x:v>46232.5</x:v>
       </x:c>
@@ -2334,7 +2334,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2345,10 +2345,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C140" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2362,7 +2362,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2376,7 +2376,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2390,7 +2390,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2401,13 +2401,13 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C144" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" ht="15" hidden="0" customHeight="1">
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A145" s="25" t="n">
         <x:v>46232.5</x:v>
       </x:c>
@@ -2418,7 +2418,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2429,10 +2429,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C146" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2446,7 +2446,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2474,7 +2474,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2488,7 +2488,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2502,7 +2502,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2516,7 +2516,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2530,12 +2530,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
       <x:c r="A154" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B154" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2544,21 +2544,21 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
       <x:c r="A155" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B155" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C155" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2572,7 +2572,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2583,10 +2583,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C157" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2597,10 +2597,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C158" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2611,10 +2611,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C159" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2625,10 +2625,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C160" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2642,7 +2642,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2653,10 +2653,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C162" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2670,7 +2670,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2681,10 +2681,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C164" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2695,10 +2695,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C165" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2709,10 +2709,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C166" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2720,13 +2720,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B167" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2740,7 +2740,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2748,13 +2748,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B169" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2765,10 +2765,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2779,10 +2779,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2793,10 +2793,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2807,10 +2807,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2821,10 +2821,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2835,10 +2835,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2849,10 +2849,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2866,7 +2866,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2877,10 +2877,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2891,10 +2891,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2905,10 +2905,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2922,7 +2922,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2933,10 +2933,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2950,63 +2950,63 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
       <x:c r="A184" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B184" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
       <x:c r="A185" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B185" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
       <x:c r="A186" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B186" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187" ht="15" hidden="0" customHeight="1">
+        <x:v>Fix recursive event access policies.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A187" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B187" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3017,10 +3017,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3034,7 +3034,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3045,10 +3045,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3059,10 +3059,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3076,7 +3076,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3090,7 +3090,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3101,10 +3101,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3115,10 +3115,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C195" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3129,10 +3129,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C196" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3143,10 +3143,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C197" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3160,7 +3160,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3174,7 +3174,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3188,7 +3188,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3199,10 +3199,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C201" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3213,10 +3213,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C202" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3230,7 +3230,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3241,10 +3241,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C204" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3255,10 +3255,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C205" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3269,10 +3269,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C206" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3283,10 +3283,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C207" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
+        <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3297,23 +3297,51 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C208" s="28" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Fix Cloudflare package installation.</x:v>
+        <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
       <x:c r="A209" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B209" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C209" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D209" t="str">
+        <x:v>Add Supabase authentication client.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="15" hidden="0" customHeight="1">
+      <x:c r="A210" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B210" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C210" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D210" t="str">
+        <x:v>Fix Cloudflare package installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" t="n">
         <x:v>46226.5</x:v>
       </x:c>
-      <x:c r="B209" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C209" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D209" t="str">
+      <x:c r="B211" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C211" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D211" t="str">
         <x:v>Build RefHQ MVP.</x:v>
       </x:c>
     </x:row>
@@ -3329,7 +3357,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra137436417774ec8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re96bb69aadcd46d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R5fa4640153a2413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R5e1cfeeaaa3f481b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D209" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D210" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.34.2 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.34.3 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -449,16 +449,16 @@
     </x:row>
     <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="23" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -466,13 +466,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -480,27 +480,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -508,13 +508,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -522,13 +522,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -536,13 +536,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -550,13 +550,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -564,13 +564,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -578,13 +578,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -592,13 +592,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -606,13 +606,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -620,13 +620,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -634,13 +634,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -648,27 +648,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,13 +676,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,13 +690,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,13 +704,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -718,13 +718,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,13 +732,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -746,13 +746,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,13 +760,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,13 +774,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -788,13 +788,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +802,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,13 +816,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -830,13 +830,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +844,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,27 +858,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A35" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,13 +886,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -900,13 +900,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -914,13 +914,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -928,13 +928,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -942,13 +942,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -956,13 +956,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,13 +970,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -984,13 +984,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,13 +998,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1012,13 +1012,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1026,13 +1026,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1068,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1082,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,27 +1096,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
       <x:c r="A52" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,13 +1124,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,13 +1138,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,13 +1152,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1166,13 +1166,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1180,27 +1180,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
       <x:c r="A58" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1208,13 +1208,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1222,13 +1222,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1236,13 +1236,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1250,13 +1250,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1264,13 +1264,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1278,13 +1278,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1292,27 +1292,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1320,13 +1320,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1334,13 +1334,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1348,13 +1348,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1362,27 +1362,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1390,41 +1390,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
       <x:c r="A74" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1432,13 +1432,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1446,27 +1446,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1474,13 +1474,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1488,13 +1488,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1502,27 +1502,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1530,13 +1530,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1544,13 +1544,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1558,13 +1558,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1572,27 +1572,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1600,13 +1600,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1614,27 +1614,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
       <x:c r="A89" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1642,13 +1642,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1656,13 +1656,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1670,27 +1670,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
       <x:c r="A93" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1701,10 +1701,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1718,7 +1718,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1732,7 +1732,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1746,7 +1746,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1760,7 +1760,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1774,7 +1774,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1788,7 +1788,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1802,7 +1802,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1816,7 +1816,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1830,7 +1830,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1858,7 +1858,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1872,7 +1872,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1897,10 +1897,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C108" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1911,10 +1911,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C109" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1928,7 +1928,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1942,7 +1942,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1953,10 +1953,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C112" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1967,10 +1967,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C113" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1984,7 +1984,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1998,7 +1998,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2012,12 +2012,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
       <x:c r="A117" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B117" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2026,7 +2026,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2040,7 +2040,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2054,7 +2054,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2068,7 +2068,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2082,7 +2082,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2093,10 +2093,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C122" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2107,10 +2107,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C123" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2124,7 +2124,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2138,7 +2138,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2152,7 +2152,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2166,7 +2166,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2180,7 +2180,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2194,7 +2194,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2208,7 +2208,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2222,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2236,7 +2236,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2247,10 +2247,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C133" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2261,10 +2261,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C134" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2278,7 +2278,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2292,7 +2292,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2306,7 +2306,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2320,7 +2320,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2334,7 +2334,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2345,10 +2345,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C140" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2359,10 +2359,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C141" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2376,7 +2376,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2390,7 +2390,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2404,7 +2404,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2418,7 +2418,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2429,10 +2429,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C146" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2443,10 +2443,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C147" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2474,7 +2474,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2488,7 +2488,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2502,7 +2502,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2516,7 +2516,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2530,7 +2530,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2544,7 +2544,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2558,12 +2558,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
       <x:c r="A156" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B156" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2572,7 +2572,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2583,10 +2583,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C157" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2597,10 +2597,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C158" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2611,10 +2611,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C159" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2625,10 +2625,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C160" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2639,10 +2639,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C161" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2670,7 +2670,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2681,10 +2681,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C164" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2695,10 +2695,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C165" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2709,10 +2709,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C166" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2723,10 +2723,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2737,10 +2737,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C168" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2748,13 +2748,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B169" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2762,13 +2762,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B170" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2782,7 +2782,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2793,10 +2793,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2810,7 +2810,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2821,10 +2821,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2835,10 +2835,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2849,10 +2849,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2863,10 +2863,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2877,10 +2877,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2891,10 +2891,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2908,7 +2908,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2919,10 +2919,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2936,7 +2936,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2950,7 +2950,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2961,10 +2961,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2975,24 +2975,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
       <x:c r="A186" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B186" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3000,27 +3000,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B187" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
       <x:c r="A188" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B188" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3031,10 +3031,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3048,7 +3048,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3062,7 +3062,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3073,10 +3073,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3090,7 +3090,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3104,7 +3104,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3118,7 +3118,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3129,10 +3129,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C196" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3143,10 +3143,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C197" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3157,10 +3157,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C198" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3174,7 +3174,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3188,7 +3188,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3202,7 +3202,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3216,7 +3216,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3227,10 +3227,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C203" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3244,7 +3244,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3258,7 +3258,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3269,10 +3269,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C206" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3286,7 +3286,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3297,10 +3297,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C208" s="28" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
+        <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3314,7 +3314,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
+        <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3325,23 +3325,37 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C210" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Fix Cloudflare package installation.</x:v>
+        <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B211" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C211" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D211" t="str">
+        <x:v>Fix Cloudflare package installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" t="n">
         <x:v>46226.5</x:v>
       </x:c>
-      <x:c r="B211" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C211" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D211" t="str">
+      <x:c r="B212" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C212" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D212" t="str">
         <x:v>Build RefHQ MVP.</x:v>
       </x:c>
     </x:row>
@@ -3357,7 +3371,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re96bb69aadcd46d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf36752d3433f4895"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R5e1cfeeaaa3f481b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Rbcc85f4898d34109"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D210" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D211" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.34.3 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.34.4 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -449,30 +449,30 @@
     </x:row>
     <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="23" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -480,13 +480,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -494,27 +494,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -522,13 +522,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -536,13 +536,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -550,13 +550,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -564,13 +564,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -578,13 +578,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -592,13 +592,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -606,13 +606,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -620,13 +620,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -634,13 +634,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -648,13 +648,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -662,27 +662,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,13 +690,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,13 +704,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -718,13 +718,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,13 +732,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -746,13 +746,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,13 +760,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,13 +774,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -788,13 +788,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +802,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,13 +816,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -830,13 +830,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +844,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,13 +858,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,27 +872,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A36" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -900,13 +900,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -914,13 +914,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -928,13 +928,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -942,13 +942,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -956,13 +956,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,13 +970,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -984,13 +984,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,13 +998,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1012,13 +1012,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1026,13 +1026,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1068,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1082,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,13 +1096,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,27 +1110,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
       <x:c r="A53" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,13 +1138,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,13 +1152,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1166,13 +1166,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1180,13 +1180,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1194,27 +1194,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
       <x:c r="A59" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1222,13 +1222,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1236,13 +1236,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1250,13 +1250,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1264,13 +1264,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1278,13 +1278,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1292,13 +1292,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1306,27 +1306,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1334,13 +1334,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1348,13 +1348,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1362,13 +1362,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1376,27 +1376,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1404,41 +1404,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
       <x:c r="A74" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1446,13 +1446,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1460,27 +1460,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
       <x:c r="A78" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1488,13 +1488,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1502,13 +1502,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1516,27 +1516,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1544,13 +1544,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1558,13 +1558,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1572,13 +1572,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1586,27 +1586,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1614,13 +1614,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1628,27 +1628,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
       <x:c r="A90" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1656,13 +1656,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1670,13 +1670,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1684,27 +1684,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
       <x:c r="A94" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1715,10 +1715,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1732,7 +1732,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1746,7 +1746,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1760,7 +1760,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1774,7 +1774,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1788,7 +1788,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1802,7 +1802,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1816,7 +1816,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1830,7 +1830,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1858,7 +1858,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1872,7 +1872,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1900,7 +1900,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1911,10 +1911,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C109" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1925,10 +1925,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C110" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1942,7 +1942,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1956,7 +1956,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1967,10 +1967,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C113" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1981,10 +1981,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C114" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1998,7 +1998,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2012,7 +2012,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2026,12 +2026,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
       <x:c r="A118" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B118" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2040,7 +2040,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2054,7 +2054,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2068,7 +2068,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2082,7 +2082,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2096,7 +2096,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2107,10 +2107,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C123" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2121,10 +2121,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C124" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2138,7 +2138,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2152,7 +2152,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2166,7 +2166,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2180,7 +2180,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2194,7 +2194,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2208,7 +2208,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2222,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2236,7 +2236,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2250,7 +2250,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2261,10 +2261,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C134" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2275,10 +2275,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C135" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2292,7 +2292,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2306,7 +2306,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2320,7 +2320,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2334,7 +2334,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2348,7 +2348,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2359,10 +2359,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C141" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2373,10 +2373,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C142" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2390,7 +2390,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2404,7 +2404,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2418,7 +2418,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2432,7 +2432,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2443,10 +2443,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C147" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2457,10 +2457,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C148" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2474,7 +2474,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2488,7 +2488,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2502,7 +2502,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2516,7 +2516,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2530,7 +2530,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2544,7 +2544,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2558,7 +2558,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2572,12 +2572,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
       <x:c r="A157" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B157" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2586,7 +2586,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2597,10 +2597,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C158" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2611,10 +2611,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C159" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2625,10 +2625,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C160" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2639,10 +2639,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C161" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2653,10 +2653,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C162" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2684,7 +2684,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2695,10 +2695,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C165" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2709,10 +2709,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C166" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2723,10 +2723,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2737,10 +2737,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C168" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2751,10 +2751,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2762,13 +2762,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B170" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2776,13 +2776,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B171" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2796,7 +2796,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2807,10 +2807,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2824,7 +2824,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2835,10 +2835,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2849,10 +2849,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2863,10 +2863,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2877,10 +2877,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2891,10 +2891,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2905,10 +2905,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2922,7 +2922,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2933,10 +2933,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2950,7 +2950,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2964,7 +2964,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2975,10 +2975,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2989,24 +2989,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A187" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B187" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3014,27 +3014,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B188" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
       <x:c r="A189" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B189" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3045,10 +3045,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3062,7 +3062,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3076,7 +3076,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3087,10 +3087,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3104,7 +3104,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3118,7 +3118,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3132,7 +3132,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3143,10 +3143,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C197" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3157,10 +3157,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C198" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3171,10 +3171,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C199" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3188,7 +3188,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3202,7 +3202,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3216,7 +3216,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3230,7 +3230,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3241,10 +3241,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C204" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3258,7 +3258,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3272,7 +3272,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3283,10 +3283,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C207" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3300,7 +3300,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3311,10 +3311,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C209" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
+        <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3328,7 +3328,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
+        <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3339,23 +3339,37 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C211" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Fix Cloudflare package installation.</x:v>
+        <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B212" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C212" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D212" t="str">
+        <x:v>Fix Cloudflare package installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" t="n">
         <x:v>46226.5</x:v>
       </x:c>
-      <x:c r="B212" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C212" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D212" t="str">
+      <x:c r="B213" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C213" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D213" t="str">
         <x:v>Build RefHQ MVP.</x:v>
       </x:c>
     </x:row>
@@ -3371,7 +3385,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf36752d3433f4895"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba7ce2cd0dc64038"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Rbcc85f4898d34109"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R21fef28cdbbb4290"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D211" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D212" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.34.4 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.34.5 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -449,44 +449,44 @@
     </x:row>
     <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="23" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -494,13 +494,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -508,27 +508,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -536,13 +536,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -550,13 +550,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -564,13 +564,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -578,13 +578,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -592,13 +592,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -606,13 +606,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -620,13 +620,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -634,13 +634,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -648,13 +648,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -662,13 +662,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,27 +676,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,13 +704,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -718,13 +718,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,13 +732,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -746,13 +746,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,13 +760,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,13 +774,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -788,13 +788,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +802,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,13 +816,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -830,13 +830,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +844,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,13 +858,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,13 +872,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,27 +886,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A37" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -914,13 +914,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -928,13 +928,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -942,13 +942,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -956,13 +956,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,13 +970,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -984,13 +984,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,13 +998,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1012,13 +1012,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1026,13 +1026,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1068,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1082,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,13 +1096,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,13 +1110,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,27 +1124,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
       <x:c r="A54" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,13 +1152,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1166,13 +1166,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1180,13 +1180,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1194,13 +1194,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1208,27 +1208,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
       <x:c r="A60" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1236,13 +1236,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1250,13 +1250,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1264,13 +1264,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1278,13 +1278,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1292,13 +1292,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1306,13 +1306,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1320,27 +1320,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1348,13 +1348,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1362,13 +1362,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1376,13 +1376,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1390,27 +1390,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1418,41 +1418,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1460,13 +1460,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1474,27 +1474,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1502,13 +1502,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1516,13 +1516,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1530,27 +1530,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1558,13 +1558,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1572,13 +1572,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1586,13 +1586,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1600,27 +1600,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1628,13 +1628,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1642,27 +1642,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
       <x:c r="A91" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1670,13 +1670,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1684,13 +1684,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1698,27 +1698,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
       <x:c r="A95" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1729,10 +1729,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1746,7 +1746,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1760,7 +1760,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1774,7 +1774,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1788,7 +1788,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1802,7 +1802,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1816,7 +1816,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1830,7 +1830,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1858,7 +1858,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1872,7 +1872,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1900,7 +1900,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1914,7 +1914,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1925,10 +1925,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C110" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1939,10 +1939,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C111" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1956,7 +1956,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1970,7 +1970,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1981,10 +1981,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C114" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1995,10 +1995,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C115" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2012,7 +2012,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2026,7 +2026,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2040,12 +2040,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
       <x:c r="A119" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B119" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2054,7 +2054,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2068,7 +2068,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2082,7 +2082,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2096,7 +2096,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2110,7 +2110,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2121,10 +2121,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C124" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2135,10 +2135,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C125" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2152,7 +2152,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2166,7 +2166,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2180,7 +2180,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2194,7 +2194,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2208,7 +2208,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2222,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2236,7 +2236,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2250,7 +2250,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2264,7 +2264,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2275,10 +2275,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C135" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2289,10 +2289,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C136" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2306,7 +2306,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2320,7 +2320,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2334,7 +2334,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2348,7 +2348,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2362,7 +2362,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2373,10 +2373,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C142" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2387,10 +2387,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C143" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2404,7 +2404,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2418,7 +2418,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2432,7 +2432,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2446,7 +2446,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2457,10 +2457,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C148" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2471,10 +2471,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C149" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2488,7 +2488,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2502,7 +2502,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2516,7 +2516,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2530,7 +2530,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2544,7 +2544,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2558,7 +2558,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2572,7 +2572,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2586,12 +2586,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
       <x:c r="A158" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B158" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2600,7 +2600,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2611,10 +2611,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C159" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2625,10 +2625,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C160" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2639,10 +2639,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C161" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2653,10 +2653,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C162" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2667,10 +2667,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C163" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2698,7 +2698,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2709,10 +2709,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C166" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2723,10 +2723,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2737,10 +2737,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C168" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2751,10 +2751,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2765,10 +2765,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2776,13 +2776,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B171" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2790,13 +2790,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B172" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2810,7 +2810,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2821,10 +2821,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2838,7 +2838,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2849,10 +2849,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2863,10 +2863,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2877,10 +2877,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2891,10 +2891,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2905,10 +2905,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2919,10 +2919,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2936,7 +2936,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2947,10 +2947,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2964,7 +2964,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2978,7 +2978,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2989,10 +2989,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3003,24 +3003,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
       <x:c r="A188" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B188" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3028,27 +3028,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B189" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
       <x:c r="A190" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B190" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3059,10 +3059,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3076,7 +3076,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3090,7 +3090,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3101,10 +3101,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3118,7 +3118,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3132,7 +3132,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3146,7 +3146,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3157,10 +3157,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C198" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3171,10 +3171,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C199" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3185,10 +3185,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C200" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3202,7 +3202,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3216,7 +3216,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3230,7 +3230,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3244,7 +3244,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3255,10 +3255,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C205" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3272,7 +3272,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3286,7 +3286,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3297,10 +3297,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C208" s="28" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3314,7 +3314,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3325,10 +3325,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C210" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
+        <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3342,7 +3342,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
+        <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3353,23 +3353,37 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C212" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Fix Cloudflare package installation.</x:v>
+        <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B213" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C213" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D213" t="str">
+        <x:v>Fix Cloudflare package installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" t="n">
         <x:v>46226.5</x:v>
       </x:c>
-      <x:c r="B213" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C213" t="str">
+      <x:c r="B214" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C214" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D213" t="str">
+      <x:c r="D214" t="str">
         <x:v>Build RefHQ MVP.</x:v>
       </x:c>
     </x:row>
@@ -3385,7 +3399,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba7ce2cd0dc64038"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8eeaf82de5a4e48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R21fef28cdbbb4290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Rc67db85334bf41f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D212" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D213" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.34.5 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.35.0 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -449,58 +449,58 @@
     </x:row>
     <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="23" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -508,13 +508,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -522,27 +522,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -550,13 +550,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -564,13 +564,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -578,13 +578,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -592,13 +592,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -606,13 +606,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -620,13 +620,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -634,13 +634,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -648,13 +648,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -662,13 +662,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,13 +676,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,27 +690,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -718,13 +718,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,13 +732,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -746,13 +746,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,13 +760,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,13 +774,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -788,13 +788,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +802,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,13 +816,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -830,13 +830,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +844,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,13 +858,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,13 +872,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,13 +886,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -900,27 +900,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -928,13 +928,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -942,13 +942,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -956,13 +956,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,13 +970,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -984,13 +984,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,13 +998,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1012,13 +1012,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1026,13 +1026,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1068,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1082,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,13 +1096,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,13 +1110,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,13 +1124,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,27 +1138,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
       <x:c r="A55" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1166,13 +1166,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1180,13 +1180,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1194,13 +1194,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1208,13 +1208,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1222,27 +1222,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
       <x:c r="A61" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1250,13 +1250,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1264,13 +1264,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1278,13 +1278,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1292,13 +1292,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1306,13 +1306,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1320,13 +1320,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1334,27 +1334,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1362,13 +1362,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1376,13 +1376,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1390,13 +1390,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1404,27 +1404,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
       <x:c r="A74" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1432,41 +1432,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1474,13 +1474,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1488,27 +1488,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1516,13 +1516,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1530,13 +1530,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1544,27 +1544,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1572,13 +1572,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1586,13 +1586,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1600,13 +1600,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1614,27 +1614,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
       <x:c r="A89" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1642,13 +1642,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1656,27 +1656,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
       <x:c r="A92" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1684,13 +1684,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1698,13 +1698,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1712,27 +1712,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
       <x:c r="A96" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1743,10 +1743,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1760,7 +1760,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1774,7 +1774,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1788,7 +1788,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1802,7 +1802,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1816,7 +1816,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1830,7 +1830,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1858,7 +1858,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1872,7 +1872,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1900,7 +1900,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1914,7 +1914,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1928,7 +1928,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1939,10 +1939,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C111" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1953,10 +1953,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C112" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1970,7 +1970,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1984,7 +1984,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1995,10 +1995,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C115" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2009,10 +2009,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C116" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2026,7 +2026,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2040,7 +2040,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2054,12 +2054,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
       <x:c r="A120" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B120" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2068,7 +2068,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2082,7 +2082,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2096,7 +2096,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2110,7 +2110,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2124,7 +2124,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2135,10 +2135,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C125" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2149,10 +2149,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C126" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2166,7 +2166,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2180,7 +2180,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2194,7 +2194,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2208,7 +2208,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2222,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2236,7 +2236,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2250,7 +2250,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2264,7 +2264,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2278,7 +2278,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2289,10 +2289,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C136" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2303,10 +2303,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C137" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2320,7 +2320,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2334,7 +2334,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2348,7 +2348,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2362,7 +2362,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2376,7 +2376,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2387,10 +2387,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C143" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2401,10 +2401,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C144" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2418,7 +2418,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2432,7 +2432,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2446,7 +2446,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2471,10 +2471,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C149" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2485,10 +2485,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C150" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2502,7 +2502,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2516,7 +2516,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2530,7 +2530,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2544,7 +2544,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2558,7 +2558,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2572,7 +2572,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2586,7 +2586,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2600,12 +2600,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
       <x:c r="A159" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B159" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2614,7 +2614,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2625,10 +2625,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C160" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2639,10 +2639,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C161" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2653,10 +2653,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C162" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2667,10 +2667,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C163" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2681,10 +2681,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C164" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2712,7 +2712,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2723,10 +2723,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2737,10 +2737,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C168" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2751,10 +2751,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2765,10 +2765,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2779,10 +2779,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2790,13 +2790,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B172" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2804,13 +2804,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B173" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2824,7 +2824,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2835,10 +2835,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2852,7 +2852,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2863,10 +2863,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2877,10 +2877,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2891,10 +2891,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2905,10 +2905,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2919,10 +2919,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2933,10 +2933,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2950,7 +2950,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2961,10 +2961,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2978,7 +2978,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2992,7 +2992,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3003,10 +3003,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3017,24 +3017,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
       <x:c r="A189" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B189" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3042,27 +3042,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B190" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
       <x:c r="A191" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B191" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3073,10 +3073,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3090,7 +3090,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3104,7 +3104,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3115,10 +3115,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C195" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3132,7 +3132,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3146,7 +3146,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3160,7 +3160,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3171,10 +3171,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C199" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3185,10 +3185,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C200" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3199,10 +3199,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C201" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3216,7 +3216,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3230,7 +3230,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3244,7 +3244,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3258,7 +3258,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3269,10 +3269,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C206" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3286,7 +3286,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3300,7 +3300,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3311,10 +3311,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C209" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3328,7 +3328,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3339,10 +3339,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C211" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
+        <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3356,7 +3356,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
+        <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3367,23 +3367,37 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C213" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Fix Cloudflare package installation.</x:v>
+        <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B214" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C214" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D214" t="str">
+        <x:v>Fix Cloudflare package installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" t="n">
         <x:v>46226.5</x:v>
       </x:c>
-      <x:c r="B214" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C214" t="str">
+      <x:c r="B215" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C215" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D214" t="str">
+      <x:c r="D215" t="str">
         <x:v>Build RefHQ MVP.</x:v>
       </x:c>
     </x:row>
@@ -3399,7 +3413,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8eeaf82de5a4e48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf26ecfcf405042cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Rc67db85334bf41f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R127761f137324cd1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D213" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D214" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.35.0 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.35.1 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -449,72 +449,72 @@
     </x:row>
     <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="23" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -522,13 +522,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -536,27 +536,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -564,13 +564,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -578,13 +578,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -592,13 +592,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -606,13 +606,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -620,13 +620,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -634,13 +634,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -648,13 +648,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -662,13 +662,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,13 +676,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,13 +690,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,27 +704,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,13 +732,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -746,13 +746,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,13 +760,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,13 +774,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -788,13 +788,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +802,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,13 +816,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -830,13 +830,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +844,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,13 +858,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,13 +872,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,13 +886,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -900,13 +900,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -914,27 +914,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A39" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -942,13 +942,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -956,13 +956,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,13 +970,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -984,13 +984,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,13 +998,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1012,13 +1012,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1026,13 +1026,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1068,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1082,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,13 +1096,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,13 +1110,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,13 +1124,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,13 +1138,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,27 +1152,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
       <x:c r="A56" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1180,13 +1180,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1194,13 +1194,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1208,13 +1208,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1222,13 +1222,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1236,27 +1236,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
       <x:c r="A62" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1264,13 +1264,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1278,13 +1278,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1292,13 +1292,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1306,13 +1306,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1320,13 +1320,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1334,13 +1334,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1348,27 +1348,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
       <x:c r="A70" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1376,13 +1376,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1390,13 +1390,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1404,13 +1404,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1418,27 +1418,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1446,41 +1446,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
       <x:c r="A78" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1488,13 +1488,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1502,27 +1502,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1530,13 +1530,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1544,13 +1544,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1558,27 +1558,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1586,13 +1586,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1600,13 +1600,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1614,13 +1614,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1628,27 +1628,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
       <x:c r="A90" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1656,13 +1656,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1670,27 +1670,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
       <x:c r="A93" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1698,13 +1698,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1712,13 +1712,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1726,27 +1726,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1757,10 +1757,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1774,7 +1774,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1788,7 +1788,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1802,7 +1802,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1816,7 +1816,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1830,7 +1830,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1858,7 +1858,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1872,7 +1872,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1900,7 +1900,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1914,7 +1914,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1928,7 +1928,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1942,7 +1942,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1953,10 +1953,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C112" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1967,10 +1967,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C113" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1984,7 +1984,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1998,7 +1998,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2009,10 +2009,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C116" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2023,10 +2023,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C117" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2040,7 +2040,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2054,7 +2054,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2068,12 +2068,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
       <x:c r="A121" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B121" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2082,7 +2082,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2096,7 +2096,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2110,7 +2110,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2124,7 +2124,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2138,7 +2138,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2149,10 +2149,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C126" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2163,10 +2163,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C127" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2180,7 +2180,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2194,7 +2194,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2208,7 +2208,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2222,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2236,7 +2236,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2250,7 +2250,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2264,7 +2264,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2278,7 +2278,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2292,7 +2292,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2303,10 +2303,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C137" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2317,10 +2317,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C138" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2334,7 +2334,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2348,7 +2348,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2362,7 +2362,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2376,7 +2376,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2390,7 +2390,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2401,10 +2401,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C144" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2415,10 +2415,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C145" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2432,7 +2432,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2446,7 +2446,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2474,7 +2474,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2485,10 +2485,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C150" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2499,10 +2499,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C151" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2516,7 +2516,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2530,7 +2530,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2544,7 +2544,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2558,7 +2558,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2572,7 +2572,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2586,7 +2586,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2600,7 +2600,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2614,12 +2614,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
       <x:c r="A160" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B160" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2628,7 +2628,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2639,10 +2639,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C161" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2653,10 +2653,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C162" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2667,10 +2667,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C163" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2681,10 +2681,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C164" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2695,10 +2695,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C165" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2726,7 +2726,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2737,10 +2737,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C168" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2751,10 +2751,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2765,10 +2765,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2779,10 +2779,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2793,10 +2793,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2804,13 +2804,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B173" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2818,13 +2818,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B174" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2838,7 +2838,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2849,10 +2849,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2866,7 +2866,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2877,10 +2877,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2891,10 +2891,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2905,10 +2905,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2919,10 +2919,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2933,10 +2933,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2947,10 +2947,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2964,7 +2964,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2975,10 +2975,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2992,7 +2992,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3006,7 +3006,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3017,10 +3017,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3031,24 +3031,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
       <x:c r="A190" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B190" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3056,27 +3056,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B191" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
       <x:c r="A192" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B192" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3087,10 +3087,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3104,7 +3104,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3118,7 +3118,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3129,10 +3129,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C196" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3146,7 +3146,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3160,7 +3160,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3174,7 +3174,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3185,10 +3185,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C200" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3199,10 +3199,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C201" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3213,10 +3213,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C202" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3230,7 +3230,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3244,7 +3244,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3258,7 +3258,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3272,7 +3272,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3283,10 +3283,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C207" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3300,7 +3300,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3314,7 +3314,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3325,10 +3325,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C210" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3342,7 +3342,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3353,10 +3353,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C212" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
+        <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3370,7 +3370,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
+        <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3381,23 +3381,37 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C214" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Fix Cloudflare package installation.</x:v>
+        <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B215" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C215" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D215" t="str">
+        <x:v>Fix Cloudflare package installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" t="n">
         <x:v>46226.5</x:v>
       </x:c>
-      <x:c r="B215" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C215" t="str">
+      <x:c r="B216" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C216" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D215" t="str">
+      <x:c r="D216" t="str">
         <x:v>Build RefHQ MVP.</x:v>
       </x:c>
     </x:row>
@@ -3413,7 +3427,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf26ecfcf405042cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11b698f3230c4ffd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R127761f137324cd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R43cfca9ef4e64db8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D214" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D215" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.35.1 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.35.2 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -449,86 +449,86 @@
     </x:row>
     <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="23" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -536,13 +536,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -550,27 +550,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -578,13 +578,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -592,13 +592,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -606,13 +606,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -620,13 +620,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -634,13 +634,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -648,13 +648,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -662,13 +662,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,13 +676,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,13 +690,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,13 +704,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -718,27 +718,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A25" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -746,13 +746,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,13 +760,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,13 +774,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -788,13 +788,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +802,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,13 +816,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -830,13 +830,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +844,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,13 +858,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,13 +872,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,13 +886,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -900,13 +900,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -914,13 +914,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -928,27 +928,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -956,13 +956,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,13 +970,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -984,13 +984,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,13 +998,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1012,13 +1012,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1026,13 +1026,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1068,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1082,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,13 +1096,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,13 +1110,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,13 +1124,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,13 +1138,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,13 +1152,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1166,27 +1166,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A57" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1194,13 +1194,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1208,13 +1208,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1222,13 +1222,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1236,13 +1236,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1250,27 +1250,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
       <x:c r="A63" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1278,13 +1278,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1292,13 +1292,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1306,13 +1306,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1320,13 +1320,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1334,13 +1334,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1348,13 +1348,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1362,27 +1362,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1390,13 +1390,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1404,13 +1404,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1418,13 +1418,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1432,27 +1432,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1460,41 +1460,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
       <x:c r="A78" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1502,13 +1502,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1516,27 +1516,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1544,13 +1544,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1558,13 +1558,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1572,27 +1572,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1600,13 +1600,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1614,13 +1614,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1628,13 +1628,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1642,27 +1642,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
       <x:c r="A91" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1670,13 +1670,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1684,27 +1684,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
       <x:c r="A94" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1712,13 +1712,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1726,13 +1726,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1740,27 +1740,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
       <x:c r="A98" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B98" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1771,10 +1771,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1788,7 +1788,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1802,7 +1802,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1816,7 +1816,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1830,7 +1830,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1858,7 +1858,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1872,7 +1872,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1900,7 +1900,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1914,7 +1914,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1928,7 +1928,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1942,7 +1942,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1956,7 +1956,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1967,10 +1967,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C113" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1981,10 +1981,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C114" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1998,7 +1998,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2012,7 +2012,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2023,10 +2023,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C117" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2037,10 +2037,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C118" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2054,7 +2054,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2068,7 +2068,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2082,12 +2082,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
       <x:c r="A122" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B122" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2096,7 +2096,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2110,7 +2110,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2124,7 +2124,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2138,7 +2138,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2152,7 +2152,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2163,10 +2163,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C127" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2177,10 +2177,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C128" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2194,7 +2194,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2208,7 +2208,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2222,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2236,7 +2236,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2250,7 +2250,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2264,7 +2264,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2278,7 +2278,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2292,7 +2292,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2306,7 +2306,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2317,10 +2317,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C138" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2331,10 +2331,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C139" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2348,7 +2348,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2362,7 +2362,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2376,7 +2376,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2390,7 +2390,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2404,7 +2404,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2415,10 +2415,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C145" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2429,10 +2429,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C146" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2446,7 +2446,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2474,7 +2474,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2488,7 +2488,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2499,10 +2499,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C151" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2513,10 +2513,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C152" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2530,7 +2530,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2544,7 +2544,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2558,7 +2558,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2572,7 +2572,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2586,7 +2586,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2600,7 +2600,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2614,7 +2614,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2628,12 +2628,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
       <x:c r="A161" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B161" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2642,7 +2642,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2653,10 +2653,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C162" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2667,10 +2667,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C163" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2681,10 +2681,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C164" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2695,10 +2695,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C165" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2709,10 +2709,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C166" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2740,7 +2740,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2751,10 +2751,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2765,10 +2765,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2779,10 +2779,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2793,10 +2793,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2807,10 +2807,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2818,13 +2818,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B174" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2832,13 +2832,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B175" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2852,7 +2852,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2863,10 +2863,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2880,7 +2880,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2891,10 +2891,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2905,10 +2905,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2919,10 +2919,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2933,10 +2933,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2947,10 +2947,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2961,10 +2961,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2978,7 +2978,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2989,10 +2989,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3006,7 +3006,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3020,7 +3020,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3031,10 +3031,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3045,24 +3045,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
       <x:c r="A191" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B191" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3070,27 +3070,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B192" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
       <x:c r="A193" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B193" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3101,10 +3101,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3118,7 +3118,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3132,7 +3132,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3143,10 +3143,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C197" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3160,7 +3160,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3174,7 +3174,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3188,7 +3188,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3199,10 +3199,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C201" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3213,10 +3213,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C202" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3227,10 +3227,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C203" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3244,7 +3244,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3258,7 +3258,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3272,7 +3272,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3286,7 +3286,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3297,10 +3297,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C208" s="28" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3314,7 +3314,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3328,7 +3328,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3339,10 +3339,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C211" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3356,7 +3356,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3367,10 +3367,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C213" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
+        <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3384,7 +3384,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
+        <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -3395,23 +3395,37 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C215" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D215" t="str">
-        <x:v>Fix Cloudflare package installation.</x:v>
+        <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B216" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C216" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D216" t="str">
+        <x:v>Fix Cloudflare package installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" t="n">
         <x:v>46226.5</x:v>
       </x:c>
-      <x:c r="B216" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C216" t="str">
+      <x:c r="B217" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C217" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D216" t="str">
+      <x:c r="D217" t="str">
         <x:v>Build RefHQ MVP.</x:v>
       </x:c>
     </x:row>
@@ -3427,7 +3441,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11b698f3230c4ffd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R251725c6df734eaf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R43cfca9ef4e64db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Re2c3334737cd4fb0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D215" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D216" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.35.2 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.35.3 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -449,100 +449,100 @@
     </x:row>
     <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="23" t="n">
-        <x:v>46256.583333333336</x:v>
+        <x:v>46256.604166666664</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.35.2</x:v>
+        <x:v>v0.35.3</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
+        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -550,13 +550,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -564,27 +564,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -592,13 +592,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -606,13 +606,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -620,13 +620,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -634,13 +634,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -648,13 +648,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -662,13 +662,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,13 +676,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,13 +690,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,13 +704,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -718,13 +718,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,27 +732,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A26" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,13 +760,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,13 +774,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -788,13 +788,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +802,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,13 +816,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -830,13 +830,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +844,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,13 +858,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,13 +872,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,13 +886,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -900,13 +900,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -914,13 +914,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -928,13 +928,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -942,27 +942,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A41" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,13 +970,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -984,13 +984,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,13 +998,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1012,13 +1012,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1026,13 +1026,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1068,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1082,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,13 +1096,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,13 +1110,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,13 +1124,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,13 +1138,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,13 +1152,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1166,13 +1166,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1180,27 +1180,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
       <x:c r="A58" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1208,13 +1208,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1222,13 +1222,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1236,13 +1236,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1250,13 +1250,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1264,27 +1264,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
       <x:c r="A64" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1292,13 +1292,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1306,13 +1306,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1320,13 +1320,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1334,13 +1334,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1348,13 +1348,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1362,13 +1362,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1376,27 +1376,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1404,13 +1404,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1418,13 +1418,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1432,13 +1432,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1446,27 +1446,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1474,41 +1474,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1516,13 +1516,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1530,27 +1530,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1558,13 +1558,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1572,13 +1572,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1586,27 +1586,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1614,13 +1614,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1628,13 +1628,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1642,13 +1642,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1656,27 +1656,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
       <x:c r="A92" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1684,13 +1684,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1698,27 +1698,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
       <x:c r="A95" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1726,13 +1726,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1740,13 +1740,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1754,27 +1754,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B98" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
       <x:c r="A99" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B99" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1785,10 +1785,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C100" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1802,7 +1802,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1816,7 +1816,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1830,7 +1830,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1858,7 +1858,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1872,7 +1872,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1900,7 +1900,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1914,7 +1914,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1928,7 +1928,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1942,7 +1942,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1956,7 +1956,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1970,7 +1970,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1981,10 +1981,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C114" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1995,10 +1995,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C115" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2012,7 +2012,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2026,7 +2026,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2037,10 +2037,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C118" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2051,10 +2051,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C119" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2068,7 +2068,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2082,7 +2082,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2096,12 +2096,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
       <x:c r="A123" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B123" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2110,7 +2110,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2124,7 +2124,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2138,7 +2138,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2152,7 +2152,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2166,7 +2166,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2177,10 +2177,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C128" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2191,10 +2191,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C129" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2208,7 +2208,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2222,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2236,7 +2236,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2250,7 +2250,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2264,7 +2264,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2278,7 +2278,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2292,7 +2292,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2306,7 +2306,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2320,7 +2320,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2331,10 +2331,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C139" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2345,10 +2345,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C140" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2362,7 +2362,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2376,7 +2376,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2390,7 +2390,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2404,7 +2404,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2418,7 +2418,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2429,10 +2429,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C146" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2443,10 +2443,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C147" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2474,7 +2474,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2488,7 +2488,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2502,7 +2502,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2513,10 +2513,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C152" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2527,10 +2527,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C153" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2544,7 +2544,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2558,7 +2558,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2572,7 +2572,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2586,7 +2586,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2600,7 +2600,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2614,7 +2614,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2628,7 +2628,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2642,12 +2642,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
       <x:c r="A162" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B162" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2656,7 +2656,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2667,10 +2667,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C163" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2681,10 +2681,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C164" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2695,10 +2695,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C165" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2709,10 +2709,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C166" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2723,10 +2723,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2754,7 +2754,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2765,10 +2765,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2779,10 +2779,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2793,10 +2793,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2807,10 +2807,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2821,10 +2821,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2832,13 +2832,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B175" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2846,13 +2846,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B176" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2866,7 +2866,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2877,10 +2877,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2894,7 +2894,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2905,10 +2905,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2919,10 +2919,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2933,10 +2933,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2947,10 +2947,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2961,10 +2961,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2975,10 +2975,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2992,7 +2992,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3003,10 +3003,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3020,7 +3020,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3034,7 +3034,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3045,10 +3045,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3059,24 +3059,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
       <x:c r="A192" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B192" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3084,27 +3084,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B193" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
       <x:c r="A194" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B194" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3115,10 +3115,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C195" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3132,7 +3132,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3146,7 +3146,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3157,10 +3157,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C198" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3174,7 +3174,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3188,7 +3188,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3202,7 +3202,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3213,10 +3213,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C202" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3227,10 +3227,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C203" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3241,10 +3241,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C204" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3258,7 +3258,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3272,7 +3272,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3286,7 +3286,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3300,7 +3300,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3311,10 +3311,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C209" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3328,7 +3328,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3342,7 +3342,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3353,10 +3353,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C212" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3370,7 +3370,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3381,10 +3381,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C214" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
+        <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -3398,7 +3398,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D215" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
+        <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -3409,23 +3409,37 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C216" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D216" t="str">
-        <x:v>Fix Cloudflare package installation.</x:v>
+        <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B217" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C217" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D217" t="str">
+        <x:v>Fix Cloudflare package installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" t="n">
         <x:v>46226.5</x:v>
       </x:c>
-      <x:c r="B217" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C217" t="str">
+      <x:c r="B218" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C218" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D217" t="str">
+      <x:c r="D218" t="str">
         <x:v>Build RefHQ MVP.</x:v>
       </x:c>
     </x:row>
@@ -3441,7 +3455,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R251725c6df734eaf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R934f4de280344bd9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Re2c3334737cd4fb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R2c0603daa30d41c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D216" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D217" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.35.3 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.35.4 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -449,114 +449,114 @@
     </x:row>
     <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="23" t="n">
-        <x:v>46256.604166666664</x:v>
+        <x:v>46256.625</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.35.3</x:v>
+        <x:v>v0.35.4</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
+        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
-        <x:v>46256.583333333336</x:v>
+        <x:v>46256.604166666664</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.35.2</x:v>
+        <x:v>v0.35.3</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
+        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -564,13 +564,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -578,27 +578,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A15" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -606,13 +606,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -620,13 +620,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -634,13 +634,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -648,13 +648,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -662,13 +662,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,13 +676,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,13 +690,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,13 +704,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -718,13 +718,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,13 +732,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -746,27 +746,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,13 +774,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -788,13 +788,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +802,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,13 +816,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -830,13 +830,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +844,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,13 +858,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,13 +872,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,13 +886,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -900,13 +900,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -914,13 +914,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -928,13 +928,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -942,13 +942,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -956,27 +956,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
       <x:c r="A42" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -984,13 +984,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,13 +998,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1012,13 +1012,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1026,13 +1026,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1068,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1082,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,13 +1096,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,13 +1110,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,13 +1124,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,13 +1138,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,13 +1152,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1166,13 +1166,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1180,13 +1180,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1194,27 +1194,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
       <x:c r="A59" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1222,13 +1222,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1236,13 +1236,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1250,13 +1250,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1264,13 +1264,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1278,27 +1278,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1306,13 +1306,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1320,13 +1320,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1334,13 +1334,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1348,13 +1348,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1362,13 +1362,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1376,13 +1376,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1390,27 +1390,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1418,13 +1418,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1432,13 +1432,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1446,13 +1446,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1460,27 +1460,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
       <x:c r="A78" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1488,41 +1488,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1530,13 +1530,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1544,27 +1544,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1572,13 +1572,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1586,13 +1586,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1600,27 +1600,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1628,13 +1628,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1642,13 +1642,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1656,13 +1656,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1670,27 +1670,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
       <x:c r="A93" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1698,13 +1698,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1712,27 +1712,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
       <x:c r="A96" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1740,13 +1740,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1754,13 +1754,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B98" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1768,27 +1768,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B99" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
       <x:c r="A100" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B100" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C100" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1799,10 +1799,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C101" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1816,7 +1816,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1830,7 +1830,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1858,7 +1858,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1872,7 +1872,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1900,7 +1900,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1914,7 +1914,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1928,7 +1928,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1942,7 +1942,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1956,7 +1956,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1970,7 +1970,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1984,7 +1984,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1995,10 +1995,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C115" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2009,10 +2009,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C116" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2026,7 +2026,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2040,7 +2040,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2051,10 +2051,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C119" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2065,10 +2065,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C120" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2082,7 +2082,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2096,7 +2096,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2110,12 +2110,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
       <x:c r="A124" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B124" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2124,7 +2124,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2138,7 +2138,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2152,7 +2152,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2166,7 +2166,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2180,7 +2180,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2191,10 +2191,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C129" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2205,10 +2205,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C130" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2222,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2236,7 +2236,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2250,7 +2250,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2264,7 +2264,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2278,7 +2278,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2292,7 +2292,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2306,7 +2306,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2320,7 +2320,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2334,7 +2334,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2345,10 +2345,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C140" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2359,10 +2359,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C141" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2376,7 +2376,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2390,7 +2390,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2404,7 +2404,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2418,7 +2418,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2432,7 +2432,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2443,10 +2443,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C147" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2457,10 +2457,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C148" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2474,7 +2474,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2488,7 +2488,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2502,7 +2502,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2516,7 +2516,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2527,10 +2527,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C153" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2541,10 +2541,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C154" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2558,7 +2558,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2572,7 +2572,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2586,7 +2586,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2600,7 +2600,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2614,7 +2614,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2628,7 +2628,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2642,7 +2642,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2656,12 +2656,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
       <x:c r="A163" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B163" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2670,7 +2670,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2681,10 +2681,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C164" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2695,10 +2695,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C165" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2709,10 +2709,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C166" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2723,10 +2723,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2737,10 +2737,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C168" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2768,7 +2768,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2779,10 +2779,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2793,10 +2793,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2807,10 +2807,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2821,10 +2821,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2835,10 +2835,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2846,13 +2846,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B176" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2860,13 +2860,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B177" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2880,7 +2880,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2891,10 +2891,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2908,7 +2908,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2919,10 +2919,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2933,10 +2933,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2947,10 +2947,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2961,10 +2961,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2975,10 +2975,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2989,10 +2989,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3006,7 +3006,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3017,10 +3017,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3034,7 +3034,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3048,7 +3048,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3059,10 +3059,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3073,24 +3073,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
       <x:c r="A193" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B193" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3098,27 +3098,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B194" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
       <x:c r="A195" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B195" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C195" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3129,10 +3129,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C196" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3146,7 +3146,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3160,7 +3160,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3171,10 +3171,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C199" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3188,7 +3188,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3202,7 +3202,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3216,7 +3216,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3227,10 +3227,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C203" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3241,10 +3241,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C204" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3255,10 +3255,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C205" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3272,7 +3272,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3286,7 +3286,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3300,7 +3300,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3314,7 +3314,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3325,10 +3325,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C210" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3342,7 +3342,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3356,7 +3356,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3367,10 +3367,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C213" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3384,7 +3384,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -3395,10 +3395,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C215" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D215" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
+        <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -3412,7 +3412,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D216" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
+        <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -3423,23 +3423,37 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C217" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D217" t="str">
-        <x:v>Fix Cloudflare package installation.</x:v>
+        <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B218" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C218" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="D218" t="str">
+        <x:v>Fix Cloudflare package installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" t="n">
         <x:v>46226.5</x:v>
       </x:c>
-      <x:c r="B218" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C218" t="str">
+      <x:c r="B219" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C219" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D218" t="str">
+      <x:c r="D219" t="str">
         <x:v>Build RefHQ MVP.</x:v>
       </x:c>
     </x:row>
@@ -3455,7 +3469,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R934f4de280344bd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8be4f95194464615"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R2c0603daa30d41c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Ra08fc645eea849fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D217" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D218" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.35.4 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.35.5 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -449,128 +449,128 @@
     </x:row>
     <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="23" t="n">
-        <x:v>46256.625</x:v>
+        <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.35.4</x:v>
+        <x:v>v0.35.5</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
+        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
-        <x:v>46256.604166666664</x:v>
+        <x:v>46256.625</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.35.3</x:v>
+        <x:v>v0.35.4</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
+        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
-        <x:v>46256.583333333336</x:v>
+        <x:v>46256.604166666664</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.35.2</x:v>
+        <x:v>v0.35.3</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
+        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -578,13 +578,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -592,27 +592,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -620,13 +620,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -634,13 +634,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -648,13 +648,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -662,13 +662,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,13 +676,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,13 +690,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,13 +704,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -718,13 +718,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,13 +732,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -746,13 +746,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,27 +760,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -788,13 +788,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +802,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,13 +816,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -830,13 +830,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +844,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,13 +858,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,13 +872,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,13 +886,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -900,13 +900,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -914,13 +914,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -928,13 +928,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -942,13 +942,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -956,13 +956,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,27 +970,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A43" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,13 +998,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1012,13 +1012,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1026,13 +1026,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1068,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1082,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,13 +1096,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,13 +1110,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,13 +1124,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,13 +1138,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,13 +1152,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1166,13 +1166,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1180,13 +1180,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1194,13 +1194,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1208,27 +1208,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
       <x:c r="A60" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1236,13 +1236,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1250,13 +1250,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1264,13 +1264,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1278,13 +1278,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1292,27 +1292,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1320,13 +1320,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1334,13 +1334,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1348,13 +1348,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1362,13 +1362,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1376,13 +1376,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1390,13 +1390,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1404,27 +1404,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
       <x:c r="A74" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1432,13 +1432,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1446,13 +1446,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1460,13 +1460,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1474,27 +1474,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1502,41 +1502,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1544,13 +1544,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1558,27 +1558,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1586,13 +1586,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1600,13 +1600,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1614,27 +1614,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
       <x:c r="A89" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1642,13 +1642,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1656,13 +1656,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1670,13 +1670,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1684,27 +1684,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
       <x:c r="A94" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1712,13 +1712,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1726,27 +1726,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1754,13 +1754,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B98" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1768,13 +1768,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B99" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1782,27 +1782,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B100" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C100" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
       <x:c r="A101" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B101" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C101" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1813,10 +1813,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C102" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1830,7 +1830,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1858,7 +1858,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1872,7 +1872,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1900,7 +1900,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1914,7 +1914,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1928,7 +1928,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1942,7 +1942,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1956,7 +1956,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1970,7 +1970,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1984,7 +1984,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1998,7 +1998,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2009,10 +2009,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C116" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2023,10 +2023,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C117" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2040,7 +2040,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2054,7 +2054,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2065,10 +2065,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C120" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2079,10 +2079,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C121" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2096,7 +2096,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2110,7 +2110,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2124,12 +2124,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
       <x:c r="A125" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B125" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2138,7 +2138,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2152,7 +2152,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2166,7 +2166,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2180,7 +2180,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2194,7 +2194,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2205,10 +2205,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C130" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2219,10 +2219,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C131" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2236,7 +2236,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2250,7 +2250,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2264,7 +2264,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2278,7 +2278,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2292,7 +2292,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2306,7 +2306,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2320,7 +2320,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2334,7 +2334,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2348,7 +2348,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2359,10 +2359,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C141" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2373,10 +2373,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C142" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2390,7 +2390,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2404,7 +2404,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2418,7 +2418,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2432,7 +2432,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2446,7 +2446,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2457,10 +2457,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C148" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2471,10 +2471,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C149" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2488,7 +2488,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2502,7 +2502,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2516,7 +2516,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2530,7 +2530,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2541,10 +2541,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C154" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2555,10 +2555,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C155" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2572,7 +2572,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2586,7 +2586,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2600,7 +2600,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2614,7 +2614,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2628,7 +2628,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2642,7 +2642,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2656,7 +2656,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2670,12 +2670,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
       <x:c r="A164" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B164" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2684,7 +2684,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2695,10 +2695,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C165" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2709,10 +2709,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C166" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2723,10 +2723,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2737,10 +2737,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C168" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2751,10 +2751,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2782,7 +2782,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2793,10 +2793,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2807,10 +2807,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2821,10 +2821,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2835,10 +2835,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2849,10 +2849,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2860,13 +2860,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B177" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2874,13 +2874,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B178" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2894,7 +2894,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2905,10 +2905,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2922,7 +2922,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2933,10 +2933,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2947,10 +2947,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2961,10 +2961,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2975,10 +2975,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2989,10 +2989,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3003,10 +3003,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3020,7 +3020,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3031,10 +3031,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3048,7 +3048,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3062,7 +3062,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3073,10 +3073,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3087,24 +3087,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
       <x:c r="A194" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B194" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3112,27 +3112,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B195" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C195" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
       <x:c r="A196" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B196" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C196" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3143,10 +3143,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C197" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3160,7 +3160,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3174,7 +3174,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3185,10 +3185,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C200" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3202,7 +3202,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3216,7 +3216,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3230,7 +3230,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3241,10 +3241,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C204" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3255,10 +3255,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C205" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3269,10 +3269,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C206" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3286,7 +3286,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3300,7 +3300,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3314,7 +3314,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3328,7 +3328,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3339,10 +3339,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C211" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3356,7 +3356,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3370,7 +3370,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3381,10 +3381,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C214" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -3398,7 +3398,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D215" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -3409,10 +3409,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C216" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D216" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
+        <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -3426,7 +3426,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D217" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
+        <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -3437,10 +3437,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C218" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D218" t="str">
-        <x:v>Fix Cloudflare package installation.</x:v>
+        <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -3469,7 +3469,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8be4f95194464615"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R002191e58d794899"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Ra08fc645eea849fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Rf23ed94dd10042e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D218" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D219" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.35.5 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.36.0 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -452,139 +452,139 @@
         <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.35.5</x:v>
+        <x:v>v0.36.0</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
+        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
-        <x:v>46256.625</x:v>
+        <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.35.4</x:v>
+        <x:v>v0.35.5</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
+        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
-        <x:v>46256.604166666664</x:v>
+        <x:v>46256.625</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.35.3</x:v>
+        <x:v>v0.35.4</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
+        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
-        <x:v>46256.583333333336</x:v>
+        <x:v>46256.604166666664</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.35.2</x:v>
+        <x:v>v0.35.3</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
+        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -592,13 +592,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -606,27 +606,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -634,13 +634,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -648,13 +648,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -662,13 +662,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,13 +676,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,13 +690,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,13 +704,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -718,13 +718,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,13 +732,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -746,13 +746,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,13 +760,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,27 +774,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A29" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +802,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,13 +816,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -830,13 +830,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +844,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,13 +858,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,13 +872,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,13 +886,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -900,13 +900,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -914,13 +914,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -928,13 +928,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -942,13 +942,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -956,13 +956,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,13 +970,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -984,27 +984,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
       <x:c r="A44" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1012,13 +1012,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1026,13 +1026,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1068,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1082,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,13 +1096,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,13 +1110,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,13 +1124,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,13 +1138,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,13 +1152,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1166,13 +1166,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1180,13 +1180,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1194,13 +1194,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1208,13 +1208,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1222,27 +1222,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
       <x:c r="A61" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1250,13 +1250,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1264,13 +1264,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1278,13 +1278,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1292,13 +1292,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1306,27 +1306,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1334,13 +1334,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1348,13 +1348,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1362,13 +1362,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1376,13 +1376,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1390,13 +1390,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1404,13 +1404,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1418,27 +1418,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1446,13 +1446,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1460,13 +1460,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1474,13 +1474,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1488,27 +1488,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1516,41 +1516,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1558,13 +1558,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1572,27 +1572,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1600,13 +1600,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1614,13 +1614,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1628,27 +1628,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
       <x:c r="A90" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1656,13 +1656,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1670,13 +1670,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1684,13 +1684,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1698,27 +1698,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
       <x:c r="A95" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1726,13 +1726,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1740,27 +1740,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
       <x:c r="A98" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B98" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1768,13 +1768,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B99" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1782,13 +1782,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B100" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C100" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1796,27 +1796,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B101" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C101" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
       <x:c r="A102" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B102" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C102" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1827,10 +1827,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C103" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1858,7 +1858,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1872,7 +1872,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1900,7 +1900,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1914,7 +1914,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1928,7 +1928,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1942,7 +1942,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1956,7 +1956,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1970,7 +1970,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1984,7 +1984,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1998,7 +1998,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2012,7 +2012,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2023,10 +2023,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C117" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2037,10 +2037,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C118" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2054,7 +2054,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2068,7 +2068,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2079,10 +2079,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C121" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2093,10 +2093,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C122" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2110,7 +2110,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2124,7 +2124,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2138,12 +2138,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
       <x:c r="A126" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B126" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2152,7 +2152,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2166,7 +2166,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2180,7 +2180,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2194,7 +2194,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2208,7 +2208,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2219,10 +2219,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C131" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2233,10 +2233,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C132" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2250,7 +2250,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2264,7 +2264,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2278,7 +2278,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2292,7 +2292,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2306,7 +2306,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2320,7 +2320,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2334,7 +2334,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2348,7 +2348,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2362,7 +2362,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2373,10 +2373,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C142" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2387,10 +2387,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C143" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2404,7 +2404,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2418,7 +2418,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2432,7 +2432,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2446,7 +2446,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2471,10 +2471,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C149" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2485,10 +2485,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C150" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2502,7 +2502,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2516,7 +2516,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2530,7 +2530,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2544,7 +2544,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2555,10 +2555,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C155" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2569,10 +2569,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C156" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2586,7 +2586,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2600,7 +2600,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2614,7 +2614,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2628,7 +2628,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2642,7 +2642,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2656,7 +2656,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2670,7 +2670,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2684,12 +2684,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
       <x:c r="A165" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B165" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2698,7 +2698,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2709,10 +2709,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C166" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2723,10 +2723,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2737,10 +2737,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C168" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2751,10 +2751,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2765,10 +2765,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2796,7 +2796,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2807,10 +2807,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2821,10 +2821,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2835,10 +2835,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2849,10 +2849,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2863,10 +2863,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2874,13 +2874,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B178" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2888,13 +2888,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B179" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2908,7 +2908,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2919,10 +2919,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2936,7 +2936,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2947,10 +2947,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2961,10 +2961,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2975,10 +2975,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2989,10 +2989,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3003,10 +3003,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3017,10 +3017,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3034,7 +3034,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3045,10 +3045,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3062,7 +3062,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3076,7 +3076,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3087,10 +3087,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3101,24 +3101,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
       <x:c r="A195" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B195" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C195" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3126,27 +3126,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B196" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C196" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
       <x:c r="A197" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B197" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C197" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3157,10 +3157,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C198" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3174,7 +3174,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3188,7 +3188,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3199,10 +3199,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C201" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3216,7 +3216,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3230,7 +3230,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3244,7 +3244,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3255,10 +3255,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C205" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3269,10 +3269,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C206" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3283,10 +3283,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C207" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3300,7 +3300,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3314,7 +3314,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3328,7 +3328,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3342,7 +3342,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3353,10 +3353,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C212" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3370,7 +3370,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3384,7 +3384,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -3395,10 +3395,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C215" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D215" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -3412,7 +3412,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D216" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -3423,10 +3423,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C217" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D217" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
+        <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -3440,12 +3440,12 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D218" t="str">
-        <x:v>Add Supabase authentication client.</x:v>
+        <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" t="n">
-        <x:v>46226.5</x:v>
+        <x:v>46227.5</x:v>
       </x:c>
       <x:c r="B219" t="str">
         <x:v>Early build</x:v>
@@ -3454,7 +3454,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D219" t="str">
-        <x:v>Build RefHQ MVP.</x:v>
+        <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3469,7 +3469,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R002191e58d794899"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7f9402b8d334569"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Rf23ed94dd10042e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Ra3429555ef0245a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -421,7 +421,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.36.0 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.37.1 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -449,170 +449,170 @@
     </x:row>
     <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="23" t="n">
-        <x:v>46256.833333333336</x:v>
+        <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.36.0</x:v>
+        <x:v>v0.37.1</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
+        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="n">
-        <x:v>46256.833333333336</x:v>
+        <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.35.5</x:v>
+        <x:v>v0.37.0</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
+        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
-        <x:v>46256.625</x:v>
+        <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.35.4</x:v>
+        <x:v>v0.36.0</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
+        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
-        <x:v>46256.604166666664</x:v>
+        <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.35.3</x:v>
+        <x:v>v0.35.5</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
+        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
-        <x:v>46256.583333333336</x:v>
+        <x:v>46256.625</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.35.2</x:v>
+        <x:v>v0.35.4</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
+        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.604166666664</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.3</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A15" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -620,41 +620,41 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A18" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -662,13 +662,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,13 +676,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,13 +690,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,13 +704,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -718,13 +718,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,13 +732,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -746,13 +746,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,13 +760,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,13 +774,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -788,41 +788,41 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -830,13 +830,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +844,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,13 +858,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,13 +872,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,13 +886,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -900,13 +900,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -914,13 +914,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -928,13 +928,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -942,13 +942,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -956,13 +956,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,13 +970,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -984,13 +984,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,41 +998,41 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
       <x:c r="A45" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A46" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1040,13 +1040,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1054,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1068,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1082,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,13 +1096,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,13 +1110,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,13 +1124,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,13 +1138,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,13 +1152,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1166,13 +1166,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1180,13 +1180,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1194,13 +1194,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1208,13 +1208,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1222,13 +1222,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1236,41 +1236,41 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
       <x:c r="A62" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
       <x:c r="A63" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1278,13 +1278,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1292,13 +1292,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1306,13 +1306,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1320,41 +1320,41 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1362,13 +1362,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1376,13 +1376,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1390,13 +1390,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1404,13 +1404,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1418,13 +1418,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1432,41 +1432,41 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1474,13 +1474,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1488,13 +1488,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1502,83 +1502,83 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1586,41 +1586,41 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1628,13 +1628,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1642,41 +1642,41 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
       <x:c r="A91" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
       <x:c r="A92" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1684,13 +1684,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1698,13 +1698,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1712,41 +1712,41 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
       <x:c r="A96" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1754,41 +1754,41 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B98" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
       <x:c r="A99" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B99" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
       <x:c r="A100" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B100" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C100" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1796,13 +1796,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B101" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C101" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1810,32 +1810,32 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B102" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C102" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
       <x:c r="A103" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B103" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C103" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
       <x:c r="A104" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B104" s="26" t="str">
         <x:v>Early build</x:v>
@@ -1844,7 +1844,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1855,10 +1855,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C105" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1872,7 +1872,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1886,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1900,7 +1900,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1914,7 +1914,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1928,7 +1928,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1942,7 +1942,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1956,7 +1956,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1970,7 +1970,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1984,7 +1984,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1998,7 +1998,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2012,7 +2012,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2026,7 +2026,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2037,10 +2037,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C118" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2054,7 +2054,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2065,10 +2065,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C120" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2082,7 +2082,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2093,10 +2093,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C122" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2110,7 +2110,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2121,10 +2121,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C124" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2138,7 +2138,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2152,12 +2152,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
       <x:c r="A127" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B127" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2166,12 +2166,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
       <x:c r="A128" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B128" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2180,7 +2180,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2194,7 +2194,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2208,7 +2208,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2222,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2233,10 +2233,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C132" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2250,7 +2250,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2261,10 +2261,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C134" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2278,7 +2278,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2292,7 +2292,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2306,7 +2306,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2320,7 +2320,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2334,7 +2334,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2348,7 +2348,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2362,7 +2362,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2376,7 +2376,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2387,10 +2387,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C143" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2404,7 +2404,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2415,10 +2415,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C145" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2432,7 +2432,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2446,7 +2446,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2460,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2474,7 +2474,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2485,10 +2485,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C150" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2502,7 +2502,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2513,10 +2513,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C152" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2530,7 +2530,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2544,7 +2544,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2558,7 +2558,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2569,10 +2569,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C156" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2586,7 +2586,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2597,10 +2597,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C158" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2614,7 +2614,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2628,7 +2628,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2642,7 +2642,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2656,7 +2656,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2670,7 +2670,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2684,7 +2684,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2698,12 +2698,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
       <x:c r="A166" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B166" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2712,21 +2712,21 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
       <x:c r="A167" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B167" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C167" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2740,7 +2740,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2751,10 +2751,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2765,10 +2765,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2779,10 +2779,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2793,10 +2793,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2810,7 +2810,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2821,10 +2821,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2838,7 +2838,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2849,10 +2849,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2863,10 +2863,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2877,10 +2877,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2888,13 +2888,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B179" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2908,7 +2908,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2916,13 +2916,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B181" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2933,10 +2933,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2947,10 +2947,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2961,10 +2961,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2975,10 +2975,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2989,10 +2989,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3003,10 +3003,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3017,10 +3017,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3034,7 +3034,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3045,10 +3045,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3059,10 +3059,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3073,10 +3073,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3090,7 +3090,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3101,10 +3101,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3118,63 +3118,63 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
       <x:c r="A196" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B196" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C196" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
       <x:c r="A197" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B197" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C197" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
       <x:c r="A198" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B198" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C198" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
       <x:c r="A199" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B199" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C199" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3185,10 +3185,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C200" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3202,7 +3202,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3213,10 +3213,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C202" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3227,10 +3227,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C203" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3244,7 +3244,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3258,7 +3258,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3269,10 +3269,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C206" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3283,10 +3283,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C207" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3297,98 +3297,98 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C208" s="28" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
+        <x:v>Add Law18Referee Management brand assets.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="15" hidden="0" customHeight="1">
+      <x:c r="A209" s="10" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B209" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C209" t="str">
+        <x:v>Changed</x:v>
+      </x:c>
+      <x:c r="D209" t="str">
+        <x:v>Rename platform to Law18Referee Management.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="15" hidden="0" customHeight="1">
+      <x:c r="A210" s="10" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B210" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C210" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D210" t="str">
         <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
-    <x:row r="209" ht="15" hidden="0" customHeight="1">
-      <x:c r="A209" t="n">
+    <x:row r="211">
+      <x:c r="A211" s="10" t="n">
         <x:v>46227.5</x:v>
       </x:c>
-      <x:c r="B209" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C209" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D209" t="str">
+      <x:c r="B211" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C211" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D211" t="str">
         <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
-    <x:row r="210" ht="15" hidden="0" customHeight="1">
-      <x:c r="A210" t="n">
+    <x:row r="212">
+      <x:c r="A212" s="10" t="n">
         <x:v>46227.5</x:v>
       </x:c>
-      <x:c r="B210" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C210" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D210" t="str">
+      <x:c r="B212" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C212" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D212" t="str">
         <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
-    <x:row r="211">
-      <x:c r="A211" t="n">
+    <x:row r="213">
+      <x:c r="A213" s="10" t="n">
         <x:v>46227.5</x:v>
       </x:c>
-      <x:c r="B211" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C211" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D211" t="str">
+      <x:c r="B213" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C213" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D213" t="str">
         <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
-    <x:row r="212">
-      <x:c r="A212" t="n">
+    <x:row r="214">
+      <x:c r="A214" s="10" t="n">
         <x:v>46227.5</x:v>
       </x:c>
-      <x:c r="B212" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C212" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D212" t="str">
+      <x:c r="B214" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C214" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D214" t="str">
         <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
-    <x:row r="213">
-      <x:c r="A213" t="n">
-        <x:v>46227.5</x:v>
-      </x:c>
-      <x:c r="B213" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C213" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D213" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214">
-      <x:c r="A214" t="n">
-        <x:v>46227.5</x:v>
-      </x:c>
-      <x:c r="B214" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C214" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D214" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
-      </x:c>
-    </x:row>
     <x:row r="215">
-      <x:c r="A215" t="n">
+      <x:c r="A215" s="10" t="n">
         <x:v>46227.5</x:v>
       </x:c>
       <x:c r="B215" t="str">
@@ -3398,62 +3398,90 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D215" t="str">
+        <x:v>Add small-tournament Supabase migration.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="10" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B216" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C216" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D216" t="str">
+        <x:v>Add installable mobile RefHQ experience.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="10" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B217" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C217" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D217" t="str">
         <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
-    <x:row r="216">
-      <x:c r="A216" t="n">
+    <x:row r="218">
+      <x:c r="A218" s="10" t="n">
         <x:v>46227.5</x:v>
       </x:c>
-      <x:c r="B216" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C216" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D216" t="str">
+      <x:c r="B218" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C218" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D218" t="str">
         <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
-    <x:row r="217">
-      <x:c r="A217" t="n">
+    <x:row r="219">
+      <x:c r="A219" s="10" t="n">
         <x:v>46227.5</x:v>
       </x:c>
-      <x:c r="B217" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C217" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D217" t="str">
+      <x:c r="B219" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C219" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D219" t="str">
         <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
-    <x:row r="218">
-      <x:c r="A218" t="n">
+    <x:row r="220">
+      <x:c r="A220" s="10" t="n">
         <x:v>46227.5</x:v>
       </x:c>
-      <x:c r="B218" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C218" t="str">
+      <x:c r="B220" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C220" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D218" t="str">
+      <x:c r="D220" t="str">
         <x:v>Add RefHQ sign-in screen.</x:v>
       </x:c>
     </x:row>
-    <x:row r="219">
-      <x:c r="A219" t="n">
+    <x:row r="221">
+      <x:c r="A221" s="10" t="n">
         <x:v>46227.5</x:v>
       </x:c>
-      <x:c r="B219" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C219" t="str">
+      <x:c r="B221" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C221" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D219" t="str">
+      <x:c r="D221" t="str">
         <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
@@ -3469,7 +3497,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7f9402b8d334569"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re45730c2db194832"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Ra3429555ef0245a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Ree924b287d554cd4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,8 +13,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="201" formatCode="mmm d, yyyy"/>
   </x:numFmts>
   <x:fonts count="5">
     <x:font>
@@ -93,7 +94,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -156,6 +157,9 @@
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -199,7 +203,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D219" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D220" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -421,7 +425,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.37.1 · Brief descriptions of additions, removals, fixes, and updates since the initial build.</x:v>
+        <x:v>Current version: v0.38.0 · Brief descriptions of additions, removals, fixes, and updates</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -447,18 +451,18 @@
         <x:v>Brief Summary</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A5" s="23" t="n">
+    <x:row r="5" ht="48" hidden="0" customHeight="1">
+      <x:c r="A5" s="30" t="n">
         <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
-        <x:v>v0.37.1</x:v>
+        <x:v>v0.38.0</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
+        <x:v>Separated first and last names in referee and account records; kept combined-name displays; changed referee, coach, merge, rating, filter, and assignment selectors to last-name sorting with Last, First labels; added import/export support and safe backfill synchronization for existing records.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -466,27 +470,27 @@
         <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.37.0</x:v>
+        <x:v>v0.37.1</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
+        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="n">
-        <x:v>46256.833333333336</x:v>
+        <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.36.0</x:v>
+        <x:v>v0.37.0</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
+        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -494,139 +498,139 @@
         <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.35.5</x:v>
+        <x:v>v0.36.0</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
+        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
-        <x:v>46256.625</x:v>
+        <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.35.4</x:v>
+        <x:v>v0.35.5</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
+        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
-        <x:v>46256.604166666664</x:v>
+        <x:v>46256.625</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.35.3</x:v>
+        <x:v>v0.35.4</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
+        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
-        <x:v>46256.583333333336</x:v>
+        <x:v>46256.604166666664</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.35.2</x:v>
+        <x:v>v0.35.3</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
+        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A15" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -634,13 +638,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -648,27 +652,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -676,13 +680,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -690,13 +694,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -704,13 +708,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -718,13 +722,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -732,13 +736,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -746,13 +750,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -760,13 +764,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -774,13 +778,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -788,13 +792,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -802,13 +806,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -816,27 +820,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -844,13 +848,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -858,13 +862,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -872,13 +876,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -886,13 +890,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -900,13 +904,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -914,13 +918,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -928,13 +932,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -942,13 +946,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -956,13 +960,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -970,13 +974,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -984,13 +988,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -998,13 +1002,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1012,13 +1016,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1026,27 +1030,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1054,13 +1058,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1068,13 +1072,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1082,13 +1086,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1096,13 +1100,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1110,13 +1114,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1124,13 +1128,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1138,13 +1142,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1152,13 +1156,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1166,13 +1170,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1180,13 +1184,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1194,13 +1198,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1208,13 +1212,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1222,13 +1226,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1236,13 +1240,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1250,13 +1254,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1264,27 +1268,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
       <x:c r="A64" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1292,13 +1296,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1306,13 +1310,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1320,13 +1324,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1334,13 +1338,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1348,27 +1352,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
       <x:c r="A70" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1376,13 +1380,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1390,13 +1394,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1404,13 +1408,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1418,13 +1422,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1432,13 +1436,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1446,13 +1450,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1460,27 +1464,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
       <x:c r="A78" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1488,13 +1492,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1502,13 +1506,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1516,13 +1520,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1530,27 +1534,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1558,41 +1562,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1600,13 +1604,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1614,27 +1618,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
       <x:c r="A89" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1642,13 +1646,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1656,13 +1660,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1670,27 +1674,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
       <x:c r="A93" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1698,13 +1702,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1712,13 +1716,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1726,13 +1730,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1740,27 +1744,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
       <x:c r="A98" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B98" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1768,13 +1772,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B99" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1782,27 +1786,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B100" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C100" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
       <x:c r="A101" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B101" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C101" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1810,13 +1814,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B102" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C102" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1824,13 +1828,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B103" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C103" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1838,27 +1842,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B104" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C104" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
       <x:c r="A105" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B105" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C105" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1869,10 +1873,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C106" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1886,7 +1890,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1900,7 +1904,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1914,7 +1918,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1928,7 +1932,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1942,7 +1946,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1956,7 +1960,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1970,7 +1974,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1984,7 +1988,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -1998,7 +2002,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2012,7 +2016,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2026,7 +2030,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2040,7 +2044,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2054,7 +2058,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2065,10 +2069,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C120" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2079,10 +2083,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C121" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2096,7 +2100,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2110,7 +2114,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2121,10 +2125,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C124" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2135,10 +2139,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C125" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2152,7 +2156,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2166,7 +2170,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2180,12 +2184,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
       <x:c r="A129" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B129" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2194,7 +2198,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2208,7 +2212,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2222,7 +2226,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2236,7 +2240,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2250,7 +2254,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2261,10 +2265,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C134" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2275,10 +2279,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C135" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2292,7 +2296,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2306,7 +2310,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2320,7 +2324,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2334,7 +2338,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2348,7 +2352,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2362,7 +2366,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2376,7 +2380,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2390,7 +2394,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2404,7 +2408,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2415,10 +2419,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C145" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2429,10 +2433,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C146" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2446,7 +2450,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2460,7 +2464,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2474,7 +2478,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2488,7 +2492,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2502,7 +2506,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2513,10 +2517,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C152" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2527,10 +2531,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C153" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2544,7 +2548,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2558,7 +2562,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2572,7 +2576,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2586,7 +2590,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2597,10 +2601,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C158" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2611,10 +2615,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C159" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2628,7 +2632,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2642,7 +2646,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2656,7 +2660,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2670,7 +2674,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2684,7 +2688,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2698,7 +2702,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2712,7 +2716,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2726,12 +2730,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
       <x:c r="A168" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B168" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2740,7 +2744,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2751,10 +2755,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C169" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2765,10 +2769,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2779,10 +2783,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2793,10 +2797,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2807,10 +2811,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2838,7 +2842,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2849,10 +2853,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2863,10 +2867,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2877,10 +2881,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2891,10 +2895,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2905,10 +2909,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2916,13 +2920,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B181" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2930,13 +2934,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B182" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2950,7 +2954,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2961,10 +2965,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2978,7 +2982,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2989,10 +2993,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3003,10 +3007,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3017,10 +3021,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3031,10 +3035,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3045,10 +3049,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3059,10 +3063,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3076,7 +3080,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3087,10 +3091,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3104,7 +3108,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3118,7 +3122,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3129,10 +3133,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C196" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3143,24 +3147,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C197" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
       <x:c r="A198" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B198" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C198" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3168,27 +3172,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B199" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C199" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
       <x:c r="A200" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B200" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C200" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3199,10 +3203,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C201" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3216,7 +3220,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3230,7 +3234,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3241,10 +3245,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C204" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3258,7 +3262,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3272,7 +3276,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3286,7 +3290,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3297,10 +3301,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C208" s="28" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3311,10 +3315,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C209" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3325,10 +3329,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C210" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3342,7 +3346,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3356,7 +3360,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3370,7 +3374,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3384,7 +3388,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -3395,10 +3399,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C215" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D215" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -3412,7 +3416,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D216" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -3426,7 +3430,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D217" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -3437,10 +3441,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C218" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D218" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -3454,7 +3458,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D219" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Require Supabase login for RefHQ.</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -3465,23 +3469,29 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C220" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D220" t="str">
+        <x:v>Style Supabase sign-in.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="10"/>
+      <x:c r="B221"/>
+      <x:c r="C221"/>
+      <x:c r="D221"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B222" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C222" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D220" t="str">
-        <x:v>Add RefHQ sign-in screen.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="221">
-      <x:c r="A221" s="10" t="n">
-        <x:v>46227.5</x:v>
-      </x:c>
-      <x:c r="B221" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C221" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D221" t="str">
+      <x:c r="D222" t="str">
         <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
@@ -3497,7 +3507,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re45730c2db194832"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb75d3183dbec47f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Ree924b287d554cd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R1bd224497fa0451e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,9 +13,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="mmm d, yyyy"/>
+    <x:numFmt numFmtId="202" formatCode="@"/>
   </x:numFmts>
   <x:fonts count="5">
     <x:font>
@@ -94,7 +95,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -160,6 +161,10 @@
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -203,7 +208,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D220" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D221" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -425,11 +430,15 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.38.0 · Brief descriptions of additions, removals, fixes, and updates</x:v>
-      </x:c>
-      <x:c r="B2"/>
-      <x:c r="C2"/>
-      <x:c r="D2"/>
+        <x:v>Current version: v0.38.1 · Brief descriptions of additions, removals, fixes, and updates</x:v>
+      </x:c>
+      <x:c r="B2" s="31" t="str">
+        <x:v>v0.38.1</x:v>
+      </x:c>
+      <x:c r="C2" t="str"/>
+      <x:c r="D2" t="str">
+        <x:v>Updated 2026-08-23</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3"/>
@@ -452,17 +461,17 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="48" hidden="0" customHeight="1">
-      <x:c r="A5" s="30" t="n">
-        <x:v>46256.666666666664</x:v>
-      </x:c>
-      <x:c r="B5" s="29" t="str">
-        <x:v>v0.38.0</x:v>
+      <x:c r="A5" s="30" t="str">
+        <x:v>2026-08-23</x:v>
+      </x:c>
+      <x:c r="B5" s="32" t="str">
+        <x:v>v0.38.1</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Separated first and last names in referee and account records; kept combined-name displays; changed referee, coach, merge, rating, filter, and assignment selectors to last-name sorting with Last, First labels; added import/export support and safe backfill synchronization for existing records.</x:v>
+        <x:v>Added an atomic schedule tool to swap two staffed assignments between games in the same event while preserving each game's position slot; applies game-management permissions, leaves ratings unchanged, records an audit entry, sends no notification, and marks both games as updated.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -470,13 +479,13 @@
         <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>v0.37.1</x:v>
+        <x:v>v0.38.0</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
+        <x:v>Separated first and last names in referee and account records; kept combined-name displays; changed referee, coach, merge, rating, filter, and assignment selectors to last-name sorting with Last, First labels; added import/export support and safe backfill synchronization for existing records.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -484,27 +493,27 @@
         <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.37.0</x:v>
+        <x:v>v0.37.1</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
+        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="n">
-        <x:v>46256.833333333336</x:v>
+        <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.36.0</x:v>
+        <x:v>v0.37.0</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
+        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -512,139 +521,139 @@
         <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.35.5</x:v>
+        <x:v>v0.36.0</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
+        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
-        <x:v>46256.625</x:v>
+        <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.35.4</x:v>
+        <x:v>v0.35.5</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
+        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
-        <x:v>46256.604166666664</x:v>
+        <x:v>46256.625</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.35.3</x:v>
+        <x:v>v0.35.4</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
+        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
-        <x:v>46256.583333333336</x:v>
+        <x:v>46256.604166666664</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.35.2</x:v>
+        <x:v>v0.35.3</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
+        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A15" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A18" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -652,13 +661,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -666,27 +675,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -694,13 +703,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -708,13 +717,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -722,13 +731,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -736,13 +745,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -750,13 +759,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -764,13 +773,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -778,13 +787,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -792,13 +801,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -806,13 +815,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -820,13 +829,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -834,27 +843,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A33" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -862,13 +871,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -876,13 +885,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -890,13 +899,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -904,13 +913,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -918,13 +927,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -932,13 +941,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -946,13 +955,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -960,13 +969,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -974,13 +983,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -988,13 +997,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -1002,13 +1011,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1016,13 +1025,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1030,13 +1039,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1044,27 +1053,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
       <x:c r="A48" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1072,13 +1081,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1086,13 +1095,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1100,13 +1109,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1114,13 +1123,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1128,13 +1137,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1142,13 +1151,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1156,13 +1165,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1170,13 +1179,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1184,13 +1193,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1198,13 +1207,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1212,13 +1221,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1226,13 +1235,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1240,13 +1249,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1254,13 +1263,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1268,13 +1277,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1282,27 +1291,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1310,13 +1319,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1324,13 +1333,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1338,13 +1347,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1352,13 +1361,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1366,27 +1375,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1394,13 +1403,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1408,13 +1417,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1422,13 +1431,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1436,13 +1445,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1450,13 +1459,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1464,13 +1473,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1478,27 +1487,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1506,13 +1515,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1520,13 +1529,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1534,13 +1543,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1548,27 +1557,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1576,41 +1585,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -1618,13 +1627,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1632,27 +1641,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
       <x:c r="A90" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1660,13 +1669,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1674,13 +1683,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1688,27 +1697,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
       <x:c r="A94" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1716,13 +1725,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1730,13 +1739,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1744,13 +1753,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1758,27 +1767,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B98" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
       <x:c r="A99" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B99" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1786,13 +1795,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B100" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C100" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1800,27 +1809,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B101" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C101" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
       <x:c r="A102" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B102" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C102" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1828,13 +1837,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B103" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C103" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1842,13 +1851,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B104" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C104" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1856,27 +1865,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B105" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C105" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
       <x:c r="A106" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B106" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C106" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1887,10 +1896,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C107" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1904,7 +1913,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1918,7 +1927,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1932,7 +1941,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1946,7 +1955,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1960,7 +1969,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1974,7 +1983,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1988,7 +1997,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -2002,7 +2011,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2016,7 +2025,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2030,7 +2039,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2044,7 +2053,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2058,7 +2067,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2072,7 +2081,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2083,10 +2092,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C121" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2097,10 +2106,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C122" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2114,7 +2123,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2128,7 +2137,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2139,10 +2148,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C125" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2153,10 +2162,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C126" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2170,7 +2179,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2184,7 +2193,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2198,12 +2207,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
       <x:c r="A130" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B130" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2212,7 +2221,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2226,7 +2235,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2240,7 +2249,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2254,7 +2263,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2268,7 +2277,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2279,10 +2288,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C135" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2293,10 +2302,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C136" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2310,7 +2319,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2324,7 +2333,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2338,7 +2347,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2352,7 +2361,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2366,7 +2375,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2380,7 +2389,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2394,7 +2403,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2408,7 +2417,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2422,7 +2431,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2433,10 +2442,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C146" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2447,10 +2456,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C147" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2464,7 +2473,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2478,7 +2487,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2492,7 +2501,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2506,7 +2515,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2520,7 +2529,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2531,10 +2540,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C153" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2545,10 +2554,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C154" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2562,7 +2571,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2576,7 +2585,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2590,7 +2599,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2604,7 +2613,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2615,10 +2624,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C159" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2629,10 +2638,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C160" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2646,7 +2655,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2660,7 +2669,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2674,7 +2683,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2688,7 +2697,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2702,7 +2711,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2716,7 +2725,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2730,7 +2739,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2744,12 +2753,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
       <x:c r="A169" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B169" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2758,7 +2767,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2769,10 +2778,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C170" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2783,10 +2792,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2797,10 +2806,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2811,10 +2820,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2825,10 +2834,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2856,7 +2865,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2867,10 +2876,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2881,10 +2890,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2895,10 +2904,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2909,10 +2918,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2923,10 +2932,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2934,13 +2943,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B182" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2948,13 +2957,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B183" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2968,7 +2977,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2979,10 +2988,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -2996,7 +3005,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3007,10 +3016,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3021,10 +3030,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3035,10 +3044,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3049,10 +3058,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3063,10 +3072,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3077,10 +3086,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3094,7 +3103,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3105,10 +3114,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3122,7 +3131,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3136,7 +3145,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3147,10 +3156,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C197" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3161,24 +3170,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C198" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
       <x:c r="A199" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B199" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C199" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3186,27 +3195,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B200" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C200" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
       <x:c r="A201" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B201" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C201" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3217,10 +3226,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C202" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3234,7 +3243,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3248,7 +3257,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3259,10 +3268,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C205" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3276,7 +3285,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3290,7 +3299,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3304,7 +3313,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3315,10 +3324,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C209" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3329,10 +3338,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C210" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3343,10 +3352,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C211" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3360,7 +3369,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3374,7 +3383,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3388,7 +3397,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -3402,7 +3411,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D215" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -3413,10 +3422,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C216" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D216" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -3430,7 +3439,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D217" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -3444,7 +3453,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D218" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -3455,10 +3464,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C219" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D219" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -3472,26 +3481,40 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D220" t="str">
+        <x:v>Require Supabase login for RefHQ.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="10" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B221" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C221" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D221" t="str">
         <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
-    <x:row r="221">
-      <x:c r="A221" s="10"/>
-      <x:c r="B221"/>
-      <x:c r="C221"/>
-      <x:c r="D221"/>
-    </x:row>
     <x:row r="222">
-      <x:c r="A222" t="n">
+      <x:c r="A222" t="str"/>
+      <x:c r="B222" t="str"/>
+      <x:c r="C222" t="str"/>
+      <x:c r="D222" t="str"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" t="n">
         <x:v>46227.5</x:v>
       </x:c>
-      <x:c r="B222" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C222" t="str">
+      <x:c r="B223" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C223" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D222" t="str">
+      <x:c r="D223" t="str">
         <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
@@ -3507,7 +3530,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb75d3183dbec47f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bc9ce80593c4a72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R1bd224497fa0451e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Ra97efb268d594506"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -95,7 +95,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -165,6 +165,9 @@
     <x:xf numFmtId="202" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -208,7 +211,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D221" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D222" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -430,10 +433,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.38.1 · Brief descriptions of additions, removals, fixes, and updates</x:v>
+        <x:v>Current version: v0.38.2 · Brief descriptions of additions, removals, fixes, and updates</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>v0.38.1</x:v>
+        <x:v>v0.38.2</x:v>
       </x:c>
       <x:c r="C2" t="str"/>
       <x:c r="D2" t="str">
@@ -465,27 +468,27 @@
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="B5" s="32" t="str">
+        <x:v>v0.38.2</x:v>
+      </x:c>
+      <x:c r="C5" s="24" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D5" s="24" t="str">
+        <x:v>Limited the Schedule assignment-swap game selectors to games matching the Schedule's currently active filters.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A6" s="25" t="str">
+        <x:v>2026-08-23</x:v>
+      </x:c>
+      <x:c r="B6" s="33" t="str">
         <x:v>v0.38.1</x:v>
       </x:c>
-      <x:c r="C5" s="24" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D5" s="24" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Added an atomic schedule tool to swap two staffed assignments between games in the same event while preserving each game's position slot; applies game-management permissions, leaves ratings unchanged, records an audit entry, sends no notification, and marks both games as updated.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A6" s="25" t="n">
-        <x:v>46256.666666666664</x:v>
-      </x:c>
-      <x:c r="B6" s="26" t="str">
-        <x:v>v0.38.0</x:v>
-      </x:c>
-      <x:c r="C6" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D6" s="26" t="str">
-        <x:v>Separated first and last names in referee and account records; kept combined-name displays; changed referee, coach, merge, rating, filter, and assignment selectors to last-name sorting with Last, First labels; added import/export support and safe backfill synchronization for existing records.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -493,13 +496,13 @@
         <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>v0.37.1</x:v>
+        <x:v>v0.38.0</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
+        <x:v>Separated first and last names in referee and account records; kept combined-name displays; changed referee, coach, merge, rating, filter, and assignment selectors to last-name sorting with Last, First labels; added import/export support and safe backfill synchronization for existing records.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -507,27 +510,27 @@
         <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.37.0</x:v>
+        <x:v>v0.37.1</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
+        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="n">
-        <x:v>46256.833333333336</x:v>
+        <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.36.0</x:v>
+        <x:v>v0.37.0</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
+        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -535,139 +538,139 @@
         <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.35.5</x:v>
+        <x:v>v0.36.0</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
+        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
-        <x:v>46256.625</x:v>
+        <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.35.4</x:v>
+        <x:v>v0.35.5</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
+        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
-        <x:v>46256.604166666664</x:v>
+        <x:v>46256.625</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.35.3</x:v>
+        <x:v>v0.35.4</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
+        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
-        <x:v>46256.583333333336</x:v>
+        <x:v>46256.604166666664</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.35.2</x:v>
+        <x:v>v0.35.3</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
+        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="25" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A15" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A18" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -675,13 +678,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -689,27 +692,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -717,13 +720,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -731,13 +734,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -745,13 +748,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -759,13 +762,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -773,13 +776,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -787,13 +790,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -801,13 +804,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -815,13 +818,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -829,13 +832,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -843,13 +846,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -857,27 +860,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -885,13 +888,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -899,13 +902,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -913,13 +916,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -927,13 +930,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -941,13 +944,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -955,13 +958,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -969,13 +972,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -983,13 +986,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -997,13 +1000,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -1011,13 +1014,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1025,13 +1028,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1039,13 +1042,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1053,13 +1056,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1067,27 +1070,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
       <x:c r="A49" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1095,13 +1098,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1109,13 +1112,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1123,13 +1126,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1137,13 +1140,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1151,13 +1154,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1165,13 +1168,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1179,13 +1182,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1193,13 +1196,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1207,13 +1210,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1221,13 +1224,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1235,13 +1238,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1249,13 +1252,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1263,13 +1266,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1277,13 +1280,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1291,13 +1294,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1305,27 +1308,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1333,13 +1336,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1347,13 +1350,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1361,13 +1364,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1375,13 +1378,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1389,27 +1392,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1417,13 +1420,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1431,13 +1434,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1445,13 +1448,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1459,13 +1462,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1473,13 +1476,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1487,13 +1490,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1501,27 +1504,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1529,13 +1532,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1543,13 +1546,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1557,13 +1560,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1571,27 +1574,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1599,41 +1602,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -1641,13 +1644,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1655,27 +1658,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
       <x:c r="A91" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1683,13 +1686,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1697,13 +1700,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1711,27 +1714,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
       <x:c r="A95" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1739,13 +1742,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1753,13 +1756,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1767,13 +1770,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B98" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1781,27 +1784,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B99" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
       <x:c r="A100" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B100" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C100" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1809,13 +1812,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B101" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C101" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1823,27 +1826,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B102" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C102" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
       <x:c r="A103" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B103" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C103" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1851,13 +1854,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B104" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C104" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1865,13 +1868,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B105" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C105" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1879,27 +1882,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B106" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C106" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
       <x:c r="A107" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B107" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C107" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1910,10 +1913,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C108" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1927,7 +1930,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1941,7 +1944,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1955,7 +1958,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1969,7 +1972,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1983,7 +1986,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -1997,7 +2000,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -2011,7 +2014,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2025,7 +2028,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2039,7 +2042,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2053,7 +2056,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2067,7 +2070,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2081,7 +2084,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2095,7 +2098,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2106,10 +2109,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C122" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2120,10 +2123,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C123" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2137,7 +2140,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2151,7 +2154,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2162,10 +2165,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C126" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2176,10 +2179,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C127" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2193,7 +2196,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2207,7 +2210,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2221,12 +2224,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
       <x:c r="A131" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B131" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2235,7 +2238,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2249,7 +2252,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2263,7 +2266,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2277,7 +2280,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2291,7 +2294,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2302,10 +2305,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C136" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2316,10 +2319,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C137" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2333,7 +2336,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2347,7 +2350,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2361,7 +2364,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2375,7 +2378,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2389,7 +2392,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2403,7 +2406,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2417,7 +2420,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2431,7 +2434,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2445,7 +2448,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2456,10 +2459,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C147" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2470,10 +2473,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C148" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2487,7 +2490,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2501,7 +2504,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2515,7 +2518,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2529,7 +2532,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2543,7 +2546,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2554,10 +2557,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C154" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2568,10 +2571,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C155" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2585,7 +2588,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2599,7 +2602,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2613,7 +2616,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2627,7 +2630,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2638,10 +2641,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C160" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2652,10 +2655,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C161" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2669,7 +2672,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2683,7 +2686,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2697,7 +2700,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2711,7 +2714,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2725,7 +2728,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2739,7 +2742,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2753,7 +2756,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2767,12 +2770,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
       <x:c r="A170" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B170" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2781,7 +2784,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2792,10 +2795,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C171" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2806,10 +2809,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2820,10 +2823,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2834,10 +2837,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2848,10 +2851,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2879,7 +2882,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2890,10 +2893,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2904,10 +2907,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2918,10 +2921,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2932,10 +2935,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2946,10 +2949,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2957,13 +2960,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B183" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2971,13 +2974,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B184" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2991,7 +2994,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -3002,10 +3005,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C186" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3019,7 +3022,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3030,10 +3033,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3044,10 +3047,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3058,10 +3061,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3072,10 +3075,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3086,10 +3089,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3100,10 +3103,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3117,7 +3120,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3128,10 +3131,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C195" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3145,7 +3148,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3159,7 +3162,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3170,10 +3173,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C198" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3184,24 +3187,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C199" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
       <x:c r="A200" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B200" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C200" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3209,27 +3212,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B201" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C201" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
       <x:c r="A202" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B202" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C202" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -3240,10 +3243,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C203" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3257,7 +3260,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3271,7 +3274,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3282,10 +3285,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C206" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3299,7 +3302,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3313,7 +3316,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3327,7 +3330,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3338,10 +3341,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C210" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3352,10 +3355,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C211" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3366,10 +3369,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C212" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3383,7 +3386,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3397,7 +3400,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -3411,7 +3414,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D215" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -3425,7 +3428,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D216" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -3436,10 +3439,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C217" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D217" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -3453,7 +3456,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D218" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -3467,7 +3470,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D219" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -3478,10 +3481,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C220" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D220" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
@@ -3495,26 +3498,40 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D221" t="str">
+        <x:v>Require Supabase login for RefHQ.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B222" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C222" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D222" t="str">
         <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
-    <x:row r="222">
-      <x:c r="A222" t="str"/>
-      <x:c r="B222" t="str"/>
-      <x:c r="C222" t="str"/>
-      <x:c r="D222" t="str"/>
-    </x:row>
     <x:row r="223">
-      <x:c r="A223" t="n">
+      <x:c r="A223" t="str"/>
+      <x:c r="B223" t="str"/>
+      <x:c r="C223" t="str"/>
+      <x:c r="D223" t="str"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" t="n">
         <x:v>46227.5</x:v>
       </x:c>
-      <x:c r="B223" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C223" t="str">
+      <x:c r="B224" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C224" t="str">
         <x:v>Added</x:v>
       </x:c>
-      <x:c r="D223" t="str">
+      <x:c r="D224" t="str">
         <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
@@ -3530,7 +3547,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bc9ce80593c4a72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re453a7a631eb45a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Ra97efb268d594506"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R1a00964cbc8d4306"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D222" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D223" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -433,10 +433,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.38.2 · Brief descriptions of additions, removals, fixes, and updates</x:v>
+        <x:v>Current version: v0.38.3 · Brief descriptions of additions, removals, fixes, and updates</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>v0.38.2</x:v>
+        <x:v>v0.38.3</x:v>
       </x:c>
       <x:c r="C2" t="str"/>
       <x:c r="D2" t="str">
@@ -468,13 +468,13 @@
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="B5" s="32" t="str">
-        <x:v>v0.38.2</x:v>
+        <x:v>v0.38.3</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Limited the Schedule assignment-swap game selectors to games matching the Schedule's currently active filters.</x:v>
+        <x:v>Added an atomic full-crew swap option for two filtered Schedule games with matching staffed crew sizes, preserving each game's position structure and imported crew order while leaving ratings unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -482,27 +482,27 @@
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="B6" s="33" t="str">
+        <x:v>v0.38.2</x:v>
+      </x:c>
+      <x:c r="C6" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D6" s="26" t="str">
+        <x:v>Limited the Schedule assignment-swap game selectors to games matching the Schedule's currently active filters.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A7" s="25" t="str">
+        <x:v>2026-08-23</x:v>
+      </x:c>
+      <x:c r="B7" s="33" t="str">
         <x:v>v0.38.1</x:v>
       </x:c>
-      <x:c r="C6" s="26" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D6" s="26" t="str">
+      <x:c r="C7" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D7" s="26" t="str">
         <x:v>Added an atomic schedule tool to swap two staffed assignments between games in the same event while preserving each game's position slot; applies game-management permissions, leaves ratings unchanged, records an audit entry, sends no notification, and marks both games as updated.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A7" s="25" t="n">
-        <x:v>46256.666666666664</x:v>
-      </x:c>
-      <x:c r="B7" s="26" t="str">
-        <x:v>v0.38.0</x:v>
-      </x:c>
-      <x:c r="C7" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D7" s="26" t="str">
-        <x:v>Separated first and last names in referee and account records; kept combined-name displays; changed referee, coach, merge, rating, filter, and assignment selectors to last-name sorting with Last, First labels; added import/export support and safe backfill synchronization for existing records.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -510,13 +510,13 @@
         <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>v0.37.1</x:v>
+        <x:v>v0.38.0</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
+        <x:v>Separated first and last names in referee and account records; kept combined-name displays; changed referee, coach, merge, rating, filter, and assignment selectors to last-name sorting with Last, First labels; added import/export support and safe backfill synchronization for existing records.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -524,27 +524,27 @@
         <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>v0.37.0</x:v>
+        <x:v>v0.37.1</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D9" s="26" t="str">
-        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
+        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="25" t="n">
-        <x:v>46256.833333333336</x:v>
+        <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.36.0</x:v>
+        <x:v>v0.37.0</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
+        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -552,139 +552,139 @@
         <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.35.5</x:v>
+        <x:v>v0.36.0</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
+        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
-        <x:v>46256.625</x:v>
+        <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.35.4</x:v>
+        <x:v>v0.35.5</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
+        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
-        <x:v>46256.604166666664</x:v>
+        <x:v>46256.625</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.35.3</x:v>
+        <x:v>v0.35.4</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
+        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="25" t="n">
-        <x:v>46256.583333333336</x:v>
+        <x:v>46256.604166666664</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.35.2</x:v>
+        <x:v>v0.35.3</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
+        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A15" s="25" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A18" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -692,13 +692,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -706,27 +706,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -734,13 +734,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -748,13 +748,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -762,13 +762,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -776,13 +776,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -790,13 +790,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -804,13 +804,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -818,13 +818,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -832,13 +832,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -846,13 +846,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -860,13 +860,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -874,27 +874,27 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A35" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -902,13 +902,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -916,13 +916,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -930,13 +930,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -944,13 +944,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -958,13 +958,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -972,13 +972,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -986,13 +986,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1000,13 +1000,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -1014,13 +1014,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1028,13 +1028,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1042,13 +1042,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1056,13 +1056,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1070,13 +1070,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1084,27 +1084,27 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
       <x:c r="A50" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1112,13 +1112,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1126,13 +1126,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1140,13 +1140,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1154,13 +1154,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1168,13 +1168,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1182,13 +1182,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1196,13 +1196,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1210,13 +1210,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1224,13 +1224,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1238,13 +1238,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1252,13 +1252,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1266,13 +1266,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1280,13 +1280,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1294,13 +1294,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1308,13 +1308,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1322,27 +1322,27 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -1350,13 +1350,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -1364,13 +1364,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1378,13 +1378,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1392,13 +1392,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1406,27 +1406,27 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -1434,13 +1434,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -1448,13 +1448,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1462,13 +1462,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1476,13 +1476,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1490,13 +1490,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1504,13 +1504,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1518,27 +1518,27 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -1546,13 +1546,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -1560,13 +1560,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1574,13 +1574,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1588,27 +1588,27 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -1616,41 +1616,41 @@
         <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
       <x:c r="A89" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -1658,13 +1658,13 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -1672,27 +1672,27 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
       <x:c r="A92" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -1700,13 +1700,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -1714,13 +1714,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1728,27 +1728,27 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
       <x:c r="A96" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -1756,13 +1756,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -1770,13 +1770,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B98" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1784,13 +1784,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B99" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1798,27 +1798,27 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B100" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C100" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
       <x:c r="A101" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B101" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C101" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -1826,13 +1826,13 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B102" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C102" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -1840,27 +1840,27 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B103" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C103" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
       <x:c r="A104" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B104" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C104" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -1868,13 +1868,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B105" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C105" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -1882,13 +1882,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B106" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C106" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1896,27 +1896,27 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B107" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C107" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
       <x:c r="A108" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B108" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C108" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -1927,10 +1927,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C109" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -1944,7 +1944,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1958,7 +1958,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1972,7 +1972,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1986,7 +1986,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -2000,7 +2000,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -2014,7 +2014,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2028,7 +2028,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2042,7 +2042,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2056,7 +2056,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2070,7 +2070,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2084,7 +2084,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2098,7 +2098,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2112,7 +2112,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2123,10 +2123,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C123" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2137,10 +2137,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C124" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2154,7 +2154,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2168,7 +2168,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2179,10 +2179,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C127" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2193,10 +2193,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C128" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2210,7 +2210,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2224,7 +2224,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2238,12 +2238,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
       <x:c r="A132" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B132" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2252,7 +2252,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -2266,7 +2266,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -2280,7 +2280,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2294,7 +2294,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2308,7 +2308,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2319,10 +2319,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C137" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2333,10 +2333,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C138" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2350,7 +2350,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2364,7 +2364,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2378,7 +2378,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2392,7 +2392,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2406,7 +2406,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2420,7 +2420,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2434,7 +2434,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2448,7 +2448,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2462,7 +2462,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2473,10 +2473,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C148" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2487,10 +2487,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C149" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2504,7 +2504,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2518,7 +2518,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2532,7 +2532,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2546,7 +2546,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2560,7 +2560,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2571,10 +2571,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C155" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2585,10 +2585,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C156" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2602,7 +2602,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2616,7 +2616,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2630,7 +2630,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2644,7 +2644,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2655,10 +2655,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C161" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2669,10 +2669,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C162" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2686,7 +2686,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2700,7 +2700,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2714,7 +2714,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2728,7 +2728,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2742,7 +2742,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2756,7 +2756,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2770,7 +2770,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2784,12 +2784,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
       <x:c r="A171" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B171" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2798,7 +2798,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -2809,10 +2809,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C172" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -2823,10 +2823,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2837,10 +2837,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C174" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2851,10 +2851,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2865,10 +2865,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2896,7 +2896,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2907,10 +2907,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C179" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2921,10 +2921,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2935,10 +2935,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C181" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2949,10 +2949,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2963,10 +2963,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2974,13 +2974,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B184" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2988,13 +2988,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B185" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -3008,7 +3008,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3019,10 +3019,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3036,7 +3036,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3047,10 +3047,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3061,10 +3061,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3075,10 +3075,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3089,10 +3089,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3103,10 +3103,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3117,10 +3117,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3134,7 +3134,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3145,10 +3145,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C196" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3162,7 +3162,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3176,7 +3176,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3187,10 +3187,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C199" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3201,24 +3201,24 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C200" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
       <x:c r="A201" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B201" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C201" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -3226,27 +3226,27 @@
         <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B202" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C202" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
       <x:c r="A203" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B203" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C203" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -3257,10 +3257,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C204" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -3274,7 +3274,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3288,7 +3288,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3299,10 +3299,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C207" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3316,7 +3316,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3330,7 +3330,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3344,7 +3344,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3355,10 +3355,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C211" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3369,10 +3369,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C212" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3383,10 +3383,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C213" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3400,7 +3400,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -3414,7 +3414,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D215" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -3428,7 +3428,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D216" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -3442,7 +3442,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D217" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -3453,10 +3453,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C218" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D218" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -3470,7 +3470,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D219" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -3484,7 +3484,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D220" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
@@ -3495,10 +3495,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C221" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D221" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -3512,26 +3512,40 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D222" t="str">
+        <x:v>Require Supabase login for RefHQ.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B223" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C223" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D223" t="str">
         <x:v>Style Supabase sign-in.</x:v>
       </x:c>
     </x:row>
-    <x:row r="223">
-      <x:c r="A223" t="str"/>
-      <x:c r="B223" t="str"/>
-      <x:c r="C223" t="str"/>
-      <x:c r="D223" t="str"/>
-    </x:row>
     <x:row r="224">
-      <x:c r="A224" t="n">
+      <x:c r="A224" t="str"/>
+      <x:c r="B224" t="str"/>
+      <x:c r="C224" t="str"/>
+      <x:c r="D224" t="str"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" t="n">
         <x:v>46227.5</x:v>
       </x:c>
-      <x:c r="B224" t="str">
-        <x:v>Early build</x:v>
-      </x:c>
-      <x:c r="C224" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D224" t="str">
+      <x:c r="B225" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C225" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D225" t="str">
         <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
@@ -3547,7 +3561,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re453a7a631eb45a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90476a34b27d4e0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R1a00964cbc8d4306"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R812d5787f27d407c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D223" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D225" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -433,10 +433,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.38.3 · Brief descriptions of additions, removals, fixes, and updates</x:v>
+        <x:v>Current version: v0.39.1 · Brief descriptions of additions, removals, fixes, and updates</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>v0.38.3</x:v>
+        <x:v>v0.39.1</x:v>
       </x:c>
       <x:c r="C2" t="str"/>
       <x:c r="D2" t="str">
@@ -468,13 +468,13 @@
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="B5" s="32" t="str">
-        <x:v>v0.38.3</x:v>
+        <x:v>v0.39.1</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Added an atomic full-crew swap option for two filtered Schedule games with matching staffed crew sizes, preserving each game's position structure and imported crew order while leaving ratings unchanged.</x:v>
+        <x:v>Added an optional atomic crew-with-game mode to game-detail swaps, allowing complete staffed crews to remain with their matchups when games switch schedule slots while preserving ratings and source identifiers.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -482,13 +482,13 @@
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="B6" s="33" t="str">
-        <x:v>v0.38.2</x:v>
+        <x:v>v0.39.0</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Limited the Schedule assignment-swap game selectors to games matching the Schedule's currently active filters.</x:v>
+        <x:v>Added permission-gated game information editing and atomic swapping of matchup and competition details between filtered schedule slots while preserving crews, ratings, source identifiers, and unchanged slot time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -496,41 +496,41 @@
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="B7" s="33" t="str">
+        <x:v>v0.38.3</x:v>
+      </x:c>
+      <x:c r="C7" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D7" s="26" t="str">
+        <x:v>Added an atomic full-crew swap option for two filtered Schedule games with matching staffed crew sizes, preserving each game's position structure and imported crew order while leaving ratings unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="25" t="str">
+        <x:v>2026-08-23</x:v>
+      </x:c>
+      <x:c r="B8" s="33" t="str">
+        <x:v>v0.38.2</x:v>
+      </x:c>
+      <x:c r="C8" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D8" s="26" t="str">
+        <x:v>Limited the Schedule assignment-swap game selectors to games matching the Schedule's currently active filters.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="25" t="str">
+        <x:v>2026-08-23</x:v>
+      </x:c>
+      <x:c r="B9" s="33" t="str">
         <x:v>v0.38.1</x:v>
       </x:c>
-      <x:c r="C7" s="26" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D7" s="26" t="str">
+      <x:c r="C9" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D9" s="26" t="str">
         <x:v>Added an atomic schedule tool to swap two staffed assignments between games in the same event while preserving each game's position slot; applies game-management permissions, leaves ratings unchanged, records an audit entry, sends no notification, and marks both games as updated.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="25" t="n">
-        <x:v>46256.666666666664</x:v>
-      </x:c>
-      <x:c r="B8" s="26" t="str">
-        <x:v>v0.38.0</x:v>
-      </x:c>
-      <x:c r="C8" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D8" s="26" t="str">
-        <x:v>Separated first and last names in referee and account records; kept combined-name displays; changed referee, coach, merge, rating, filter, and assignment selectors to last-name sorting with Last, First labels; added import/export support and safe backfill synchronization for existing records.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="25" t="n">
-        <x:v>46256.666666666664</x:v>
-      </x:c>
-      <x:c r="B9" s="26" t="str">
-        <x:v>v0.37.1</x:v>
-      </x:c>
-      <x:c r="C9" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D9" s="26" t="str">
-        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -538,181 +538,181 @@
         <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B10" s="26" t="str">
-        <x:v>v0.37.0</x:v>
+        <x:v>v0.38.0</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D10" s="26" t="str">
-        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
+        <x:v>Separated first and last names in referee and account records; kept combined-name displays; changed referee, coach, merge, rating, filter, and assignment selectors to last-name sorting with Last, First labels; added import/export support and safe backfill synchronization for existing records.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="25" t="n">
-        <x:v>46256.833333333336</x:v>
+        <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.36.0</x:v>
+        <x:v>v0.37.1</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
+        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="25" t="n">
-        <x:v>46256.833333333336</x:v>
+        <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.35.5</x:v>
+        <x:v>v0.37.0</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
+        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
-        <x:v>46256.625</x:v>
+        <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.35.4</x:v>
+        <x:v>v0.36.0</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
+        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="25" t="n">
-        <x:v>46256.604166666664</x:v>
+        <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.35.3</x:v>
+        <x:v>v0.35.5</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
+        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A15" s="25" t="n">
-        <x:v>46256.583333333336</x:v>
+        <x:v>46256.625</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.35.2</x:v>
+        <x:v>v0.35.4</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
+        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="25" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.604166666664</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.3</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A18" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -720,41 +720,41 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A25" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -762,13 +762,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -776,13 +776,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -790,13 +790,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -804,13 +804,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -818,13 +818,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -832,13 +832,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -846,13 +846,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -860,13 +860,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -874,13 +874,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.31.6</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
+        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -888,41 +888,41 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.31.5</x:v>
+        <x:v>v0.31.8</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
+        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific official schedule views.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A36" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B36" s="26" t="str">
-        <x:v>v0.31.4</x:v>
+        <x:v>v0.31.6</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
-        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
+        <x:v>Makes the live check-in counter reflect the roster currently visible after applying name, status, and site filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A37" s="25" t="n">
-        <x:v>46254.5</x:v>
+        <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B37" s="26" t="str">
-        <x:v>v0.31.3</x:v>
+        <x:v>v0.31.5</x:v>
       </x:c>
       <x:c r="C37" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D37" s="26" t="str">
-        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
+        <x:v>Rebuilds the schedule assignment editor as a contained, vertically stacked modal instead of allowing assignment cards to spread horizontally.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -930,13 +930,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B38" s="26" t="str">
-        <x:v>v0.31.2</x:v>
+        <x:v>v0.31.4</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D38" s="26" t="str">
-        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
+        <x:v>Restores game visibility for every linked Referee Coach based on their saved coaching assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -944,13 +944,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B39" s="26" t="str">
-        <x:v>v0.31.1</x:v>
+        <x:v>v0.31.3</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D39" s="26" t="str">
-        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
+        <x:v>Fixes Site Supervisor schedules displaying assigned crew positions as Unassigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -958,13 +958,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B40" s="26" t="str">
-        <x:v>v0.31.0</x:v>
+        <x:v>v0.31.2</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D40" s="26" t="str">
-        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
+        <x:v>Adds a prominent full-width schedule link immediately below the welcome area on every dashboard.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -972,13 +972,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B41" s="26" t="str">
-        <x:v>v0.30.5</x:v>
+        <x:v>v0.31.1</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D41" s="26" t="str">
-        <x:v>Expands Help according to the active role hierarchy.</x:v>
+        <x:v>Adds date-specific Not Expected attendance overrides without removing officials or changing their assignments.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -986,13 +986,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B42" s="26" t="str">
-        <x:v>v0.30.4</x:v>
+        <x:v>v0.31.0</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D42" s="26" t="str">
-        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
+        <x:v>Moves primary page navigation from the fixed header into a right-side tray opened by the user badge.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1000,13 +1000,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B43" s="26" t="str">
-        <x:v>v0.30.3</x:v>
+        <x:v>v0.30.5</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D43" s="26" t="str">
-        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
+        <x:v>Expands Help according to the active role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -1014,13 +1014,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B44" s="26" t="str">
-        <x:v>v0.30.2</x:v>
+        <x:v>v0.30.4</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D44" s="26" t="str">
-        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
+        <x:v>Opens Referee Coach schedules on one date by default: the current event date, or the event's first game date when it has not started.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -1028,13 +1028,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B45" s="26" t="str">
-        <x:v>v0.30.1</x:v>
+        <x:v>v0.30.3</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D45" s="26" t="str">
-        <x:v>Adds an event-level External Check-In completion mode.</x:v>
+        <x:v>Ensures Site Supervisors can read the crews for operational and REF HQ schedule records within their assigned dates and sites even when assignment editing is disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1042,13 +1042,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B46" s="26" t="str">
-        <x:v>v0.30.0</x:v>
+        <x:v>v0.30.2</x:v>
       </x:c>
       <x:c r="C46" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D46" s="26" t="str">
-        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
+        <x:v>Adds live first-name or last-name search to both administrative Check-In roster views.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -1056,13 +1056,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B47" s="26" t="str">
-        <x:v>v0.29.5</x:v>
+        <x:v>v0.30.1</x:v>
       </x:c>
       <x:c r="C47" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D47" s="26" t="str">
-        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
+        <x:v>Adds an event-level External Check-In completion mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -1070,13 +1070,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B48" s="26" t="str">
-        <x:v>v0.29.4</x:v>
+        <x:v>v0.30.0</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D48" s="26" t="str">
-        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
+        <x:v>Removes implicit anonymous execution from every elevated public database function.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -1084,13 +1084,13 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B49" s="26" t="str">
-        <x:v>v0.29.3</x:v>
+        <x:v>v0.29.5</x:v>
       </x:c>
       <x:c r="C49" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D49" s="26" t="str">
-        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
+        <x:v>Schedule imports now skip only a conflicting contact field instead of stopping the batch.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1098,41 +1098,41 @@
         <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B50" s="26" t="str">
-        <x:v>v0.29.2</x:v>
+        <x:v>v0.29.4</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D50" s="26" t="str">
-        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
+        <x:v>Limits Coaching-system assignments to ratings-enabled games.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B51" s="26" t="str">
-        <x:v>v0.29.0</x:v>
+        <x:v>v0.29.3</x:v>
       </x:c>
       <x:c r="C51" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D51" s="26" t="str">
-        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
+        <x:v>Corrects Assignr contact and assignment matching when two officials share an email address.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
       <x:c r="A52" s="25" t="n">
-        <x:v>46253.5</x:v>
+        <x:v>46254.5</x:v>
       </x:c>
       <x:c r="B52" s="26" t="str">
-        <x:v>v0.28.1</x:v>
+        <x:v>v0.29.2</x:v>
       </x:c>
       <x:c r="C52" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D52" s="26" t="str">
-        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
+        <x:v>Uses nonblank email addresses and mobile phone numbers from Assignr Assignments exports to create or update Officials Directory records during a schedule import.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -1140,13 +1140,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B53" s="26" t="str">
-        <x:v>v0.28.0</x:v>
+        <x:v>v0.29.0</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D53" s="26" t="str">
-        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
+        <x:v>Added automatic support for Assignr Assignments exports where each official appears on a separate row.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1154,13 +1154,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B54" s="26" t="str">
-        <x:v>v0.27.14</x:v>
+        <x:v>v0.28.1</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D54" s="26" t="str">
-        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
+        <x:v>Keeps Schedule crew cards in fixed Referee, AR1, AR2, and Fourth Official columns even in browsers that do not apply modern range-style media queries.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -1168,13 +1168,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B55" s="26" t="str">
-        <x:v>v0.27.12</x:v>
+        <x:v>v0.28.0</x:v>
       </x:c>
       <x:c r="C55" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D55" s="26" t="str">
-        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
+        <x:v>Replaces Last Login in the Officials directory with Last Active, refreshed when a linked user opens Law18Ref, navigates its tabs, returns to the visible app, or continues an active session.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -1182,13 +1182,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B56" s="26" t="str">
-        <x:v>v0.27.10</x:v>
+        <x:v>v0.27.14</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D56" s="26" t="str">
-        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
+        <x:v>Makes the administrative check-in QR card collapsible and collapsed by default while keeping QR generation and printing out of referee-only and coach-only views.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1196,13 +1196,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B57" s="26" t="str">
-        <x:v>v0.27.9</x:v>
+        <x:v>v0.27.12</x:v>
       </x:c>
       <x:c r="C57" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D57" s="26" t="str">
-        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
+        <x:v>Aligns Referee, AR, and Fourth Official columns consistently across games in the desktop Schedule view.</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -1210,13 +1210,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B58" s="26" t="str">
-        <x:v>v0.27.8</x:v>
+        <x:v>v0.27.10</x:v>
       </x:c>
       <x:c r="C58" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D58" s="26" t="str">
-        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
+        <x:v>Makes each coach's assigned games collapsible within Coach Access Summary and makes the full game-assignment schedule collapsible by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -1224,13 +1224,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B59" s="26" t="str">
-        <x:v>v0.27.7</x:v>
+        <x:v>v0.27.9</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D59" s="26" t="str">
-        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
+        <x:v>Moves the collapsed Coach Access Summary above the long game-assignment schedule for immediate access.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -1238,13 +1238,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B60" s="26" t="str">
-        <x:v>v0.27.6</x:v>
+        <x:v>v0.27.8</x:v>
       </x:c>
       <x:c r="C60" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D60" s="26" t="str">
-        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
+        <x:v>Makes the Coaching tab's coach-access summary collapsible and collapsed by default, with the assigned-coach count visible in its header.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -1252,13 +1252,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B61" s="26" t="str">
-        <x:v>v0.27.5</x:v>
+        <x:v>v0.27.7</x:v>
       </x:c>
       <x:c r="C61" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D61" s="26" t="str">
-        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
+        <x:v>Omits a misleading first field from Check-In when a referee coach covers multiple fields at their earliest coaching time.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -1266,13 +1266,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B62" s="26" t="str">
-        <x:v>v0.27.2</x:v>
+        <x:v>v0.27.6</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D62" s="26" t="str">
-        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
+        <x:v>Suppresses browser-generated headers and footers when printing QR sheets while preserving safe internal page spacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -1280,13 +1280,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B63" s="26" t="str">
-        <x:v>v0.27.1</x:v>
+        <x:v>v0.27.5</x:v>
       </x:c>
       <x:c r="C63" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D63" s="26" t="str">
-        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
+        <x:v>Prints every event-day check-in QR as a separate, clean page with large event and date labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -1294,13 +1294,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B64" s="26" t="str">
-        <x:v>v0.27.0</x:v>
+        <x:v>v0.27.2</x:v>
       </x:c>
       <x:c r="C64" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D64" s="26" t="str">
-        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
+        <x:v>Adds role-aware PDF quick guides to the Help modal for each supported active group or event role.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -1308,13 +1308,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B65" s="26" t="str">
-        <x:v>v0.26.1</x:v>
+        <x:v>v0.27.1</x:v>
       </x:c>
       <x:c r="C65" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D65" s="26" t="str">
-        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
+        <x:v>Consolidates the Coaching tab's access summary into one card per referee coach, with all assigned game access listed inside that card.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -1322,13 +1322,13 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B66" s="26" t="str">
-        <x:v>v0.26.0</x:v>
+        <x:v>v0.27.0</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D66" s="26" t="str">
-        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
+        <x:v>Separates schedule date, filters, and sorting controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -1336,41 +1336,41 @@
         <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B67" s="26" t="str">
-        <x:v>v0.25.3</x:v>
+        <x:v>v0.26.1</x:v>
       </x:c>
       <x:c r="C67" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D67" s="26" t="str">
-        <x:v>Filters the officials directory by one or more group roles.</x:v>
+        <x:v>Locks background scrolling while the official schedule modal scrolls.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B68" s="26" t="str">
-        <x:v>v0.25.2</x:v>
+        <x:v>v0.26.0</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D68" s="26" t="str">
-        <x:v>Updated the platform for the v0.25.2 release.</x:v>
+        <x:v>Keeps authentication private and makes shared filters mobile friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="25" t="n">
-        <x:v>46252.5</x:v>
+        <x:v>46253.5</x:v>
       </x:c>
       <x:c r="B69" s="26" t="str">
-        <x:v>v0.25.1</x:v>
+        <x:v>v0.25.3</x:v>
       </x:c>
       <x:c r="C69" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D69" s="26" t="str">
-        <x:v>Filters coaching games by venue or site.</x:v>
+        <x:v>Filters the officials directory by one or more group roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -1378,13 +1378,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B70" s="26" t="str">
-        <x:v>v0.25.0</x:v>
+        <x:v>v0.25.2</x:v>
       </x:c>
       <x:c r="C70" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D70" s="26" t="str">
-        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
+        <x:v>Updated the platform for the v0.25.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -1392,13 +1392,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B71" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.25.1</x:v>
       </x:c>
       <x:c r="C71" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D71" s="26" t="str">
-        <x:v>Guide.</x:v>
+        <x:v>Filters coaching games by venue or site.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -1406,13 +1406,13 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B72" s="26" t="str">
-        <x:v>v0.24.0</x:v>
+        <x:v>v0.25.0</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D72" s="26" t="str">
-        <x:v>Securely copies selected officials into another managed group.</x:v>
+        <x:v>Upgrades assignment board grouping and Site Supervisor schedules.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -1420,41 +1420,41 @@
         <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B73" s="26" t="str">
-        <x:v>v0.23.2</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C73" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D73" s="26" t="str">
-        <x:v>Updated the platform for the v0.23.2 release.</x:v>
+        <x:v>Guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
       <x:c r="A74" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B74" s="26" t="str">
-        <x:v>v0.23.1</x:v>
+        <x:v>v0.24.0</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D74" s="26" t="str">
-        <x:v>Retires the secondary email before an official merge claims it.</x:v>
+        <x:v>Securely copies selected officials into another managed group.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="25" t="n">
-        <x:v>46248.5</x:v>
+        <x:v>46252.5</x:v>
       </x:c>
       <x:c r="B75" s="26" t="str">
-        <x:v>v0.23.0</x:v>
+        <x:v>v0.23.2</x:v>
       </x:c>
       <x:c r="C75" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D75" s="26" t="str">
-        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
+        <x:v>Updated the platform for the v0.23.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -1462,13 +1462,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B76" s="26" t="str">
-        <x:v>v0.22.0</x:v>
+        <x:v>v0.23.1</x:v>
       </x:c>
       <x:c r="C76" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D76" s="26" t="str">
-        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
+        <x:v>Retires the secondary email before an official merge claims it.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -1476,13 +1476,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B77" s="26" t="str">
-        <x:v>v0.21.9</x:v>
+        <x:v>v0.23.0</x:v>
       </x:c>
       <x:c r="C77" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D77" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.9 release.</x:v>
+        <x:v>Scopes Site Supervisor operations and tracks posted schedule corrections.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -1490,13 +1490,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B78" s="26" t="str">
-        <x:v>v0.21.8</x:v>
+        <x:v>v0.22.0</x:v>
       </x:c>
       <x:c r="C78" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D78" s="26" t="str">
-        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
+        <x:v>Event schedules support reusable filters, ordered sorting, and Excel or PDF exports.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -1504,13 +1504,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B79" s="26" t="str">
-        <x:v>v0.21.7</x:v>
+        <x:v>v0.21.9</x:v>
       </x:c>
       <x:c r="C79" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D79" s="26" t="str">
-        <x:v>Updated the platform for the v0.21.7 release.</x:v>
+        <x:v>Updated the platform for the v0.21.9 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -1518,13 +1518,13 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B80" s="26" t="str">
-        <x:v>v0.21.6</x:v>
+        <x:v>v0.21.8</x:v>
       </x:c>
       <x:c r="C80" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D80" s="26" t="str">
-        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
+        <x:v>Filtered coaching schedules support checkbox selection and one-action bulk assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -1532,41 +1532,41 @@
         <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B81" s="26" t="str">
-        <x:v>v0.21.5</x:v>
+        <x:v>v0.21.7</x:v>
       </x:c>
       <x:c r="C81" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D81" s="26" t="str">
-        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
+        <x:v>Updated the platform for the v0.21.7 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B82" s="26" t="str">
-        <x:v>v0.21.3</x:v>
+        <x:v>v0.21.6</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D82" s="26" t="str">
-        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
+        <x:v>Linked and provisional official records can merge with last-name ordered selectors.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="25" t="n">
-        <x:v>46247.5</x:v>
+        <x:v>46248.5</x:v>
       </x:c>
       <x:c r="B83" s="26" t="str">
-        <x:v>v0.21.2</x:v>
+        <x:v>v0.21.5</x:v>
       </x:c>
       <x:c r="C83" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D83" s="26" t="str">
-        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
+        <x:v>Provisional coach activation waits for the linked user's public profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -1574,13 +1574,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B84" s="26" t="str">
-        <x:v>v0.21.1</x:v>
+        <x:v>v0.21.3</x:v>
       </x:c>
       <x:c r="C84" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D84" s="26" t="str">
-        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
+        <x:v>Complete game crews use referee, numbered assistant, fourth-official order everywhere.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -1588,13 +1588,13 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B85" s="26" t="str">
-        <x:v>v0.20.1</x:v>
+        <x:v>v0.21.2</x:v>
       </x:c>
       <x:c r="C85" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D85" s="26" t="str">
-        <x:v>Event insert returning rls.</x:v>
+        <x:v>Schedule rating buttons follow game-level and full-event coaching scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -1602,83 +1602,83 @@
         <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B86" s="26" t="str">
-        <x:v>v0.20.0</x:v>
+        <x:v>v0.21.1</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D86" s="26" t="str">
-        <x:v>Updated the platform for the v0.20.0 release.</x:v>
+        <x:v>Provisional referee coaches can be assigned before account creation.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B87" s="26" t="str">
-        <x:v>v0.19.2</x:v>
+        <x:v>v0.20.1</x:v>
       </x:c>
       <x:c r="C87" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D87" s="26" t="str">
-        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
+        <x:v>Event insert returning rls.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="25" t="n">
-        <x:v>46242.5</x:v>
+        <x:v>46247.5</x:v>
       </x:c>
       <x:c r="B88" s="26" t="str">
-        <x:v>v0.19.1</x:v>
+        <x:v>v0.20.0</x:v>
       </x:c>
       <x:c r="C88" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D88" s="26" t="str">
-        <x:v>External check in arrival options.</x:v>
+        <x:v>Updated the platform for the v0.20.0 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
       <x:c r="A89" s="25" t="n">
-        <x:v>46241.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B89" s="26" t="str">
-        <x:v>v0.19.0</x:v>
+        <x:v>v0.19.2</x:v>
       </x:c>
       <x:c r="C89" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D89" s="26" t="str">
-        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
+        <x:v>Mobile header and administrative context no longer overlap a persistent event bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
       <x:c r="A90" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46242.5</x:v>
       </x:c>
       <x:c r="B90" s="26" t="str">
-        <x:v>v0.18.1</x:v>
+        <x:v>v0.19.1</x:v>
       </x:c>
       <x:c r="C90" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D90" s="26" t="str">
-        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
+        <x:v>External check in arrival options.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
       <x:c r="A91" s="25" t="n">
-        <x:v>46240.5</x:v>
+        <x:v>46241.5</x:v>
       </x:c>
       <x:c r="B91" s="26" t="str">
-        <x:v>v0.18.0</x:v>
+        <x:v>v0.19.0</x:v>
       </x:c>
       <x:c r="C91" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D91" s="26" t="str">
-        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
+        <x:v>External check-in supports configurable identity, messages, links, and two-stage failures.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -1686,41 +1686,41 @@
         <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B92" s="26" t="str">
-        <x:v>v0.17.0</x:v>
+        <x:v>v0.18.1</x:v>
       </x:c>
       <x:c r="C92" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D92" s="26" t="str">
-        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
+        <x:v>Account merge review supports field-by-field profile resolution.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
       <x:c r="A93" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B93" s="26" t="str">
-        <x:v>v0.16.0</x:v>
+        <x:v>v0.18.0</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D93" s="26" t="str">
-        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
+        <x:v>User-facing groups replace organization terminology and Site Owner controls group features.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
       <x:c r="A94" s="25" t="n">
-        <x:v>46239.5</x:v>
+        <x:v>46240.5</x:v>
       </x:c>
       <x:c r="B94" s="26" t="str">
-        <x:v>v0.15.1</x:v>
+        <x:v>v0.17.0</x:v>
       </x:c>
       <x:c r="C94" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D94" s="26" t="str">
-        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
+        <x:v>Guest check-in matches an imported official and confirms the full daily schedule without an account.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -1728,13 +1728,13 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B95" s="26" t="str">
-        <x:v>v0.15.0</x:v>
+        <x:v>v0.16.0</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D95" s="26" t="str">
-        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
+        <x:v>Skills Eval uses position-specific categories and expanded written feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -1742,41 +1742,41 @@
         <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B96" s="26" t="str">
-        <x:v>v0.14.0</x:v>
+        <x:v>v0.15.1</x:v>
       </x:c>
       <x:c r="C96" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D96" s="26" t="str">
-        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
+        <x:v>Rating configuration requires an explicit reliable save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B97" s="26" t="str">
-        <x:v>v0.12.5</x:v>
+        <x:v>v0.15.0</x:v>
       </x:c>
       <x:c r="C97" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D97" s="26" t="str">
-        <x:v>Application header remains visible while scrolling.</x:v>
+        <x:v>Event settings respect organization feature ceilings and enforce disabled modules.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
       <x:c r="A98" s="25" t="n">
-        <x:v>46238.5</x:v>
+        <x:v>46239.5</x:v>
       </x:c>
       <x:c r="B98" s="26" t="str">
-        <x:v>v0.12.4</x:v>
+        <x:v>v0.14.0</x:v>
       </x:c>
       <x:c r="C98" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D98" s="26" t="str">
-        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
+        <x:v>Event types and private Rules of Competition documents are available throughout assigned-event views.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -1784,13 +1784,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B99" s="26" t="str">
-        <x:v>v0.12.3</x:v>
+        <x:v>v0.12.5</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D99" s="26" t="str">
-        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
+        <x:v>Application header remains visible while scrolling.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -1798,13 +1798,13 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B100" s="26" t="str">
-        <x:v>v0.12.2</x:v>
+        <x:v>v0.12.4</x:v>
       </x:c>
       <x:c r="C100" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D100" s="26" t="str">
-        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
+        <x:v>Event access can be staged for provisional officials and activates when accounts link.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -1812,41 +1812,41 @@
         <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B101" s="26" t="str">
-        <x:v>v0.12.0</x:v>
+        <x:v>v0.12.3</x:v>
       </x:c>
       <x:c r="C101" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D101" s="26" t="str">
-        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
+        <x:v>Users can lock personal contact fields without locking organization or event permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
       <x:c r="A102" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B102" s="26" t="str">
-        <x:v>v0.11.2</x:v>
+        <x:v>v0.12.2</x:v>
       </x:c>
       <x:c r="C102" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D102" s="26" t="str">
-        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
+        <x:v>Active-event permissions are integrated into the official editor and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
       <x:c r="A103" s="25" t="n">
-        <x:v>46237.5</x:v>
+        <x:v>46238.5</x:v>
       </x:c>
       <x:c r="B103" s="26" t="str">
-        <x:v>v0.11.1</x:v>
+        <x:v>v0.12.0</x:v>
       </x:c>
       <x:c r="C103" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D103" s="26" t="str">
-        <x:v>Updated the platform for the v0.11.1 release.</x:v>
+        <x:v>Prevents profile self-escalation and enforces the organization role hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -1854,41 +1854,41 @@
         <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B104" s="26" t="str">
-        <x:v>v0.11.0</x:v>
+        <x:v>v0.11.2</x:v>
       </x:c>
       <x:c r="C104" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D104" s="26" t="str">
-        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
+        <x:v>Calendar colors support combined presentation modes and custom dropdowns close outside.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
       <x:c r="A105" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B105" s="26" t="str">
-        <x:v>v0.10.4</x:v>
+        <x:v>v0.11.1</x:v>
       </x:c>
       <x:c r="C105" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D105" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.4 release.</x:v>
+        <x:v>Updated the platform for the v0.11.1 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
       <x:c r="A106" s="25" t="n">
-        <x:v>46234.5</x:v>
+        <x:v>46237.5</x:v>
       </x:c>
       <x:c r="B106" s="26" t="str">
-        <x:v>v0.10.3</x:v>
+        <x:v>v0.11.0</x:v>
       </x:c>
       <x:c r="C106" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D106" s="26" t="str">
-        <x:v>Unified assignment filter context.</x:v>
+        <x:v>Adds color-coded date-filtered assignments and reusable session filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -1896,13 +1896,13 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B107" s="26" t="str">
-        <x:v>v0.10.2</x:v>
+        <x:v>v0.10.4</x:v>
       </x:c>
       <x:c r="C107" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D107" s="26" t="str">
-        <x:v>Updated the platform for the v0.10.2 release.</x:v>
+        <x:v>Updated the platform for the v0.10.4 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -1910,32 +1910,32 @@
         <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B108" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.3</x:v>
       </x:c>
       <x:c r="C108" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D108" s="26" t="str">
-        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
+        <x:v>Unified assignment filter context.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
       <x:c r="A109" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B109" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.10.2</x:v>
       </x:c>
       <x:c r="C109" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D109" s="26" t="str">
-        <x:v>Add assignment import policy inheritance.</x:v>
+        <x:v>Updated the platform for the v0.10.2 release.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
       <x:c r="A110" s="25" t="n">
-        <x:v>46233.5</x:v>
+        <x:v>46234.5</x:v>
       </x:c>
       <x:c r="B110" s="26" t="str">
         <x:v>Early build</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D110" s="26" t="str">
-        <x:v>Document assignment import and notification behavior.</x:v>
+        <x:v>Sessions refresh automatically and non-auth failures preserve login.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -1955,10 +1955,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C111" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D111" s="26" t="str">
-        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
+        <x:v>Add assignment import policy inheritance.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -1972,7 +1972,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D112" s="26" t="str">
-        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
+        <x:v>Document assignment import and notification behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -1986,7 +1986,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D113" s="26" t="str">
-        <x:v>Rating history identifies each rating submitter.</x:v>
+        <x:v>Public ratings support approval, unread referee badges, and retained deletion.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -2000,7 +2000,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D114" s="26" t="str">
-        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
+        <x:v>Ratings can be filtered and sorted by score with match crews in position order.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -2014,7 +2014,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D115" s="26" t="str">
-        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
+        <x:v>Rating history identifies each rating submitter.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -2028,7 +2028,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D116" s="26" t="str">
-        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
+        <x:v>Full-game ratings use one collapsible horizontal official row.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -2042,7 +2042,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D117" s="26" t="str">
-        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
+        <x:v>Rating selection checkbox uses a compact column beside rating information.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -2056,7 +2056,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D118" s="26" t="str">
-        <x:v>Page refresh restores the current view and active event.</x:v>
+        <x:v>Role help uses an isolated single-column scrollable dialog.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -2070,7 +2070,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D119" s="26" t="str">
-        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
+        <x:v>Event members and assigned referee coaches load into officials and check-in rosters.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -2084,7 +2084,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D120" s="26" t="str">
-        <x:v>Align archived event actions.</x:v>
+        <x:v>Page refresh restores the current view and active event.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -2098,7 +2098,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D121" s="26" t="str">
-        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
+        <x:v>Organization administrators can upload a logo for the active organization bar.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -2112,7 +2112,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D122" s="26" t="str">
-        <x:v>Sort officials by last name.</x:v>
+        <x:v>Align archived event actions.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -2126,7 +2126,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D123" s="26" t="str">
-        <x:v>Official directory sorts populated values before missing values.</x:v>
+        <x:v>Organization admins can review audited actions and copy one officials join link.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -2137,10 +2137,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C124" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D124" s="26" t="str">
-        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
+        <x:v>Sort officials by last name.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -2154,7 +2154,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D125" s="26" t="str">
-        <x:v>Archived event selection and restore control share one compact row.</x:v>
+        <x:v>Official directory sorts populated values before missing values.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -2165,10 +2165,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C126" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D126" s="26" t="str">
-        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
+        <x:v>Site owner and delegated administrator access follow protected removal hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -2182,7 +2182,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D127" s="26" t="str">
-        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
+        <x:v>Archived event selection and restore control share one compact row.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -2193,10 +2193,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C128" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D128" s="26" t="str">
-        <x:v>Fix ratings history migration syntax.</x:v>
+        <x:v>Responsive shell and header remain contained within the viewport.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -2210,7 +2210,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D129" s="26" t="str">
-        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
+        <x:v>Failed dashboard startup returns to login with a session-expired notice.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -2221,10 +2221,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C130" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D130" s="26" t="str">
-        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
+        <x:v>Fix ratings history migration syntax.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -2238,7 +2238,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D131" s="26" t="str">
-        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
+        <x:v>Administrators can bulk manage officials, ratings, and events.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -2252,12 +2252,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D132" s="26" t="str">
-        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
+        <x:v>Ratings history survives event archiving and supports grouped export and lifecycle controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
       <x:c r="A133" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B133" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2266,12 +2266,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D133" s="26" t="str">
-        <x:v>Refine organization capability hierarchy.</x:v>
+        <x:v>Authorized event staff can manually or automatically archive events.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
       <x:c r="A134" s="25" t="n">
-        <x:v>46232.5</x:v>
+        <x:v>46233.5</x:v>
       </x:c>
       <x:c r="B134" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2280,7 +2280,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D134" s="26" t="str">
-        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
+        <x:v>Organization admins can review audited actions and manage Join Group links.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -2294,7 +2294,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D135" s="26" t="str">
-        <x:v>Order first assignments by time and field.</x:v>
+        <x:v>Refine organization capability hierarchy.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -2308,7 +2308,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D136" s="26" t="str">
-        <x:v>Stack check-in schedule cards vertically.</x:v>
+        <x:v>Roadmap records organization capability and check-in method controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -2322,7 +2322,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D137" s="26" t="str">
-        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
+        <x:v>Order first assignments by time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -2333,10 +2333,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C138" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D138" s="26" t="str">
-        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
+        <x:v>Stack check-in schedule cards vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2350,7 +2350,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D139" s="26" t="str">
-        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
+        <x:v>Check-in schedule modal uses one-column game cards with positions and crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -2361,10 +2361,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C140" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D140" s="26" t="str">
-        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
+        <x:v>Authorized administrators can create an event without importing a schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -2378,7 +2378,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D141" s="26" t="str">
-        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
+        <x:v>Check-in roster sorts by first assignment field instead of site.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -2392,7 +2392,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D142" s="26" t="str">
-        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
+        <x:v>Site owner appearance supports secure drag-and-drop logo uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -2406,7 +2406,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D143" s="26" t="str">
-        <x:v>Open ratings modal from page button.</x:v>
+        <x:v>Officials directory shows authorized submitted-rating averages.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -2420,7 +2420,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D144" s="26" t="str">
-        <x:v>Improve ratings referee and date filters.</x:v>
+        <x:v>Rating authors can reopen and edit an entire game crew.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -2434,7 +2434,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D145" s="26" t="str">
-        <x:v>Normalize dashboard label capitalization.</x:v>
+        <x:v>Open ratings modal from page button.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -2448,7 +2448,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D146" s="26" t="str">
-        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
+        <x:v>Improve ratings referee and date filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -2462,7 +2462,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D147" s="26" t="str">
-        <x:v>Rating drafts are readable only by their creator.</x:v>
+        <x:v>Normalize dashboard label capitalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -2476,7 +2476,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D148" s="26" t="str">
-        <x:v>Compact basic rating cards.</x:v>
+        <x:v>Administrative dashboard shows today's check-in progress and role only.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -2487,10 +2487,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C149" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D149" s="26" t="str">
-        <x:v>Convert rating filters to dropdowns.</x:v>
+        <x:v>Rating drafts are readable only by their creator.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -2504,7 +2504,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D150" s="26" t="str">
-        <x:v>Redesign role help navigation guide.</x:v>
+        <x:v>Compact basic rating cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -2515,10 +2515,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C151" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D151" s="26" t="str">
-        <x:v>Unify crew rating modal flow.</x:v>
+        <x:v>Convert rating filters to dropdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -2532,7 +2532,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D152" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
+        <x:v>Redesign role help navigation guide.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -2546,7 +2546,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D153" s="26" t="str">
-        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
+        <x:v>Unify crew rating modal flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -2560,7 +2560,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D154" s="26" t="str">
-        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -2574,7 +2574,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D155" s="26" t="str">
-        <x:v>All users have active-group role-aware help.</x:v>
+        <x:v>Ratings history supports multi-select filters independent of sorting.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -2585,10 +2585,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C156" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D156" s="26" t="str">
-        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
+        <x:v>Assessment upsert uses a non-partial matching unique index.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -2602,7 +2602,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D157" s="26" t="str">
-        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
+        <x:v>All users have active-group role-aware help.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -2613,10 +2613,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C158" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D158" s="26" t="str">
-        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
+        <x:v>Rate Crew buttons and rating choices exclude HQ and operational games.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -2630,7 +2630,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D159" s="26" t="str">
-        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
+        <x:v>Administrative roster supports immediate manual check-in and undo.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -2644,7 +2644,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D160" s="26" t="str">
-        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
+        <x:v>Rating configuration requires an explicit save and Basic Eval stores notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -2658,7 +2658,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D161" s="26" t="str">
-        <x:v>Coaching administration is hidden from referee coaches.</x:v>
+        <x:v>Check-in roster names open a complete daily schedule modal.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -2669,10 +2669,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C162" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D162" s="26" t="str">
-        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
+        <x:v>Assigned referee coaches participate in daily check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -2686,7 +2686,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D163" s="26" t="str">
-        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
+        <x:v>Coaching administration is hidden from referee coaches.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -2697,10 +2697,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C164" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D164" s="26" t="str">
-        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
+        <x:v>Coach-only schedules exclude operational and HQ locations.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -2714,7 +2714,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D165" s="26" t="str">
-        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
+        <x:v>Ratings game options are concise and mobile controls stay within the workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -2728,7 +2728,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D166" s="26" t="str">
-        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
+        <x:v>Coach schedule lists crews and opens the selected game's rating workspace.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -2742,7 +2742,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D167" s="26" t="str">
-        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
+        <x:v>Top bar has an accessible page refresh button beside the account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -2756,7 +2756,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D168" s="26" t="str">
-        <x:v>Official editor uses structured fields and role cards.</x:v>
+        <x:v>Daily check-in uses the camera scanner and hides it after check-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -2770,7 +2770,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D169" s="26" t="str">
-        <x:v>Officials directory displays all organization roles.</x:v>
+        <x:v>Event access is discoverable and site-owner access is locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -2784,7 +2784,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D170" s="26" t="str">
-        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
+        <x:v>Official editor uses structured fields and role cards.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -2798,12 +2798,12 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D171" s="26" t="str">
-        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
+        <x:v>Officials directory displays all organization roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
       <x:c r="A172" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B172" s="26" t="str">
         <x:v>Early build</x:v>
@@ -2812,21 +2812,21 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D172" s="26" t="str">
-        <x:v>Align assignment board crew tiles.</x:v>
+        <x:v>Assignr import supports drag and drop with CSV validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
       <x:c r="A173" s="25" t="n">
-        <x:v>46229.5</x:v>
+        <x:v>46232.5</x:v>
       </x:c>
       <x:c r="B173" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C173" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D173" s="26" t="str">
-        <x:v>Add check-in roster sorting and filters.</x:v>
+        <x:v>Account merge migration transfers operational records and audits the merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -2840,7 +2840,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D174" s="26" t="str">
-        <x:v>Auto-refresh live check-in attendance.</x:v>
+        <x:v>Align assignment board crew tiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -2851,10 +2851,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C175" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D175" s="26" t="str">
-        <x:v>Fix daily check-in upsert constraint.</x:v>
+        <x:v>Add check-in roster sorting and filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -2865,10 +2865,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C176" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D176" s="26" t="str">
-        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
+        <x:v>Auto-refresh live check-in attendance.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -2879,10 +2879,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C177" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D177" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Fix daily check-in upsert constraint.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -2893,10 +2893,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C178" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D178" s="26" t="str">
-        <x:v>Sort game times chronologically.</x:v>
+        <x:v>Enable QR check-in for dual-role staff accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -2910,7 +2910,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D179" s="26" t="str">
-        <x:v>Support private owner records and multiple official roles.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -2921,10 +2921,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C180" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D180" s="26" t="str">
-        <x:v>Add official record editing.</x:v>
+        <x:v>Sort game times chronologically.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -2938,7 +2938,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D181" s="26" t="str">
-        <x:v>Title-case dashboard navigation labels.</x:v>
+        <x:v>Support private owner records and multiple official roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -2949,10 +2949,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C182" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D182" s="26" t="str">
-        <x:v>Rename referee ratings tab to My Evals.</x:v>
+        <x:v>Add official record editing.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -2963,10 +2963,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C183" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D183" s="26" t="str">
-        <x:v>Fix recursive game privacy policy.</x:v>
+        <x:v>Title-case dashboard navigation labels.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -2977,10 +2977,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C184" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D184" s="26" t="str">
-        <x:v>Restrict referee schedules and require QR scanning.</x:v>
+        <x:v>Rename referee ratings tab to My Evals.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -2988,13 +2988,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B185" s="26" t="str">
-        <x:v>v0.4.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C185" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D185" s="26" t="str">
-        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
+        <x:v>Fix recursive game privacy policy.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -3008,7 +3008,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D186" s="26" t="str">
-        <x:v>Interpret imported game times in event timezone.</x:v>
+        <x:v>Restrict referee schedules and require QR scanning.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -3016,13 +3016,13 @@
         <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B187" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.4.0</x:v>
       </x:c>
       <x:c r="C187" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D187" s="26" t="str">
-        <x:v>Activate intended roles when officials claim accounts.</x:v>
+        <x:v>Bump Law18Ref to version 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -3033,10 +3033,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C188" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D188" s="26" t="str">
-        <x:v>Add sortable operations and scoped event roles.</x:v>
+        <x:v>Interpret imported game times in event timezone.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -3047,10 +3047,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C189" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D189" s="26" t="str">
-        <x:v>Add organization and event position aliases.</x:v>
+        <x:v>Activate intended roles when officials claim accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -3061,10 +3061,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C190" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D190" s="26" t="str">
-        <x:v>Preserve Assignr assignment position titles.</x:v>
+        <x:v>Add sortable operations and scoped event roles.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -3075,10 +3075,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C191" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D191" s="26" t="str">
-        <x:v>Fix scoped import job permissions.</x:v>
+        <x:v>Add organization and event position aliases.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -3089,10 +3089,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C192" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D192" s="26" t="str">
-        <x:v>Add official account invitation email draft.</x:v>
+        <x:v>Preserve Assignr assignment position titles.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -3103,10 +3103,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C193" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D193" s="26" t="str">
-        <x:v>Document NFC and multi-site operations roadmap.</x:v>
+        <x:v>Fix scoped import job permissions.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -3117,10 +3117,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C194" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D194" s="26" t="str">
-        <x:v>Fix schedule timestamp formatting.</x:v>
+        <x:v>Add official account invitation email draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -3134,7 +3134,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D195" s="26" t="str">
-        <x:v>Show dates on game schedule.</x:v>
+        <x:v>Document NFC and multi-site operations roadmap.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -3145,10 +3145,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C196" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D196" s="26" t="str">
-        <x:v>Expand appearance themes and scheduling controls.</x:v>
+        <x:v>Fix schedule timestamp formatting.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -3159,10 +3159,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C197" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D197" s="26" t="str">
-        <x:v>Add configurable crew ratings.</x:v>
+        <x:v>Show dates on game schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -3173,10 +3173,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C198" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D198" s="26" t="str">
-        <x:v>Add reusable appearance themes.</x:v>
+        <x:v>Expand appearance themes and scheduling controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -3190,7 +3190,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D199" s="26" t="str">
-        <x:v>Add organization context and manual records.</x:v>
+        <x:v>Add configurable crew ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -3201,10 +3201,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C200" s="26" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D200" s="26" t="str">
-        <x:v>Replace Georgia display font with Inter.</x:v>
+        <x:v>Add reusable appearance themes.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -3218,63 +3218,63 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D201" s="26" t="str">
-        <x:v>Add site owner organization management.</x:v>
+        <x:v>Add organization context and manual records.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
       <x:c r="A202" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B202" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C202" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D202" s="26" t="str">
-        <x:v>Fix recursive event access policies.</x:v>
+        <x:v>Replace Georgia display font with Inter.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
       <x:c r="A203" s="25" t="n">
-        <x:v>46228.5</x:v>
+        <x:v>46229.5</x:v>
       </x:c>
       <x:c r="B203" s="26" t="str">
-        <x:v>v0.2.0</x:v>
+        <x:v>Early build</x:v>
       </x:c>
       <x:c r="C203" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D203" s="26" t="str">
-        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
+        <x:v>Add site owner organization management.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
       <x:c r="A204" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B204" s="26" t="str">
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C204" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D204" s="26" t="str">
-        <x:v>Remove footer slogan.</x:v>
+        <x:v>Fix recursive event access policies.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
       <x:c r="A205" s="25" t="n">
-        <x:v>46227.5</x:v>
+        <x:v>46228.5</x:v>
       </x:c>
       <x:c r="B205" s="26" t="str">
-        <x:v>Early build</x:v>
+        <x:v>v0.2.0</x:v>
       </x:c>
       <x:c r="C205" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D205" s="26" t="str">
-        <x:v>Add account membership controls.</x:v>
+        <x:v>Launch Law18Ref tournament operations v0.2.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -3285,10 +3285,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C206" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D206" s="26" t="str">
-        <x:v>Add dashboard and account menu.</x:v>
+        <x:v>Remove footer slogan.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -3302,7 +3302,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D207" s="26" t="str">
-        <x:v>Add selected Law18Ref logo.</x:v>
+        <x:v>Add account membership controls.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -3313,10 +3313,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C208" s="28" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D208" s="28" t="str">
-        <x:v>Apply navy and berry site branding.</x:v>
+        <x:v>Add dashboard and account menu.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -3327,10 +3327,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C209" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D209" t="str">
-        <x:v>Update database comments for new brand.</x:v>
+        <x:v>Add selected Law18Ref logo.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -3344,7 +3344,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D210" t="str">
-        <x:v>Update tests for Law18Referee Management.</x:v>
+        <x:v>Apply navy and berry site branding.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3358,7 +3358,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D211" t="str">
-        <x:v>Document Law18Referee Management rebrand.</x:v>
+        <x:v>Update database comments for new brand.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3369,10 +3369,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C212" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D212" t="str">
-        <x:v>Add Law18Referee Management brand assets.</x:v>
+        <x:v>Update tests for Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3383,10 +3383,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C213" t="str">
-        <x:v>Changed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D213" t="str">
-        <x:v>Rename platform to Law18Referee Management.</x:v>
+        <x:v>Document Law18Referee Management rebrand.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3397,10 +3397,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C214" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D214" t="str">
-        <x:v>Test repeat schedule imports.</x:v>
+        <x:v>Add Law18Referee Management brand assets.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -3411,10 +3411,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C215" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Changed</x:v>
       </x:c>
       <x:c r="D215" t="str">
-        <x:v>Document repeat schedule imports.</x:v>
+        <x:v>Rename platform to Law18Referee Management.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -3428,7 +3428,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D216" t="str">
-        <x:v>Support staged schedule imports.</x:v>
+        <x:v>Test repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -3442,7 +3442,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D217" t="str">
-        <x:v>Grant authenticated access to RLS tables.</x:v>
+        <x:v>Document repeat schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -3456,7 +3456,7 @@
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D218" t="str">
-        <x:v>Document small-tournament pilot.</x:v>
+        <x:v>Support staged schedule imports.</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -3467,10 +3467,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C219" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D219" t="str">
-        <x:v>Add small-tournament Supabase migration.</x:v>
+        <x:v>Grant authenticated access to RLS tables.</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -3481,10 +3481,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C220" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D220" t="str">
-        <x:v>Add installable mobile RefHQ experience.</x:v>
+        <x:v>Document small-tournament pilot.</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
@@ -3498,7 +3498,7 @@
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D221" t="str">
-        <x:v>Build small-tournament pilot workflows.</x:v>
+        <x:v>Add small-tournament Supabase migration.</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -3509,10 +3509,10 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C222" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D222" t="str">
-        <x:v>Require Supabase login for RefHQ.</x:v>
+        <x:v>Add installable mobile RefHQ experience.</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
@@ -3523,17 +3523,25 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C223" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D223" t="str">
-        <x:v>Style Supabase sign-in.</x:v>
+        <x:v>Build small-tournament pilot workflows.</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" t="str"/>
-      <x:c r="B224" t="str"/>
-      <x:c r="C224" t="str"/>
-      <x:c r="D224" t="str"/>
+      <x:c r="A224" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B224" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C224" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D224" t="str">
+        <x:v>Require Supabase login for RefHQ.</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" t="n">
@@ -3543,9 +3551,29 @@
         <x:v>Early build</x:v>
       </x:c>
       <x:c r="C225" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D225" t="str">
+        <x:v>Style Supabase sign-in.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" t="str"/>
+      <x:c r="B226" t="str"/>
+      <x:c r="C226" t="str"/>
+      <x:c r="D226" t="str"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" t="n">
+        <x:v>46227.5</x:v>
+      </x:c>
+      <x:c r="B227" t="str">
+        <x:v>Early build</x:v>
+      </x:c>
+      <x:c r="C227" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D227" t="str">
         <x:v>Add Supabase authentication client.</x:v>
       </x:c>
     </x:row>
@@ -3561,7 +3589,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90476a34b27d4e0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re27382ef57c94622"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/Law18Ref_Update_History.xlsx
+++ b/docs/Law18Ref_Update_History.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="R812d5787f27d407c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Summaries" sheetId="1" r:id="Rac807ca6c88547a6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D225" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UpdateSummaryTable" displayName="UpdateSummaryTable" ref="A4:D226" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Version"/>
@@ -433,10 +433,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Current version: v0.39.1 · Brief descriptions of additions, removals, fixes, and updates</x:v>
+        <x:v>Current version: v0.39.2 · Brief descriptions of additions, removals, fixes, and updates</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>v0.39.1</x:v>
+        <x:v>v0.39.2</x:v>
       </x:c>
       <x:c r="C2" t="str"/>
       <x:c r="D2" t="str">
@@ -468,13 +468,13 @@
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="B5" s="32" t="str">
-        <x:v>v0.39.1</x:v>
+        <x:v>v0.39.2</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Added an optional atomic crew-with-game mode to game-detail swaps, allowing complete staffed crews to remain with their matchups when games switch schedule slots while preserving ratings and source identifiers.</x:v>
+        <x:v>Made Assignment Board matchups open the permission-gated Game Info editor and changed the editor to a compact single-column vertical field layout across desktop and mobile views.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -482,13 +482,13 @@
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="B6" s="33" t="str">
-        <x:v>v0.39.0</x:v>
+        <x:v>v0.39.1</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D6" s="26" t="str">
-        <x:v>Added permission-gated game information editing and atomic swapping of matchup and competition details between filtered schedule slots while preserving crews, ratings, source identifiers, and unchanged slot time and field.</x:v>
+        <x:v>Added an optional atomic crew-with-game mode to game-detail swaps, allowing complete staffed crews to remain with their matchups when games switch schedule slots while preserving ratings and source identifiers.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -496,13 +496,13 @@
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="B7" s="33" t="str">
-        <x:v>v0.38.3</x:v>
+        <x:v>v0.39.0</x:v>
       </x:c>
       <x:c r="C7" s="26" t="str">
         <x:v>Added</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>Added an atomic full-crew swap option for two filtered Schedule games with matching staffed crew sizes, preserving each game's position structure and imported crew order while leaving ratings unchanged.</x:v>
+        <x:v>Added permission-gated game information editing and atomic swapping of matchup and competition details between filtered schedule slots while preserving crews, ratings, source identifiers, and unchanged slot time and field.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -510,13 +510,13 @@
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="B8" s="33" t="str">
-        <x:v>v0.38.2</x:v>
+        <x:v>v0.38.3</x:v>
       </x:c>
       <x:c r="C8" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D8" s="26" t="str">
-        <x:v>Limited the Schedule assignment-swap game selectors to games matching the Schedule's currently active filters.</x:v>
+        <x:v>Added an atomic full-crew swap option for two filtered Schedule games with matching staffed crew sizes, preserving each game's position structure and imported crew order while leaving ratings unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -524,27 +524,27 @@
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="B9" s="33" t="str">
+        <x:v>v0.38.2</x:v>
+      </x:c>
+      <x:c r="C9" s="26" t="str">
+        <x:v>Updated</x:v>
+      </x:c>
+      <x:c r="D9" s="26" t="str">
+        <x:v>Limited the Schedule assignment-swap game selectors to games matching the Schedule's currently active filters.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="25" t="str">
+        <x:v>2026-08-23</x:v>
+      </x:c>
+      <x:c r="B10" s="33" t="str">
         <x:v>v0.38.1</x:v>
       </x:c>
-      <x:c r="C9" s="26" t="str">
-        <x:v>Added</x:v>
-      </x:c>
-      <x:c r="D9" s="26" t="str">
+      <x:c r="C10" s="26" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D10" s="26" t="str">
         <x:v>Added an atomic schedule tool to swap two staffed assignments between games in the same event while preserving each game's position slot; applies game-management permissions, leaves ratings unchanged, records an audit entry, sends no notification, and marks both games as updated.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="25" t="n">
-        <x:v>46256.666666666664</x:v>
-      </x:c>
-      <x:c r="B10" s="26" t="str">
-        <x:v>v0.38.0</x:v>
-      </x:c>
-      <x:c r="C10" s="26" t="str">
-        <x:v>Updated</x:v>
-      </x:c>
-      <x:c r="D10" s="26" t="str">
-        <x:v>Separated first and last names in referee and account records; kept combined-name displays; changed referee, coach, merge, rating, filter, and assignment selectors to last-name sorting with Last, First labels; added import/export support and safe backfill synchronization for existing records.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -552,13 +552,13 @@
         <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B11" s="26" t="str">
-        <x:v>v0.37.1</x:v>
+        <x:v>v0.38.0</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D11" s="26" t="str">
-        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
+        <x:v>Separated first and last names in referee and account records; kept combined-name displays; changed referee, coach, merge, rating, filter, and assignment selectors to last-name sorting with Last, First labels; added import/export support and safe backfill synchronization for existing records.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -566,27 +566,27 @@
         <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
-        <x:v>v0.37.0</x:v>
+        <x:v>v0.37.1</x:v>
       </x:c>
       <x:c r="C12" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
+        <x:v>Split the post-event summary schedule into a separate dated worksheet for every game date, making daily assignments easier to print, distribute, and review.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="25" t="n">
-        <x:v>46256.833333333336</x:v>
+        <x:v>46256.666666666664</x:v>
       </x:c>
       <x:c r="B13" s="26" t="str">
-        <x:v>v0.36.0</x:v>
+        <x:v>v0.37.0</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D13" s="26" t="str">
-        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
+        <x:v>Added a post-event Excel summary covering daily event metrics, the full assigned schedule, grouped and individual ratings, official contact and rating summaries, and daily check-in details.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -594,139 +594,139 @@
         <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>v0.35.5</x:v>
+        <x:v>v0.36.0</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D14" s="26" t="str">
-        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
+        <x:v>Added first-assignment-time and changed-assignment filters, last-name assignment lists, phone search, detailed rating summaries, collapse controls, admin rating access, and mobile rating/navigation fixes.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A15" s="25" t="n">
-        <x:v>46256.625</x:v>
+        <x:v>46256.833333333336</x:v>
       </x:c>
       <x:c r="B15" s="26" t="str">
-        <x:v>v0.35.4</x:v>
+        <x:v>v0.35.5</x:v>
       </x:c>
       <x:c r="C15" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D15" s="26" t="str">
-        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
+        <x:v>Authorized staff can remove all coaching access for one coach or bulk-remove a selected coach from selected/filtered games while preserving access to unselected games.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="25" t="n">
-        <x:v>46256.604166666664</x:v>
+        <x:v>46256.625</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>v0.35.3</x:v>
+        <x:v>v0.35.4</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D16" s="26" t="str">
-        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
+        <x:v>Changed games now remain orange and labeled Updated throughout every Assignment Board view until their schedule-change marker is confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="25" t="n">
-        <x:v>46256.583333333336</x:v>
+        <x:v>46256.604166666664</x:v>
       </x:c>
       <x:c r="B17" s="26" t="str">
-        <x:v>v0.35.2</x:v>
+        <x:v>v0.35.3</x:v>
       </x:c>
       <x:c r="C17" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D17" s="26" t="str">
-        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
+        <x:v>Expanded the Assignment Board grid toward full viewport dimensions and restored page scrolling when the grid reaches a vertical boundary.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A18" s="25" t="n">
-        <x:v>46256.541666666664</x:v>
+        <x:v>46256.583333333336</x:v>
       </x:c>
       <x:c r="B18" s="26" t="str">
-        <x:v>v0.35.1</x:v>
+        <x:v>v0.35.2</x:v>
       </x:c>
       <x:c r="C18" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D18" s="26" t="str">
-        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
+        <x:v>Assignment Board field headers and time headers now remain frozen while the grid scrolls horizontally or vertically.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="25" t="n">
-        <x:v>46255.75</x:v>
+        <x:v>46256.541666666664</x:v>
       </x:c>
       <x:c r="B19" s="26" t="str">
-        <x:v>v0.35.0</x:v>
+        <x:v>v0.35.1</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D19" s="26" t="str">
-        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
+        <x:v>Crew-rating saves now require database confirmation and wait for refreshed event data before reporting success or closing the form.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="25" t="n">
-        <x:v>46255.729166666664</x:v>
+        <x:v>46255.75</x:v>
       </x:c>
       <x:c r="B20" s="26" t="str">
-        <x:v>v0.34.5</x:v>
+        <x:v>v0.35.0</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D20" s="26" t="str">
-        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
+        <x:v>Schedule PDFs now use compact dynamic position columns, density and paper presets, abbreviated names, optional details, and optional group separators.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="25" t="n">
-        <x:v>46255.708333333336</x:v>
+        <x:v>46255.729166666664</x:v>
       </x:c>
       <x:c r="B21" s="26" t="str">
-        <x:v>v0.34.4</x:v>
+        <x:v>v0.34.5</x:v>
       </x:c>
       <x:c r="C21" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D21" s="26" t="str">
-        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
+        <x:v>Installed and reopened apps now check for newer deployments on startup, focus, visibility changes, and a short interval, then activate versioned caches and reload once into the latest release.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="25" t="n">
-        <x:v>46255.6875</x:v>
+        <x:v>46255.708333333336</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>v0.34.3</x:v>
+        <x:v>v0.34.4</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D22" s="26" t="str">
-        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
+        <x:v>Ratings export filenames now describe active filters with compact date ranges, event labels, abbreviated referee names, and selected criteria instead of the UTC export date.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="25" t="n">
-        <x:v>46255.666666666664</x:v>
+        <x:v>46255.6875</x:v>
       </x:c>
       <x:c r="B23" s="26" t="str">
-        <x:v>v0.34.2</x:v>
+        <x:v>v0.34.3</x:v>
       </x:c>
       <x:c r="C23" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D23" s="26" t="str">
-        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
+        <x:v>Ratings exports now sort deterministically by event and game, keeping multiple submissions for the same game in adjacent rows and ordering duplicates by submission time.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -734,13 +734,13 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B24" s="26" t="str">
-        <x:v>v0.34.1</x:v>
+        <x:v>v0.34.2</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>Fixed</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D24" s="26" t="str">
-        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
+        <x:v>Rating CSV exports omit Skills Eval-only columns when the filtered results contain only Basic Evals; Basic Eval notes remain included.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -748,27 +748,27 @@
         <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B25" s="26" t="str">
-        <x:v>v0.34.0</x:v>
+        <x:v>v0.34.1</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="D25" s="26" t="str">
-        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
+        <x:v>Restored the Ratings tab for users who have both Site Supervisor and Referee Coach access so their combined event capabilities remain available.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A26" s="25" t="n">
-        <x:v>46255.5</x:v>
+        <x:v>46255.666666666664</x:v>
       </x:c>
       <x:c r="B26" s="26" t="str">
-        <x:v>v0.33.0</x:v>
+        <x:v>v0.34.0</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D26" s="26" t="str">
-        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
+        <x:v>Made referee-coach rating history private to each author, added direct draft submission and status filtering, and expanded filtered exports with individual, grouped-game, duplicate-marked, and configurable summary formats.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -776,13 +776,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B27" s="26" t="str">
-        <x:v>v0.32.5</x:v>
+        <x:v>v0.33.0</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D27" s="26" t="str">
-        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
+        <x:v>Updated dashboard text and the browser favicon, added the Site Owner version display, and added controls to exclude ratings from averages while keeping them staff-visible and hidden from referees.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -790,13 +790,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B28" s="26" t="str">
-        <x:v>v0.32.4</x:v>
+        <x:v>v0.32.5</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D28" s="26" t="str">
-        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
+        <x:v>Adds a permission-gated Refresh Check-Ins button to the Assignment Board and Schedule.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -804,13 +804,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B29" s="26" t="str">
-        <x:v>v0.32.3</x:v>
+        <x:v>v0.32.4</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D29" s="26" t="str">
-        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
+        <x:v>Applies stable natural numeric field ordering across every Assignment Board view, including the Time and Field Grid.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -818,13 +818,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B30" s="26" t="str">
-        <x:v>v0.32.2</x:v>
+        <x:v>v0.32.3</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D30" s="26" t="str">
-        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
+        <x:v>Shows the deployed application version beside Help in the header for the Site Owner only.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -832,13 +832,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B31" s="26" t="str">
-        <x:v>v0.32.1</x:v>
+        <x:v>v0.32.2</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
         <x:v>Updated</x:v>
       </x:c>
       <x:c r="D31" s="26" t="str">
-        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
+        <x:v>Makes the official schedule popup a single continuous scrolling surface so contact details cannot cover or clip the first assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -846,13 +846,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B32" s="26" t="str">
-        <x:v>v0.32.0</x:v>
+        <x:v>v0.32.1</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>Removed / Restricted</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D32" s="26" t="str">
-        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
+        <x:v>Makes updated schedule imports idempotent for game crews.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -860,13 +860,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B33" s="26" t="str">
-        <x:v>v0.31.10</x:v>
+        <x:v>v0.32.0</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Removed / Restricted</x:v>
       </x:c>
       <x:c r="D33" s="26" t="str">
-        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
+        <x:v>Prevents games, groups, officials, or user profiles from cascade-deleting related ratings; ratings must be removed through the explicit rating deletion workflow.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -874,13 +874,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B34" s="26" t="str">
-        <x:v>v0.31.9</x:v>
+        <x:v>v0.31.10</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>Added</x:v>
+        <x:v>Updated</x:v>
       </x:c>
       <x:c r="D34" s="26" t="str">
-        <x:v>Enables posted-assignment editing directly from Assignment Board game tiles for users who already have assignment-editing permission.</x:v>
+        <x:v>Preserves each game's imported crew sequence with an explicit assignment order stored in Supabase.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -888,13 +888,13 @@
         <x:v>46255.5</x:v>
       </x:c>
       <x:c r="B35" s="26" t="str">
-        <x:v>v0.31.8</x:v>
+        <x:v>v0.31.9</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>Updated</x:v>
+        <x:v>Added</x:v>
       </x:c>
       <x:c r="D35" s="26" t="str">
-        <x:v>Standardizes the default event date across Assignment Board, Schedule, Check-In, Coaching, and date-specific 